--- a/Newdata/成品報工.XLSX
+++ b/Newdata/成品報工.XLSX
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1575" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1506" uniqueCount="178">
   <si>
     <t>100003410</t>
   </si>
@@ -19,34 +19,118 @@
     <t>7</t>
   </si>
   <si>
+    <t>0220</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>1F004</t>
+  </si>
+  <si>
+    <t>1540010</t>
+  </si>
+  <si>
+    <t>旋臂零組件組裝</t>
+  </si>
+  <si>
+    <t>EA</t>
+  </si>
+  <si>
+    <t>PP01</t>
+  </si>
+  <si>
+    <t>1366666</t>
+  </si>
+  <si>
+    <t>REL</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>0230</t>
+  </si>
+  <si>
+    <t>1540008</t>
+  </si>
+  <si>
+    <t>油電系統組裝</t>
+  </si>
+  <si>
+    <t>1366667</t>
+  </si>
+  <si>
+    <t>100003437</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>0170</t>
+  </si>
+  <si>
+    <t>3010082</t>
+  </si>
+  <si>
+    <t>馬達動平衡校正</t>
+  </si>
+  <si>
+    <t>1377178</t>
+  </si>
+  <si>
+    <t>100003438</t>
+  </si>
+  <si>
+    <t>0620</t>
+  </si>
+  <si>
+    <t>2550005</t>
+  </si>
+  <si>
+    <t>線上主軸精度校正</t>
+  </si>
+  <si>
+    <t>1377318</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>0340</t>
+  </si>
+  <si>
+    <t>1377323</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>0370</t>
+  </si>
+  <si>
+    <t>3020026</t>
+  </si>
+  <si>
+    <t>主軸馬達安裝</t>
+  </si>
+  <si>
+    <t>1377329</t>
+  </si>
+  <si>
+    <t>100003446</t>
+  </si>
+  <si>
     <t>0200</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>1F004</t>
-  </si>
-  <si>
     <t>1540003</t>
   </si>
   <si>
     <t>旋臂座介面座清潔</t>
   </si>
   <si>
-    <t>EA</t>
-  </si>
-  <si>
-    <t>PP01</t>
-  </si>
-  <si>
-    <t>1366664</t>
-  </si>
-  <si>
-    <t>REL</t>
-  </si>
-  <si>
-    <t>0</t>
+    <t>1379120</t>
   </si>
   <si>
     <t>0210</t>
@@ -58,166 +142,70 @@
     <t>旋臂組清潔除漆</t>
   </si>
   <si>
-    <t>1366665</t>
-  </si>
-  <si>
-    <t>0220</t>
-  </si>
-  <si>
-    <t>1540010</t>
-  </si>
-  <si>
-    <t>旋臂零組件組裝</t>
-  </si>
-  <si>
-    <t>1366666</t>
-  </si>
-  <si>
-    <t>0230</t>
-  </si>
-  <si>
-    <t>1540008</t>
-  </si>
-  <si>
-    <t>油電系統組裝</t>
-  </si>
-  <si>
-    <t>1366667</t>
-  </si>
-  <si>
-    <t>100003412</t>
-  </si>
-  <si>
-    <t>5</t>
+    <t>1379121</t>
+  </si>
+  <si>
+    <t>1379122</t>
+  </si>
+  <si>
+    <t>1379123</t>
+  </si>
+  <si>
+    <t>100003448</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>0310</t>
+  </si>
+  <si>
+    <t>1379509</t>
+  </si>
+  <si>
+    <t>100003449</t>
+  </si>
+  <si>
+    <t>1379722</t>
+  </si>
+  <si>
+    <t>100003450</t>
+  </si>
+  <si>
+    <t>1379933</t>
+  </si>
+  <si>
+    <t>100003451</t>
+  </si>
+  <si>
+    <t>0392</t>
+  </si>
+  <si>
+    <t>1380248</t>
+  </si>
+  <si>
+    <t>0394</t>
+  </si>
+  <si>
+    <t>1380249</t>
+  </si>
+  <si>
+    <t>0396</t>
+  </si>
+  <si>
+    <t>1380250</t>
+  </si>
+  <si>
+    <t>0398</t>
+  </si>
+  <si>
+    <t>1380251</t>
+  </si>
+  <si>
+    <t>100003465</t>
   </si>
   <si>
     <t>0190</t>
-  </si>
-  <si>
-    <t>3010082</t>
-  </si>
-  <si>
-    <t>馬達動平衡校正</t>
-  </si>
-  <si>
-    <t>1366996</t>
-  </si>
-  <si>
-    <t>100003437</t>
-  </si>
-  <si>
-    <t>0170</t>
-  </si>
-  <si>
-    <t>1377178</t>
-  </si>
-  <si>
-    <t>100003438</t>
-  </si>
-  <si>
-    <t>0620</t>
-  </si>
-  <si>
-    <t>2550005</t>
-  </si>
-  <si>
-    <t>線上主軸精度校正</t>
-  </si>
-  <si>
-    <t>1377318</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>0340</t>
-  </si>
-  <si>
-    <t>1377323</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>0370</t>
-  </si>
-  <si>
-    <t>3020026</t>
-  </si>
-  <si>
-    <t>主軸馬達安裝</t>
-  </si>
-  <si>
-    <t>1377329</t>
-  </si>
-  <si>
-    <t>100003446</t>
-  </si>
-  <si>
-    <t>1379120</t>
-  </si>
-  <si>
-    <t>1379121</t>
-  </si>
-  <si>
-    <t>1379122</t>
-  </si>
-  <si>
-    <t>1379123</t>
-  </si>
-  <si>
-    <t>100003448</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>0310</t>
-  </si>
-  <si>
-    <t>1379509</t>
-  </si>
-  <si>
-    <t>100003449</t>
-  </si>
-  <si>
-    <t>1379722</t>
-  </si>
-  <si>
-    <t>100003450</t>
-  </si>
-  <si>
-    <t>1379933</t>
-  </si>
-  <si>
-    <t>100003451</t>
-  </si>
-  <si>
-    <t>0392</t>
-  </si>
-  <si>
-    <t>1380248</t>
-  </si>
-  <si>
-    <t>0394</t>
-  </si>
-  <si>
-    <t>1380249</t>
-  </si>
-  <si>
-    <t>0396</t>
-  </si>
-  <si>
-    <t>1380250</t>
-  </si>
-  <si>
-    <t>0398</t>
-  </si>
-  <si>
-    <t>1380251</t>
-  </si>
-  <si>
-    <t>100003465</t>
   </si>
   <si>
     <t>1386306</t>
@@ -670,7 +658,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AH68"/>
+  <dimension ref="A1:AH65"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="11" customWidth="1"/>
@@ -711,106 +699,106 @@
   <sheetData>
     <row r="1" spans="1:34">
       <c r="A1" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="H1" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="I1" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="J1" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="K1" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="M1" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="Q1" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="R1" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="S1" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="T1" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="U1" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="V1" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>177</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="2" spans="1:34">
@@ -842,13 +830,13 @@
         <v>7</v>
       </c>
       <c r="J2" s="3">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="K2" s="3">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="L2" s="3">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="M2" t="s">
         <v>8</v>
@@ -942,13 +930,13 @@
         <v>7</v>
       </c>
       <c r="J3" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="K3" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="L3" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="M3" t="s">
         <v>8</v>
@@ -1015,13 +1003,13 @@
     </row>
     <row r="4" spans="1:34">
       <c r="A4" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
         <v>3</v>
@@ -1030,10 +1018,10 @@
         <v>4</v>
       </c>
       <c r="F4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H4" s="2">
         <v>1</v>
@@ -1042,13 +1030,13 @@
         <v>7</v>
       </c>
       <c r="J4" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="K4" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="L4" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="M4" t="s">
         <v>8</v>
@@ -1069,7 +1057,7 @@
         <v>0.000</v>
       </c>
       <c r="S4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="T4" s="5"/>
       <c r="U4" s="5"/>
@@ -1115,13 +1103,13 @@
     </row>
     <row r="5" spans="1:34">
       <c r="A5" t="s">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
         <v>3</v>
@@ -1130,10 +1118,10 @@
         <v>4</v>
       </c>
       <c r="F5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H5" s="2">
         <v>1</v>
@@ -1169,7 +1157,7 @@
         <v>0.000</v>
       </c>
       <c r="S5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="T5" s="5"/>
       <c r="U5" s="5"/>
@@ -1215,13 +1203,13 @@
     </row>
     <row r="6" spans="1:34">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
         <v>3</v>
@@ -1230,10 +1218,10 @@
         <v>4</v>
       </c>
       <c r="F6" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G6" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H6" s="2">
         <v>1</v>
@@ -1315,10 +1303,10 @@
     </row>
     <row r="7" spans="1:34">
       <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s">
         <v>30</v>
-      </c>
-      <c r="B7" t="s">
-        <v>25</v>
       </c>
       <c r="C7" t="s">
         <v>31</v>
@@ -1330,10 +1318,10 @@
         <v>4</v>
       </c>
       <c r="F7" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G7" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H7" s="2">
         <v>1</v>
@@ -1342,13 +1330,13 @@
         <v>7</v>
       </c>
       <c r="J7" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="K7" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="L7" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="M7" t="s">
         <v>8</v>
@@ -1369,7 +1357,7 @@
         <v>0.000</v>
       </c>
       <c r="S7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T7" s="5"/>
       <c r="U7" s="5"/>
@@ -1415,13 +1403,13 @@
     </row>
     <row r="8" spans="1:34">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
         <v>3</v>
@@ -1430,10 +1418,10 @@
         <v>4</v>
       </c>
       <c r="F8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H8" s="2">
         <v>1</v>
@@ -1442,13 +1430,13 @@
         <v>7</v>
       </c>
       <c r="J8" s="3">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="K8" s="3">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="L8" s="3">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="M8" t="s">
         <v>8</v>
@@ -1469,7 +1457,7 @@
         <v>0.000</v>
       </c>
       <c r="S8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="T8" s="5"/>
       <c r="U8" s="5"/>
@@ -1515,13 +1503,13 @@
     </row>
     <row r="9" spans="1:34">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B9" t="s">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
         <v>3</v>
@@ -1530,10 +1518,10 @@
         <v>4</v>
       </c>
       <c r="F9" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="G9" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="H9" s="2">
         <v>1</v>
@@ -1542,13 +1530,13 @@
         <v>7</v>
       </c>
       <c r="J9" s="3">
-        <v>1.5</v>
+        <v>3.0</v>
       </c>
       <c r="K9" s="3">
-        <v>1.5</v>
+        <v>3.0</v>
       </c>
       <c r="L9" s="3">
-        <v>1.5</v>
+        <v>3.0</v>
       </c>
       <c r="M9" t="s">
         <v>8</v>
@@ -1569,7 +1557,7 @@
         <v>0.000</v>
       </c>
       <c r="S9" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="T9" s="5"/>
       <c r="U9" s="5"/>
@@ -1615,13 +1603,13 @@
     </row>
     <row r="10" spans="1:34">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="D10" t="s">
         <v>3</v>
@@ -1630,10 +1618,10 @@
         <v>4</v>
       </c>
       <c r="F10" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="G10" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="H10" s="2">
         <v>1</v>
@@ -1669,7 +1657,7 @@
         <v>0.000</v>
       </c>
       <c r="S10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="T10" s="5"/>
       <c r="U10" s="5"/>
@@ -1715,13 +1703,13 @@
     </row>
     <row r="11" spans="1:34">
       <c r="A11" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="B11" t="s">
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D11" t="s">
         <v>3</v>
@@ -1730,10 +1718,10 @@
         <v>4</v>
       </c>
       <c r="F11" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G11" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="H11" s="2">
         <v>1</v>
@@ -1742,13 +1730,13 @@
         <v>7</v>
       </c>
       <c r="J11" s="3">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="K11" s="3">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="L11" s="3">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="M11" t="s">
         <v>8</v>
@@ -1769,7 +1757,7 @@
         <v>0.000</v>
       </c>
       <c r="S11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="T11" s="5"/>
       <c r="U11" s="5"/>
@@ -1818,10 +1806,10 @@
         <v>46</v>
       </c>
       <c r="B12" t="s">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="C12" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="D12" t="s">
         <v>3</v>
@@ -1830,10 +1818,10 @@
         <v>4</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G12" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H12" s="2">
         <v>1</v>
@@ -1842,13 +1830,13 @@
         <v>7</v>
       </c>
       <c r="J12" s="3">
-        <v>3.0</v>
+        <v>1.5</v>
       </c>
       <c r="K12" s="3">
-        <v>3.0</v>
+        <v>1.5</v>
       </c>
       <c r="L12" s="3">
-        <v>3.0</v>
+        <v>1.5</v>
       </c>
       <c r="M12" t="s">
         <v>8</v>
@@ -1869,7 +1857,7 @@
         <v>0.000</v>
       </c>
       <c r="S12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="T12" s="5"/>
       <c r="U12" s="5"/>
@@ -1915,13 +1903,13 @@
     </row>
     <row r="13" spans="1:34">
       <c r="A13" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B13" t="s">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="C13" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="D13" t="s">
         <v>3</v>
@@ -1930,10 +1918,10 @@
         <v>4</v>
       </c>
       <c r="F13" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G13" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H13" s="2">
         <v>1</v>
@@ -1942,13 +1930,13 @@
         <v>7</v>
       </c>
       <c r="J13" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="K13" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="L13" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="M13" t="s">
         <v>8</v>
@@ -1969,7 +1957,7 @@
         <v>0.000</v>
       </c>
       <c r="S13" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="T13" s="5"/>
       <c r="U13" s="5"/>
@@ -2015,13 +2003,13 @@
     </row>
     <row r="14" spans="1:34">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B14" t="s">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="D14" t="s">
         <v>3</v>
@@ -2030,10 +2018,10 @@
         <v>4</v>
       </c>
       <c r="F14" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G14" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H14" s="2">
         <v>1</v>
@@ -2042,13 +2030,13 @@
         <v>7</v>
       </c>
       <c r="J14" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="K14" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="L14" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="M14" t="s">
         <v>8</v>
@@ -2069,7 +2057,7 @@
         <v>0.000</v>
       </c>
       <c r="S14" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="T14" s="5"/>
       <c r="U14" s="5"/>
@@ -2115,13 +2103,13 @@
     </row>
     <row r="15" spans="1:34">
       <c r="A15" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B15" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C15" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D15" t="s">
         <v>3</v>
@@ -2130,10 +2118,10 @@
         <v>4</v>
       </c>
       <c r="F15" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="G15" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="H15" s="2">
         <v>1</v>
@@ -2142,13 +2130,13 @@
         <v>7</v>
       </c>
       <c r="J15" s="3">
-        <v>1.5</v>
+        <v>1.0</v>
       </c>
       <c r="K15" s="3">
-        <v>1.5</v>
+        <v>1.0</v>
       </c>
       <c r="L15" s="3">
-        <v>1.5</v>
+        <v>1.0</v>
       </c>
       <c r="M15" t="s">
         <v>8</v>
@@ -2169,7 +2157,7 @@
         <v>0.000</v>
       </c>
       <c r="S15" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="T15" s="5"/>
       <c r="U15" s="5"/>
@@ -2215,13 +2203,13 @@
     </row>
     <row r="16" spans="1:34">
       <c r="A16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B16" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C16" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D16" t="s">
         <v>3</v>
@@ -2230,10 +2218,10 @@
         <v>4</v>
       </c>
       <c r="F16" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="G16" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="H16" s="2">
         <v>1</v>
@@ -2242,13 +2230,13 @@
         <v>7</v>
       </c>
       <c r="J16" s="3">
-        <v>1.5</v>
+        <v>3.0</v>
       </c>
       <c r="K16" s="3">
-        <v>1.5</v>
+        <v>3.0</v>
       </c>
       <c r="L16" s="3">
-        <v>1.5</v>
+        <v>3.0</v>
       </c>
       <c r="M16" t="s">
         <v>8</v>
@@ -2269,7 +2257,7 @@
         <v>0.000</v>
       </c>
       <c r="S16" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="T16" s="5"/>
       <c r="U16" s="5"/>
@@ -2315,13 +2303,13 @@
     </row>
     <row r="17" spans="1:34">
       <c r="A17" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B17" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D17" t="s">
         <v>3</v>
@@ -2330,10 +2318,10 @@
         <v>4</v>
       </c>
       <c r="F17" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="G17" t="s">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="H17" s="2">
         <v>1</v>
@@ -2342,13 +2330,13 @@
         <v>7</v>
       </c>
       <c r="J17" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="K17" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="L17" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="M17" t="s">
         <v>8</v>
@@ -2369,7 +2357,7 @@
         <v>0.000</v>
       </c>
       <c r="S17" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="T17" s="5"/>
       <c r="U17" s="5"/>
@@ -2415,13 +2403,13 @@
     </row>
     <row r="18" spans="1:34">
       <c r="A18" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B18" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C18" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D18" t="s">
         <v>3</v>
@@ -2430,10 +2418,10 @@
         <v>4</v>
       </c>
       <c r="F18" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G18" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="H18" s="2">
         <v>1</v>
@@ -2442,13 +2430,13 @@
         <v>7</v>
       </c>
       <c r="J18" s="3">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="K18" s="3">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="L18" s="3">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="M18" t="s">
         <v>8</v>
@@ -2469,7 +2457,7 @@
         <v>0.000</v>
       </c>
       <c r="S18" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="T18" s="5"/>
       <c r="U18" s="5"/>
@@ -2515,13 +2503,13 @@
     </row>
     <row r="19" spans="1:34">
       <c r="A19" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B19" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D19" t="s">
         <v>3</v>
@@ -2530,10 +2518,10 @@
         <v>4</v>
       </c>
       <c r="F19" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G19" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H19" s="2">
         <v>1</v>
@@ -2542,13 +2530,13 @@
         <v>7</v>
       </c>
       <c r="J19" s="3">
-        <v>3.0</v>
+        <v>1.5</v>
       </c>
       <c r="K19" s="3">
-        <v>3.0</v>
+        <v>1.5</v>
       </c>
       <c r="L19" s="3">
-        <v>3.0</v>
+        <v>1.5</v>
       </c>
       <c r="M19" t="s">
         <v>8</v>
@@ -2569,7 +2557,7 @@
         <v>0.000</v>
       </c>
       <c r="S19" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="T19" s="5"/>
       <c r="U19" s="5"/>
@@ -2615,13 +2603,13 @@
     </row>
     <row r="20" spans="1:34">
       <c r="A20" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B20" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C20" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="D20" t="s">
         <v>3</v>
@@ -2630,10 +2618,10 @@
         <v>4</v>
       </c>
       <c r="F20" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G20" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H20" s="2">
         <v>1</v>
@@ -2642,13 +2630,13 @@
         <v>7</v>
       </c>
       <c r="J20" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="K20" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="L20" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="M20" t="s">
         <v>8</v>
@@ -2669,7 +2657,7 @@
         <v>0.000</v>
       </c>
       <c r="S20" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="T20" s="5"/>
       <c r="U20" s="5"/>
@@ -2715,13 +2703,13 @@
     </row>
     <row r="21" spans="1:34">
       <c r="A21" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="B21" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C21" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="D21" t="s">
         <v>3</v>
@@ -2730,10 +2718,10 @@
         <v>4</v>
       </c>
       <c r="F21" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G21" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H21" s="2">
         <v>1</v>
@@ -2742,13 +2730,13 @@
         <v>7</v>
       </c>
       <c r="J21" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="K21" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="L21" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="M21" t="s">
         <v>8</v>
@@ -2769,7 +2757,7 @@
         <v>0.000</v>
       </c>
       <c r="S21" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="T21" s="5"/>
       <c r="U21" s="5"/>
@@ -2815,13 +2803,13 @@
     </row>
     <row r="22" spans="1:34">
       <c r="A22" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="D22" t="s">
         <v>3</v>
@@ -2830,10 +2818,10 @@
         <v>4</v>
       </c>
       <c r="F22" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G22" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H22" s="2">
         <v>1</v>
@@ -2869,7 +2857,7 @@
         <v>0.000</v>
       </c>
       <c r="S22" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="T22" s="5"/>
       <c r="U22" s="5"/>
@@ -2915,13 +2903,13 @@
     </row>
     <row r="23" spans="1:34">
       <c r="A23" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B23" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="C23" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="D23" t="s">
         <v>3</v>
@@ -2930,10 +2918,10 @@
         <v>4</v>
       </c>
       <c r="F23" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G23" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H23" s="2">
         <v>1</v>
@@ -2969,7 +2957,7 @@
         <v>0.000</v>
       </c>
       <c r="S23" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="T23" s="5"/>
       <c r="U23" s="5"/>
@@ -3015,13 +3003,13 @@
     </row>
     <row r="24" spans="1:34">
       <c r="A24" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B24" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="C24" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="D24" t="s">
         <v>3</v>
@@ -3030,10 +3018,10 @@
         <v>4</v>
       </c>
       <c r="F24" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G24" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H24" s="2">
         <v>1</v>
@@ -3069,7 +3057,7 @@
         <v>0.000</v>
       </c>
       <c r="S24" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="T24" s="5"/>
       <c r="U24" s="5"/>
@@ -3115,13 +3103,13 @@
     </row>
     <row r="25" spans="1:34">
       <c r="A25" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="D25" t="s">
         <v>3</v>
@@ -3130,10 +3118,10 @@
         <v>4</v>
       </c>
       <c r="F25" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="G25" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="H25" s="2">
         <v>1</v>
@@ -3142,13 +3130,13 @@
         <v>7</v>
       </c>
       <c r="J25" s="3">
-        <v>1.5</v>
+        <v>1.0</v>
       </c>
       <c r="K25" s="3">
-        <v>1.5</v>
+        <v>1.0</v>
       </c>
       <c r="L25" s="3">
-        <v>1.5</v>
+        <v>1.0</v>
       </c>
       <c r="M25" t="s">
         <v>8</v>
@@ -3169,7 +3157,7 @@
         <v>0.000</v>
       </c>
       <c r="S25" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="T25" s="5"/>
       <c r="U25" s="5"/>
@@ -3215,13 +3203,13 @@
     </row>
     <row r="26" spans="1:34">
       <c r="A26" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B26" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="D26" t="s">
         <v>3</v>
@@ -3230,10 +3218,10 @@
         <v>4</v>
       </c>
       <c r="F26" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="G26" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="H26" s="2">
         <v>1</v>
@@ -3242,13 +3230,13 @@
         <v>7</v>
       </c>
       <c r="J26" s="3">
-        <v>1.5</v>
+        <v>3.0</v>
       </c>
       <c r="K26" s="3">
-        <v>1.5</v>
+        <v>3.0</v>
       </c>
       <c r="L26" s="3">
-        <v>1.5</v>
+        <v>3.0</v>
       </c>
       <c r="M26" t="s">
         <v>8</v>
@@ -3269,7 +3257,7 @@
         <v>0.000</v>
       </c>
       <c r="S26" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="T26" s="5"/>
       <c r="U26" s="5"/>
@@ -3315,13 +3303,13 @@
     </row>
     <row r="27" spans="1:34">
       <c r="A27" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B27" t="s">
-        <v>79</v>
+        <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="D27" t="s">
         <v>3</v>
@@ -3330,10 +3318,10 @@
         <v>4</v>
       </c>
       <c r="F27" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="G27" t="s">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="H27" s="2">
         <v>1</v>
@@ -3342,13 +3330,13 @@
         <v>7</v>
       </c>
       <c r="J27" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="K27" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="L27" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="M27" t="s">
         <v>8</v>
@@ -3415,13 +3403,13 @@
     </row>
     <row r="28" spans="1:34">
       <c r="A28" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B28" t="s">
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D28" t="s">
         <v>3</v>
@@ -3430,10 +3418,10 @@
         <v>4</v>
       </c>
       <c r="F28" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G28" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="H28" s="2">
         <v>1</v>
@@ -3442,13 +3430,13 @@
         <v>7</v>
       </c>
       <c r="J28" s="3">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="K28" s="3">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="L28" s="3">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="M28" t="s">
         <v>8</v>
@@ -3469,7 +3457,7 @@
         <v>0.000</v>
       </c>
       <c r="S28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="T28" s="5"/>
       <c r="U28" s="5"/>
@@ -3515,13 +3503,13 @@
     </row>
     <row r="29" spans="1:34">
       <c r="A29" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B29" t="s">
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="D29" t="s">
         <v>3</v>
@@ -3530,10 +3518,10 @@
         <v>4</v>
       </c>
       <c r="F29" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="G29" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="H29" s="2">
         <v>1</v>
@@ -3542,13 +3530,13 @@
         <v>7</v>
       </c>
       <c r="J29" s="3">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="K29" s="3">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="L29" s="3">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="M29" t="s">
         <v>8</v>
@@ -3615,13 +3603,13 @@
     </row>
     <row r="30" spans="1:34">
       <c r="A30" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B30" t="s">
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="D30" t="s">
         <v>3</v>
@@ -3630,10 +3618,10 @@
         <v>4</v>
       </c>
       <c r="F30" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="G30" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="H30" s="2">
         <v>1</v>
@@ -3642,13 +3630,13 @@
         <v>7</v>
       </c>
       <c r="J30" s="3">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="K30" s="3">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="L30" s="3">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="M30" t="s">
         <v>8</v>
@@ -3715,13 +3703,13 @@
     </row>
     <row r="31" spans="1:34">
       <c r="A31" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B31" t="s">
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D31" t="s">
         <v>3</v>
@@ -3730,10 +3718,10 @@
         <v>4</v>
       </c>
       <c r="F31" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="G31" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="H31" s="2">
         <v>1</v>
@@ -3815,13 +3803,13 @@
     </row>
     <row r="32" spans="1:34">
       <c r="A32" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B32" t="s">
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D32" t="s">
         <v>3</v>
@@ -3830,10 +3818,10 @@
         <v>4</v>
       </c>
       <c r="F32" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G32" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="H32" s="2">
         <v>1</v>
@@ -3842,13 +3830,13 @@
         <v>7</v>
       </c>
       <c r="J32" s="3">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="K32" s="3">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="L32" s="3">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="M32" t="s">
         <v>8</v>
@@ -3869,7 +3857,7 @@
         <v>0.000</v>
       </c>
       <c r="S32" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="T32" s="5"/>
       <c r="U32" s="5"/>
@@ -3915,13 +3903,13 @@
     </row>
     <row r="33" spans="1:34">
       <c r="A33" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B33" t="s">
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="D33" t="s">
         <v>3</v>
@@ -3930,10 +3918,10 @@
         <v>4</v>
       </c>
       <c r="F33" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="G33" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="H33" s="2">
         <v>1</v>
@@ -3942,13 +3930,13 @@
         <v>7</v>
       </c>
       <c r="J33" s="3">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="K33" s="3">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="L33" s="3">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="M33" t="s">
         <v>8</v>
@@ -4015,13 +4003,13 @@
     </row>
     <row r="34" spans="1:34">
       <c r="A34" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B34" t="s">
         <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="D34" t="s">
         <v>3</v>
@@ -4030,10 +4018,10 @@
         <v>4</v>
       </c>
       <c r="F34" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="G34" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="H34" s="2">
         <v>1</v>
@@ -4042,13 +4030,13 @@
         <v>7</v>
       </c>
       <c r="J34" s="3">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="K34" s="3">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="L34" s="3">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="M34" t="s">
         <v>8</v>
@@ -4115,13 +4103,13 @@
     </row>
     <row r="35" spans="1:34">
       <c r="A35" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B35" t="s">
         <v>1</v>
       </c>
       <c r="C35" t="s">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D35" t="s">
         <v>3</v>
@@ -4130,10 +4118,10 @@
         <v>4</v>
       </c>
       <c r="F35" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="G35" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="H35" s="2">
         <v>1</v>
@@ -4215,13 +4203,13 @@
     </row>
     <row r="36" spans="1:34">
       <c r="A36" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B36" t="s">
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D36" t="s">
         <v>3</v>
@@ -4230,10 +4218,10 @@
         <v>4</v>
       </c>
       <c r="F36" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G36" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="H36" s="2">
         <v>1</v>
@@ -4242,13 +4230,13 @@
         <v>7</v>
       </c>
       <c r="J36" s="3">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="K36" s="3">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="L36" s="3">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="M36" t="s">
         <v>8</v>
@@ -4269,7 +4257,7 @@
         <v>0.000</v>
       </c>
       <c r="S36" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="T36" s="5"/>
       <c r="U36" s="5"/>
@@ -4315,13 +4303,13 @@
     </row>
     <row r="37" spans="1:34">
       <c r="A37" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B37" t="s">
         <v>1</v>
       </c>
       <c r="C37" t="s">
-        <v>12</v>
+        <v>93</v>
       </c>
       <c r="D37" t="s">
         <v>3</v>
@@ -4330,10 +4318,10 @@
         <v>4</v>
       </c>
       <c r="F37" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="G37" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="H37" s="2">
         <v>1</v>
@@ -4342,13 +4330,13 @@
         <v>7</v>
       </c>
       <c r="J37" s="3">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="K37" s="3">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="L37" s="3">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="M37" t="s">
         <v>8</v>
@@ -4369,7 +4357,7 @@
         <v>0.000</v>
       </c>
       <c r="S37" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="T37" s="5"/>
       <c r="U37" s="5"/>
@@ -4415,13 +4403,13 @@
     </row>
     <row r="38" spans="1:34">
       <c r="A38" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B38" t="s">
         <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>16</v>
+        <v>95</v>
       </c>
       <c r="D38" t="s">
         <v>3</v>
@@ -4430,10 +4418,10 @@
         <v>4</v>
       </c>
       <c r="F38" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="G38" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="H38" s="2">
         <v>1</v>
@@ -4442,13 +4430,13 @@
         <v>7</v>
       </c>
       <c r="J38" s="3">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="K38" s="3">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="L38" s="3">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="M38" t="s">
         <v>8</v>
@@ -4469,7 +4457,7 @@
         <v>0.000</v>
       </c>
       <c r="S38" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="T38" s="5"/>
       <c r="U38" s="5"/>
@@ -4515,13 +4503,13 @@
     </row>
     <row r="39" spans="1:34">
       <c r="A39" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B39" t="s">
         <v>1</v>
       </c>
       <c r="C39" t="s">
-        <v>20</v>
+        <v>97</v>
       </c>
       <c r="D39" t="s">
         <v>3</v>
@@ -4530,10 +4518,10 @@
         <v>4</v>
       </c>
       <c r="F39" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="G39" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="H39" s="2">
         <v>1</v>
@@ -4569,7 +4557,7 @@
         <v>0.000</v>
       </c>
       <c r="S39" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="T39" s="5"/>
       <c r="U39" s="5"/>
@@ -4615,13 +4603,13 @@
     </row>
     <row r="40" spans="1:34">
       <c r="A40" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B40" t="s">
         <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D40" t="s">
         <v>3</v>
@@ -4630,10 +4618,10 @@
         <v>4</v>
       </c>
       <c r="F40" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G40" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="H40" s="2">
         <v>1</v>
@@ -4642,13 +4630,13 @@
         <v>7</v>
       </c>
       <c r="J40" s="3">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="K40" s="3">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="L40" s="3">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="M40" t="s">
         <v>8</v>
@@ -4669,7 +4657,7 @@
         <v>0.000</v>
       </c>
       <c r="S40" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="T40" s="5"/>
       <c r="U40" s="5"/>
@@ -4715,13 +4703,13 @@
     </row>
     <row r="41" spans="1:34">
       <c r="A41" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B41" t="s">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="C41" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D41" t="s">
         <v>3</v>
@@ -4730,10 +4718,10 @@
         <v>4</v>
       </c>
       <c r="F41" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G41" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H41" s="2">
         <v>1</v>
@@ -4742,13 +4730,13 @@
         <v>7</v>
       </c>
       <c r="J41" s="3">
-        <v>3.0</v>
+        <v>1.5</v>
       </c>
       <c r="K41" s="3">
-        <v>3.0</v>
+        <v>1.5</v>
       </c>
       <c r="L41" s="3">
-        <v>3.0</v>
+        <v>1.5</v>
       </c>
       <c r="M41" t="s">
         <v>8</v>
@@ -4769,7 +4757,7 @@
         <v>0.000</v>
       </c>
       <c r="S41" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="T41" s="5"/>
       <c r="U41" s="5"/>
@@ -4815,13 +4803,13 @@
     </row>
     <row r="42" spans="1:34">
       <c r="A42" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="B42" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C42" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="D42" t="s">
         <v>3</v>
@@ -4830,10 +4818,10 @@
         <v>4</v>
       </c>
       <c r="F42" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G42" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H42" s="2">
         <v>1</v>
@@ -4842,13 +4830,13 @@
         <v>7</v>
       </c>
       <c r="J42" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="K42" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="L42" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="M42" t="s">
         <v>8</v>
@@ -4869,7 +4857,7 @@
         <v>0.000</v>
       </c>
       <c r="S42" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="T42" s="5"/>
       <c r="U42" s="5"/>
@@ -4915,13 +4903,13 @@
     </row>
     <row r="43" spans="1:34">
       <c r="A43" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="B43" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C43" t="s">
-        <v>103</v>
+        <v>23</v>
       </c>
       <c r="D43" t="s">
         <v>3</v>
@@ -4930,10 +4918,10 @@
         <v>4</v>
       </c>
       <c r="F43" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G43" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H43" s="2">
         <v>1</v>
@@ -4969,7 +4957,7 @@
         <v>0.000</v>
       </c>
       <c r="S43" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="T43" s="5"/>
       <c r="U43" s="5"/>
@@ -5015,13 +5003,13 @@
     </row>
     <row r="44" spans="1:34">
       <c r="A44" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B44" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="C44" t="s">
-        <v>106</v>
+        <v>28</v>
       </c>
       <c r="D44" t="s">
         <v>3</v>
@@ -5030,10 +5018,10 @@
         <v>4</v>
       </c>
       <c r="F44" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G44" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H44" s="2">
         <v>1</v>
@@ -5069,7 +5057,7 @@
         <v>0.000</v>
       </c>
       <c r="S44" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T44" s="5"/>
       <c r="U44" s="5"/>
@@ -5115,13 +5103,13 @@
     </row>
     <row r="45" spans="1:34">
       <c r="A45" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B45" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C45" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D45" t="s">
         <v>3</v>
@@ -5130,10 +5118,10 @@
         <v>4</v>
       </c>
       <c r="F45" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G45" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H45" s="2">
         <v>1</v>
@@ -5142,13 +5130,13 @@
         <v>7</v>
       </c>
       <c r="J45" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="K45" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="L45" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="M45" t="s">
         <v>8</v>
@@ -5218,10 +5206,10 @@
         <v>110</v>
       </c>
       <c r="B46" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="C46" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="D46" t="s">
         <v>3</v>
@@ -5230,10 +5218,10 @@
         <v>4</v>
       </c>
       <c r="F46" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="G46" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="H46" s="2">
         <v>1</v>
@@ -5242,13 +5230,13 @@
         <v>7</v>
       </c>
       <c r="J46" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="K46" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="L46" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="M46" t="s">
         <v>8</v>
@@ -5315,13 +5303,13 @@
     </row>
     <row r="47" spans="1:34">
       <c r="A47" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B47" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C47" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="D47" t="s">
         <v>3</v>
@@ -5330,10 +5318,10 @@
         <v>4</v>
       </c>
       <c r="F47" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G47" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H47" s="2">
         <v>1</v>
@@ -5369,7 +5357,7 @@
         <v>0.000</v>
       </c>
       <c r="S47" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="T47" s="5"/>
       <c r="U47" s="5"/>
@@ -5415,13 +5403,13 @@
     </row>
     <row r="48" spans="1:34">
       <c r="A48" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B48" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C48" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D48" t="s">
         <v>3</v>
@@ -5430,10 +5418,10 @@
         <v>4</v>
       </c>
       <c r="F48" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="G48" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="H48" s="2">
         <v>1</v>
@@ -5442,13 +5430,13 @@
         <v>7</v>
       </c>
       <c r="J48" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="K48" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="L48" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="M48" t="s">
         <v>8</v>
@@ -5469,7 +5457,7 @@
         <v>0.000</v>
       </c>
       <c r="S48" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="T48" s="5"/>
       <c r="U48" s="5"/>
@@ -5515,13 +5503,13 @@
     </row>
     <row r="49" spans="1:34">
       <c r="A49" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B49" t="s">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="C49" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="D49" t="s">
         <v>3</v>
@@ -5530,10 +5518,10 @@
         <v>4</v>
       </c>
       <c r="F49" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="G49" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="H49" s="2">
         <v>1</v>
@@ -5542,13 +5530,13 @@
         <v>7</v>
       </c>
       <c r="J49" s="3">
-        <v>1.5</v>
+        <v>1.0</v>
       </c>
       <c r="K49" s="3">
-        <v>1.5</v>
+        <v>1.0</v>
       </c>
       <c r="L49" s="3">
-        <v>1.5</v>
+        <v>1.0</v>
       </c>
       <c r="M49" t="s">
         <v>8</v>
@@ -5569,7 +5557,7 @@
         <v>0.000</v>
       </c>
       <c r="S49" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="T49" s="5"/>
       <c r="U49" s="5"/>
@@ -5618,10 +5606,10 @@
         <v>116</v>
       </c>
       <c r="B50" t="s">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="C50" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="D50" t="s">
         <v>3</v>
@@ -5630,10 +5618,10 @@
         <v>4</v>
       </c>
       <c r="F50" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="G50" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="H50" s="2">
         <v>1</v>
@@ -5642,13 +5630,13 @@
         <v>7</v>
       </c>
       <c r="J50" s="3">
-        <v>1.5</v>
+        <v>3.0</v>
       </c>
       <c r="K50" s="3">
-        <v>1.5</v>
+        <v>3.0</v>
       </c>
       <c r="L50" s="3">
-        <v>1.5</v>
+        <v>3.0</v>
       </c>
       <c r="M50" t="s">
         <v>8</v>
@@ -5669,7 +5657,7 @@
         <v>0.000</v>
       </c>
       <c r="S50" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="T50" s="5"/>
       <c r="U50" s="5"/>
@@ -5715,13 +5703,13 @@
     </row>
     <row r="51" spans="1:34">
       <c r="A51" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B51" t="s">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="C51" t="s">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="D51" t="s">
         <v>3</v>
@@ -5730,10 +5718,10 @@
         <v>4</v>
       </c>
       <c r="F51" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="G51" t="s">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="H51" s="2">
         <v>1</v>
@@ -5742,13 +5730,13 @@
         <v>7</v>
       </c>
       <c r="J51" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="K51" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="L51" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="M51" t="s">
         <v>8</v>
@@ -5815,13 +5803,13 @@
     </row>
     <row r="52" spans="1:34">
       <c r="A52" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B52" t="s">
         <v>1</v>
       </c>
       <c r="C52" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D52" t="s">
         <v>3</v>
@@ -5830,10 +5818,10 @@
         <v>4</v>
       </c>
       <c r="F52" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G52" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="H52" s="2">
         <v>1</v>
@@ -5842,13 +5830,13 @@
         <v>7</v>
       </c>
       <c r="J52" s="3">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="K52" s="3">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="L52" s="3">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="M52" t="s">
         <v>8</v>
@@ -5869,7 +5857,7 @@
         <v>0.000</v>
       </c>
       <c r="S52" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="T52" s="5"/>
       <c r="U52" s="5"/>
@@ -5915,13 +5903,13 @@
     </row>
     <row r="53" spans="1:34">
       <c r="A53" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B53" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C53" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D53" t="s">
         <v>3</v>
@@ -5930,10 +5918,10 @@
         <v>4</v>
       </c>
       <c r="F53" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G53" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H53" s="2">
         <v>1</v>
@@ -5942,13 +5930,13 @@
         <v>7</v>
       </c>
       <c r="J53" s="3">
-        <v>3.0</v>
+        <v>1.5</v>
       </c>
       <c r="K53" s="3">
-        <v>3.0</v>
+        <v>1.5</v>
       </c>
       <c r="L53" s="3">
-        <v>3.0</v>
+        <v>1.5</v>
       </c>
       <c r="M53" t="s">
         <v>8</v>
@@ -6015,13 +6003,13 @@
     </row>
     <row r="54" spans="1:34">
       <c r="A54" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B54" t="s">
         <v>1</v>
       </c>
       <c r="C54" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="D54" t="s">
         <v>3</v>
@@ -6030,10 +6018,10 @@
         <v>4</v>
       </c>
       <c r="F54" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G54" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H54" s="2">
         <v>1</v>
@@ -6042,13 +6030,13 @@
         <v>7</v>
       </c>
       <c r="J54" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="K54" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="L54" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="M54" t="s">
         <v>8</v>
@@ -6069,7 +6057,7 @@
         <v>0.000</v>
       </c>
       <c r="S54" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="T54" s="5"/>
       <c r="U54" s="5"/>
@@ -6115,13 +6103,13 @@
     </row>
     <row r="55" spans="1:34">
       <c r="A55" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B55" t="s">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="C55" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="D55" t="s">
         <v>3</v>
@@ -6130,10 +6118,10 @@
         <v>4</v>
       </c>
       <c r="F55" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G55" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H55" s="2">
         <v>1</v>
@@ -6142,13 +6130,13 @@
         <v>7</v>
       </c>
       <c r="J55" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="K55" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="L55" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="M55" t="s">
         <v>8</v>
@@ -6169,7 +6157,7 @@
         <v>0.000</v>
       </c>
       <c r="S55" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="T55" s="5"/>
       <c r="U55" s="5"/>
@@ -6215,13 +6203,13 @@
     </row>
     <row r="56" spans="1:34">
       <c r="A56" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B56" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="C56" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="D56" t="s">
         <v>3</v>
@@ -6230,10 +6218,10 @@
         <v>4</v>
       </c>
       <c r="F56" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G56" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H56" s="2">
         <v>1</v>
@@ -6269,7 +6257,7 @@
         <v>0.000</v>
       </c>
       <c r="S56" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="T56" s="5"/>
       <c r="U56" s="5"/>
@@ -6315,13 +6303,13 @@
     </row>
     <row r="57" spans="1:34">
       <c r="A57" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B57" t="s">
         <v>1</v>
       </c>
       <c r="C57" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="D57" t="s">
         <v>3</v>
@@ -6330,10 +6318,10 @@
         <v>4</v>
       </c>
       <c r="F57" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="G57" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="H57" s="2">
         <v>1</v>
@@ -6342,13 +6330,13 @@
         <v>7</v>
       </c>
       <c r="J57" s="3">
-        <v>1.5</v>
+        <v>1.0</v>
       </c>
       <c r="K57" s="3">
-        <v>1.5</v>
+        <v>1.0</v>
       </c>
       <c r="L57" s="3">
-        <v>1.5</v>
+        <v>1.0</v>
       </c>
       <c r="M57" t="s">
         <v>8</v>
@@ -6369,7 +6357,7 @@
         <v>0.000</v>
       </c>
       <c r="S57" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="T57" s="5"/>
       <c r="U57" s="5"/>
@@ -6418,10 +6406,10 @@
         <v>129</v>
       </c>
       <c r="B58" t="s">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="C58" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="D58" t="s">
         <v>3</v>
@@ -6430,10 +6418,10 @@
         <v>4</v>
       </c>
       <c r="F58" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="G58" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="H58" s="2">
         <v>1</v>
@@ -6442,13 +6430,13 @@
         <v>7</v>
       </c>
       <c r="J58" s="3">
-        <v>1.5</v>
+        <v>3.0</v>
       </c>
       <c r="K58" s="3">
-        <v>1.5</v>
+        <v>3.0</v>
       </c>
       <c r="L58" s="3">
-        <v>1.5</v>
+        <v>3.0</v>
       </c>
       <c r="M58" t="s">
         <v>8</v>
@@ -6469,7 +6457,7 @@
         <v>0.000</v>
       </c>
       <c r="S58" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="T58" s="5"/>
       <c r="U58" s="5"/>
@@ -6515,13 +6503,13 @@
     </row>
     <row r="59" spans="1:34">
       <c r="A59" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B59" t="s">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="C59" t="s">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="D59" t="s">
         <v>3</v>
@@ -6530,10 +6518,10 @@
         <v>4</v>
       </c>
       <c r="F59" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="G59" t="s">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="H59" s="2">
         <v>1</v>
@@ -6542,13 +6530,13 @@
         <v>7</v>
       </c>
       <c r="J59" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="K59" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="L59" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="M59" t="s">
         <v>8</v>
@@ -6615,13 +6603,13 @@
     </row>
     <row r="60" spans="1:34">
       <c r="A60" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B60" t="s">
         <v>1</v>
       </c>
       <c r="C60" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D60" t="s">
         <v>3</v>
@@ -6630,10 +6618,10 @@
         <v>4</v>
       </c>
       <c r="F60" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G60" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="H60" s="2">
         <v>1</v>
@@ -6642,13 +6630,13 @@
         <v>7</v>
       </c>
       <c r="J60" s="3">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="K60" s="3">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="L60" s="3">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="M60" t="s">
         <v>8</v>
@@ -6669,7 +6657,7 @@
         <v>0.000</v>
       </c>
       <c r="S60" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="T60" s="5"/>
       <c r="U60" s="5"/>
@@ -6715,13 +6703,13 @@
     </row>
     <row r="61" spans="1:34">
       <c r="A61" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B61" t="s">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="C61" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="D61" t="s">
         <v>3</v>
@@ -6730,10 +6718,10 @@
         <v>4</v>
       </c>
       <c r="F61" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G61" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H61" s="2">
         <v>1</v>
@@ -6742,13 +6730,13 @@
         <v>7</v>
       </c>
       <c r="J61" s="3">
-        <v>3.0</v>
+        <v>1.5</v>
       </c>
       <c r="K61" s="3">
-        <v>3.0</v>
+        <v>1.5</v>
       </c>
       <c r="L61" s="3">
-        <v>3.0</v>
+        <v>1.5</v>
       </c>
       <c r="M61" t="s">
         <v>8</v>
@@ -6815,13 +6803,13 @@
     </row>
     <row r="62" spans="1:34">
       <c r="A62" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B62" t="s">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="C62" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="D62" t="s">
         <v>3</v>
@@ -6830,10 +6818,10 @@
         <v>4</v>
       </c>
       <c r="F62" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G62" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H62" s="2">
         <v>1</v>
@@ -6842,13 +6830,13 @@
         <v>7</v>
       </c>
       <c r="J62" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="K62" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="L62" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="M62" t="s">
         <v>8</v>
@@ -6869,7 +6857,7 @@
         <v>0.000</v>
       </c>
       <c r="S62" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="T62" s="5"/>
       <c r="U62" s="5"/>
@@ -6915,13 +6903,13 @@
     </row>
     <row r="63" spans="1:34">
       <c r="A63" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B63" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C63" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D63" t="s">
         <v>3</v>
@@ -6930,10 +6918,10 @@
         <v>4</v>
       </c>
       <c r="F63" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G63" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H63" s="2">
         <v>1</v>
@@ -6942,13 +6930,13 @@
         <v>7</v>
       </c>
       <c r="J63" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="K63" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="L63" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="M63" t="s">
         <v>8</v>
@@ -6969,7 +6957,7 @@
         <v>0.000</v>
       </c>
       <c r="S63" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="T63" s="5"/>
       <c r="U63" s="5"/>
@@ -7015,13 +7003,13 @@
     </row>
     <row r="64" spans="1:34">
       <c r="A64" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B64" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="C64" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="D64" t="s">
         <v>3</v>
@@ -7030,10 +7018,10 @@
         <v>4</v>
       </c>
       <c r="F64" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G64" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H64" s="2">
         <v>1</v>
@@ -7069,7 +7057,7 @@
         <v>0.000</v>
       </c>
       <c r="S64" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="T64" s="5"/>
       <c r="U64" s="5"/>
@@ -7115,13 +7103,13 @@
     </row>
     <row r="65" spans="1:34">
       <c r="A65" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B65" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="C65" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="D65" t="s">
         <v>3</v>
@@ -7130,10 +7118,10 @@
         <v>4</v>
       </c>
       <c r="F65" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G65" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H65" s="2">
         <v>1</v>
@@ -7169,7 +7157,7 @@
         <v>0.000</v>
       </c>
       <c r="S65" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="T65" s="5"/>
       <c r="U65" s="5"/>
@@ -7210,306 +7198,6 @@
         <v>3</v>
       </c>
       <c r="AH65" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="66" spans="1:34">
-      <c r="A66" t="s">
-        <v>142</v>
-      </c>
-      <c r="B66" t="s">
-        <v>25</v>
-      </c>
-      <c r="C66" t="s">
-        <v>31</v>
-      </c>
-      <c r="D66" t="s">
-        <v>3</v>
-      </c>
-      <c r="E66" t="s">
-        <v>4</v>
-      </c>
-      <c r="F66" t="s">
-        <v>27</v>
-      </c>
-      <c r="G66" t="s">
-        <v>28</v>
-      </c>
-      <c r="H66" s="2">
-        <v>1</v>
-      </c>
-      <c r="I66" t="s">
-        <v>7</v>
-      </c>
-      <c r="J66" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="K66" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="L66" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="M66" t="s">
-        <v>8</v>
-      </c>
-      <c r="N66" s="2">
-        <v>0</v>
-      </c>
-      <c r="O66" s="2">
-        <v>0</v>
-      </c>
-      <c r="P66" s="4">
-        <v>0.000</v>
-      </c>
-      <c r="Q66" s="4">
-        <v>0.000</v>
-      </c>
-      <c r="R66" s="4">
-        <v>0.000</v>
-      </c>
-      <c r="S66" t="s">
-        <v>143</v>
-      </c>
-      <c r="T66" s="5"/>
-      <c r="U66" s="5"/>
-      <c r="V66" t="s">
-        <v>10</v>
-      </c>
-      <c r="W66" t="s">
-        <v>3</v>
-      </c>
-      <c r="X66" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y66" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z66" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA66" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB66" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC66" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD66" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE66" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF66" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG66" t="s">
-        <v>3</v>
-      </c>
-      <c r="AH66" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="1:34">
-      <c r="A67" t="s">
-        <v>144</v>
-      </c>
-      <c r="B67" t="s">
-        <v>25</v>
-      </c>
-      <c r="C67" t="s">
-        <v>31</v>
-      </c>
-      <c r="D67" t="s">
-        <v>3</v>
-      </c>
-      <c r="E67" t="s">
-        <v>4</v>
-      </c>
-      <c r="F67" t="s">
-        <v>27</v>
-      </c>
-      <c r="G67" t="s">
-        <v>28</v>
-      </c>
-      <c r="H67" s="2">
-        <v>1</v>
-      </c>
-      <c r="I67" t="s">
-        <v>7</v>
-      </c>
-      <c r="J67" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="K67" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="L67" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="M67" t="s">
-        <v>8</v>
-      </c>
-      <c r="N67" s="2">
-        <v>0</v>
-      </c>
-      <c r="O67" s="2">
-        <v>0</v>
-      </c>
-      <c r="P67" s="4">
-        <v>0.000</v>
-      </c>
-      <c r="Q67" s="4">
-        <v>0.000</v>
-      </c>
-      <c r="R67" s="4">
-        <v>0.000</v>
-      </c>
-      <c r="S67" t="s">
-        <v>145</v>
-      </c>
-      <c r="T67" s="5"/>
-      <c r="U67" s="5"/>
-      <c r="V67" t="s">
-        <v>10</v>
-      </c>
-      <c r="W67" t="s">
-        <v>3</v>
-      </c>
-      <c r="X67" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y67" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z67" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA67" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB67" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC67" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD67" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE67" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF67" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG67" t="s">
-        <v>3</v>
-      </c>
-      <c r="AH67" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="68" spans="1:34">
-      <c r="A68" t="s">
-        <v>146</v>
-      </c>
-      <c r="B68" t="s">
-        <v>25</v>
-      </c>
-      <c r="C68" t="s">
-        <v>31</v>
-      </c>
-      <c r="D68" t="s">
-        <v>3</v>
-      </c>
-      <c r="E68" t="s">
-        <v>4</v>
-      </c>
-      <c r="F68" t="s">
-        <v>27</v>
-      </c>
-      <c r="G68" t="s">
-        <v>28</v>
-      </c>
-      <c r="H68" s="2">
-        <v>1</v>
-      </c>
-      <c r="I68" t="s">
-        <v>7</v>
-      </c>
-      <c r="J68" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="K68" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="L68" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="M68" t="s">
-        <v>8</v>
-      </c>
-      <c r="N68" s="2">
-        <v>0</v>
-      </c>
-      <c r="O68" s="2">
-        <v>0</v>
-      </c>
-      <c r="P68" s="4">
-        <v>0.000</v>
-      </c>
-      <c r="Q68" s="4">
-        <v>0.000</v>
-      </c>
-      <c r="R68" s="4">
-        <v>0.000</v>
-      </c>
-      <c r="S68" t="s">
-        <v>147</v>
-      </c>
-      <c r="T68" s="5"/>
-      <c r="U68" s="5"/>
-      <c r="V68" t="s">
-        <v>10</v>
-      </c>
-      <c r="W68" t="s">
-        <v>3</v>
-      </c>
-      <c r="X68" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y68" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z68" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA68" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB68" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC68" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD68" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE68" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF68" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG68" t="s">
-        <v>3</v>
-      </c>
-      <c r="AH68" t="s">
         <v>3</v>
       </c>
     </row>

--- a/Newdata/成品報工.XLSX
+++ b/Newdata/成品報工.XLSX
@@ -11,87 +11,225 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1506" uniqueCount="178">
-  <si>
-    <t>100003410</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1414" uniqueCount="174">
+  <si>
+    <t>100003438</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>0620</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>1F004</t>
+  </si>
+  <si>
+    <t>2550005</t>
+  </si>
+  <si>
+    <t>線上主軸精度校正</t>
+  </si>
+  <si>
+    <t>EA</t>
+  </si>
+  <si>
+    <t>PP01</t>
+  </si>
+  <si>
+    <t>1377318</t>
+  </si>
+  <si>
+    <t>REL</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>0370</t>
+  </si>
+  <si>
+    <t>3020026</t>
+  </si>
+  <si>
+    <t>主軸馬達安裝</t>
+  </si>
+  <si>
+    <t>1377329</t>
+  </si>
+  <si>
+    <t>100003449</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>0310</t>
+  </si>
+  <si>
+    <t>3010082</t>
+  </si>
+  <si>
+    <t>馬達動平衡校正</t>
+  </si>
+  <si>
+    <t>1379722</t>
+  </si>
+  <si>
+    <t>100003451</t>
+  </si>
+  <si>
+    <t>0394</t>
+  </si>
+  <si>
+    <t>1540009</t>
+  </si>
+  <si>
+    <t>旋臂組清潔除漆</t>
+  </si>
+  <si>
+    <t>1380249</t>
+  </si>
+  <si>
+    <t>0396</t>
+  </si>
+  <si>
+    <t>1540010</t>
+  </si>
+  <si>
+    <t>旋臂零組件組裝</t>
+  </si>
+  <si>
+    <t>1380250</t>
+  </si>
+  <si>
+    <t>0398</t>
+  </si>
+  <si>
+    <t>1540008</t>
+  </si>
+  <si>
+    <t>油電系統組裝</t>
+  </si>
+  <si>
+    <t>1380251</t>
+  </si>
+  <si>
+    <t>100003470</t>
+  </si>
+  <si>
+    <t>1387952</t>
+  </si>
+  <si>
+    <t>100003471</t>
+  </si>
+  <si>
+    <t>1388157</t>
+  </si>
+  <si>
+    <t>100003473</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>0190</t>
+  </si>
+  <si>
+    <t>1390304</t>
+  </si>
+  <si>
+    <t>100003474</t>
+  </si>
+  <si>
+    <t>0170</t>
+  </si>
+  <si>
+    <t>1390405</t>
+  </si>
+  <si>
+    <t>100003475</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>1390493</t>
+  </si>
+  <si>
+    <t>100003481</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
+    <t>0200</t>
+  </si>
+  <si>
+    <t>1540003</t>
+  </si>
+  <si>
+    <t>旋臂座介面座清潔</t>
+  </si>
+  <si>
+    <t>1394059</t>
+  </si>
+  <si>
+    <t>0210</t>
+  </si>
+  <si>
+    <t>1394060</t>
+  </si>
+  <si>
     <t>0220</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>1F004</t>
-  </si>
-  <si>
-    <t>1540010</t>
-  </si>
-  <si>
-    <t>旋臂零組件組裝</t>
-  </si>
-  <si>
-    <t>EA</t>
-  </si>
-  <si>
-    <t>PP01</t>
-  </si>
-  <si>
-    <t>1366666</t>
-  </si>
-  <si>
-    <t>REL</t>
-  </si>
-  <si>
-    <t>0</t>
+    <t>1394061</t>
   </si>
   <si>
     <t>0230</t>
   </si>
   <si>
-    <t>1540008</t>
-  </si>
-  <si>
-    <t>油電系統組裝</t>
-  </si>
-  <si>
-    <t>1366667</t>
-  </si>
-  <si>
-    <t>100003437</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>0170</t>
-  </si>
-  <si>
-    <t>3010082</t>
-  </si>
-  <si>
-    <t>馬達動平衡校正</t>
-  </si>
-  <si>
-    <t>1377178</t>
-  </si>
-  <si>
-    <t>100003438</t>
-  </si>
-  <si>
-    <t>0620</t>
-  </si>
-  <si>
-    <t>2550005</t>
-  </si>
-  <si>
-    <t>線上主軸精度校正</t>
-  </si>
-  <si>
-    <t>1377318</t>
+    <t>1394062</t>
+  </si>
+  <si>
+    <t>100003482</t>
+  </si>
+  <si>
+    <t>1394413</t>
+  </si>
+  <si>
+    <t>1394414</t>
+  </si>
+  <si>
+    <t>1394415</t>
+  </si>
+  <si>
+    <t>1394416</t>
+  </si>
+  <si>
+    <t>100003483</t>
+  </si>
+  <si>
+    <t>1394767</t>
+  </si>
+  <si>
+    <t>1394768</t>
+  </si>
+  <si>
+    <t>1394769</t>
+  </si>
+  <si>
+    <t>1394770</t>
+  </si>
+  <si>
+    <t>100003496</t>
+  </si>
+  <si>
+    <t>1403784</t>
   </si>
   <si>
     <t>2</t>
@@ -100,267 +238,12 @@
     <t>0340</t>
   </si>
   <si>
-    <t>1377323</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>0370</t>
-  </si>
-  <si>
-    <t>3020026</t>
-  </si>
-  <si>
-    <t>主軸馬達安裝</t>
-  </si>
-  <si>
-    <t>1377329</t>
-  </si>
-  <si>
-    <t>100003446</t>
-  </si>
-  <si>
-    <t>0200</t>
-  </si>
-  <si>
-    <t>1540003</t>
-  </si>
-  <si>
-    <t>旋臂座介面座清潔</t>
-  </si>
-  <si>
-    <t>1379120</t>
-  </si>
-  <si>
-    <t>0210</t>
-  </si>
-  <si>
-    <t>1540009</t>
-  </si>
-  <si>
-    <t>旋臂組清潔除漆</t>
-  </si>
-  <si>
-    <t>1379121</t>
-  </si>
-  <si>
-    <t>1379122</t>
-  </si>
-  <si>
-    <t>1379123</t>
-  </si>
-  <si>
-    <t>100003448</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>0310</t>
-  </si>
-  <si>
-    <t>1379509</t>
-  </si>
-  <si>
-    <t>100003449</t>
-  </si>
-  <si>
-    <t>1379722</t>
-  </si>
-  <si>
-    <t>100003450</t>
-  </si>
-  <si>
-    <t>1379933</t>
-  </si>
-  <si>
-    <t>100003451</t>
-  </si>
-  <si>
-    <t>0392</t>
-  </si>
-  <si>
-    <t>1380248</t>
-  </si>
-  <si>
-    <t>0394</t>
-  </si>
-  <si>
-    <t>1380249</t>
-  </si>
-  <si>
-    <t>0396</t>
-  </si>
-  <si>
-    <t>1380250</t>
-  </si>
-  <si>
-    <t>0398</t>
-  </si>
-  <si>
-    <t>1380251</t>
-  </si>
-  <si>
-    <t>100003465</t>
-  </si>
-  <si>
-    <t>0190</t>
-  </si>
-  <si>
-    <t>1386306</t>
-  </si>
-  <si>
-    <t>100003470</t>
-  </si>
-  <si>
-    <t>1387952</t>
-  </si>
-  <si>
-    <t>100003471</t>
-  </si>
-  <si>
-    <t>1388157</t>
-  </si>
-  <si>
-    <t>100003473</t>
-  </si>
-  <si>
-    <t>1390304</t>
-  </si>
-  <si>
-    <t>100003474</t>
-  </si>
-  <si>
-    <t>1390405</t>
-  </si>
-  <si>
-    <t>100003475</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>1390493</t>
-  </si>
-  <si>
-    <t>100003481</t>
-  </si>
-  <si>
-    <t>1394059</t>
-  </si>
-  <si>
-    <t>1394060</t>
-  </si>
-  <si>
-    <t>1394061</t>
-  </si>
-  <si>
-    <t>1394062</t>
-  </si>
-  <si>
-    <t>100003482</t>
-  </si>
-  <si>
-    <t>1394413</t>
-  </si>
-  <si>
-    <t>1394414</t>
-  </si>
-  <si>
-    <t>1394415</t>
-  </si>
-  <si>
-    <t>1394416</t>
-  </si>
-  <si>
-    <t>100003483</t>
-  </si>
-  <si>
-    <t>1394767</t>
-  </si>
-  <si>
-    <t>1394768</t>
-  </si>
-  <si>
-    <t>1394769</t>
-  </si>
-  <si>
-    <t>1394770</t>
-  </si>
-  <si>
-    <t>100003484</t>
-  </si>
-  <si>
-    <t>0030</t>
-  </si>
-  <si>
-    <t>1395068</t>
-  </si>
-  <si>
-    <t>0040</t>
-  </si>
-  <si>
-    <t>1395069</t>
-  </si>
-  <si>
-    <t>0050</t>
-  </si>
-  <si>
-    <t>1395070</t>
-  </si>
-  <si>
-    <t>0060</t>
-  </si>
-  <si>
-    <t>1395071</t>
-  </si>
-  <si>
-    <t>100003486</t>
-  </si>
-  <si>
-    <t>0010</t>
-  </si>
-  <si>
-    <t>1395990</t>
-  </si>
-  <si>
-    <t>100003488</t>
-  </si>
-  <si>
-    <t>1396189</t>
-  </si>
-  <si>
-    <t>100003496</t>
-  </si>
-  <si>
-    <t>1403784</t>
-  </si>
-  <si>
     <t>1403788</t>
   </si>
   <si>
     <t>1403794</t>
   </si>
   <si>
-    <t>100003501</t>
-  </si>
-  <si>
-    <t>1406143</t>
-  </si>
-  <si>
-    <t>100003502</t>
-  </si>
-  <si>
-    <t>1406347</t>
-  </si>
-  <si>
-    <t>100003503</t>
-  </si>
-  <si>
-    <t>1407086</t>
-  </si>
-  <si>
     <t>100003504</t>
   </si>
   <si>
@@ -376,12 +259,6 @@
     <t>1407417</t>
   </si>
   <si>
-    <t>100003506</t>
-  </si>
-  <si>
-    <t>1411329</t>
-  </si>
-  <si>
     <t>100003507</t>
   </si>
   <si>
@@ -415,34 +292,145 @@
     <t>1415197</t>
   </si>
   <si>
-    <t>100003512</t>
-  </si>
-  <si>
-    <t>1413065</t>
-  </si>
-  <si>
     <t>100003515</t>
   </si>
   <si>
     <t>1416109</t>
   </si>
   <si>
-    <t>100003517</t>
-  </si>
-  <si>
-    <t>1418541</t>
-  </si>
-  <si>
-    <t>100003518</t>
-  </si>
-  <si>
-    <t>1418641</t>
-  </si>
-  <si>
-    <t>100003519</t>
-  </si>
-  <si>
-    <t>1418741</t>
+    <t>100003521</t>
+  </si>
+  <si>
+    <t>1422599</t>
+  </si>
+  <si>
+    <t>100003522</t>
+  </si>
+  <si>
+    <t>1422700</t>
+  </si>
+  <si>
+    <t>100003523</t>
+  </si>
+  <si>
+    <t>1426157</t>
+  </si>
+  <si>
+    <t>100003524</t>
+  </si>
+  <si>
+    <t>1426254</t>
+  </si>
+  <si>
+    <t>100003525</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>1426821</t>
+  </si>
+  <si>
+    <t>100003526</t>
+  </si>
+  <si>
+    <t>1427454</t>
+  </si>
+  <si>
+    <t>100003527</t>
+  </si>
+  <si>
+    <t>1428430</t>
+  </si>
+  <si>
+    <t>100003534</t>
+  </si>
+  <si>
+    <t>1429824</t>
+  </si>
+  <si>
+    <t>100003535</t>
+  </si>
+  <si>
+    <t>1430037</t>
+  </si>
+  <si>
+    <t>100003536</t>
+  </si>
+  <si>
+    <t>1430250</t>
+  </si>
+  <si>
+    <t>100003537</t>
+  </si>
+  <si>
+    <t>1430463</t>
+  </si>
+  <si>
+    <t>100003538</t>
+  </si>
+  <si>
+    <t>1431484</t>
+  </si>
+  <si>
+    <t>100003539</t>
+  </si>
+  <si>
+    <t>1431584</t>
+  </si>
+  <si>
+    <t>100003540</t>
+  </si>
+  <si>
+    <t>1431684</t>
+  </si>
+  <si>
+    <t>100003541</t>
+  </si>
+  <si>
+    <t>1431777</t>
+  </si>
+  <si>
+    <t>100003542</t>
+  </si>
+  <si>
+    <t>1431916</t>
+  </si>
+  <si>
+    <t>100003543</t>
+  </si>
+  <si>
+    <t>1432135</t>
+  </si>
+  <si>
+    <t>100003544</t>
+  </si>
+  <si>
+    <t>1432354</t>
+  </si>
+  <si>
+    <t>100003545</t>
+  </si>
+  <si>
+    <t>1432573</t>
+  </si>
+  <si>
+    <t>100003546</t>
+  </si>
+  <si>
+    <t>1432792</t>
+  </si>
+  <si>
+    <t>100003547</t>
+  </si>
+  <si>
+    <t>1433011</t>
+  </si>
+  <si>
+    <t>100003548</t>
+  </si>
+  <si>
+    <t>1433230</t>
   </si>
   <si>
     <t>訂單</t>
@@ -658,7 +646,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AH65"/>
+  <dimension ref="A1:AH61"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="11" customWidth="1"/>
@@ -699,106 +687,106 @@
   <sheetData>
     <row r="1" spans="1:34">
       <c r="A1" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="H1" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="I1" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="J1" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="K1" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="M1" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="Q1" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="R1" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="S1" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="T1" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="U1" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="V1" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>173</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="2" spans="1:34">
@@ -871,7 +859,7 @@
         <v>3</v>
       </c>
       <c r="Y2" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="s">
         <v>3</v>
@@ -906,7 +894,7 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
         <v>12</v>
@@ -971,7 +959,7 @@
         <v>3</v>
       </c>
       <c r="Y3" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z3" t="s">
         <v>3</v>
@@ -1071,7 +1059,7 @@
         <v>3</v>
       </c>
       <c r="Y4" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z4" t="s">
         <v>3</v>
@@ -1106,7 +1094,7 @@
         <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
         <v>23</v>
@@ -1130,13 +1118,13 @@
         <v>7</v>
       </c>
       <c r="J5" s="3">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="K5" s="3">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="L5" s="3">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="M5" t="s">
         <v>8</v>
@@ -1171,7 +1159,7 @@
         <v>3</v>
       </c>
       <c r="Y5" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="s">
         <v>3</v>
@@ -1206,10 +1194,10 @@
         <v>22</v>
       </c>
       <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
         <v>27</v>
-      </c>
-      <c r="C6" t="s">
-        <v>28</v>
       </c>
       <c r="D6" t="s">
         <v>3</v>
@@ -1218,10 +1206,10 @@
         <v>4</v>
       </c>
       <c r="F6" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="G6" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="H6" s="2">
         <v>1</v>
@@ -1230,13 +1218,13 @@
         <v>7</v>
       </c>
       <c r="J6" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="K6" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="L6" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="M6" t="s">
         <v>8</v>
@@ -1257,7 +1245,7 @@
         <v>0.000</v>
       </c>
       <c r="S6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="T6" s="5"/>
       <c r="U6" s="5"/>
@@ -1271,7 +1259,7 @@
         <v>3</v>
       </c>
       <c r="Y6" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z6" t="s">
         <v>3</v>
@@ -1306,7 +1294,7 @@
         <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
         <v>31</v>
@@ -1371,7 +1359,7 @@
         <v>3</v>
       </c>
       <c r="Y7" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z7" t="s">
         <v>3</v>
@@ -1406,10 +1394,10 @@
         <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="D8" t="s">
         <v>3</v>
@@ -1418,10 +1406,10 @@
         <v>4</v>
       </c>
       <c r="F8" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="G8" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="H8" s="2">
         <v>1</v>
@@ -1430,13 +1418,13 @@
         <v>7</v>
       </c>
       <c r="J8" s="3">
-        <v>1.0</v>
+        <v>1.5</v>
       </c>
       <c r="K8" s="3">
-        <v>1.0</v>
+        <v>1.5</v>
       </c>
       <c r="L8" s="3">
-        <v>1.0</v>
+        <v>1.5</v>
       </c>
       <c r="M8" t="s">
         <v>8</v>
@@ -1457,7 +1445,7 @@
         <v>0.000</v>
       </c>
       <c r="S8" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="T8" s="5"/>
       <c r="U8" s="5"/>
@@ -1471,7 +1459,7 @@
         <v>3</v>
       </c>
       <c r="Y8" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z8" t="s">
         <v>3</v>
@@ -1503,13 +1491,13 @@
     </row>
     <row r="9" spans="1:34">
       <c r="A9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="D9" t="s">
         <v>3</v>
@@ -1518,10 +1506,10 @@
         <v>4</v>
       </c>
       <c r="F9" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="G9" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="H9" s="2">
         <v>1</v>
@@ -1530,13 +1518,13 @@
         <v>7</v>
       </c>
       <c r="J9" s="3">
-        <v>3.0</v>
+        <v>1.5</v>
       </c>
       <c r="K9" s="3">
-        <v>3.0</v>
+        <v>1.5</v>
       </c>
       <c r="L9" s="3">
-        <v>3.0</v>
+        <v>1.5</v>
       </c>
       <c r="M9" t="s">
         <v>8</v>
@@ -1557,7 +1545,7 @@
         <v>0.000</v>
       </c>
       <c r="S9" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="T9" s="5"/>
       <c r="U9" s="5"/>
@@ -1571,7 +1559,7 @@
         <v>3</v>
       </c>
       <c r="Y9" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z9" t="s">
         <v>3</v>
@@ -1603,13 +1591,13 @@
     </row>
     <row r="10" spans="1:34">
       <c r="A10" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
         <v>3</v>
@@ -1618,10 +1606,10 @@
         <v>4</v>
       </c>
       <c r="F10" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="G10" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H10" s="2">
         <v>1</v>
@@ -1630,13 +1618,13 @@
         <v>7</v>
       </c>
       <c r="J10" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="K10" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="L10" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="M10" t="s">
         <v>8</v>
@@ -1657,7 +1645,7 @@
         <v>0.000</v>
       </c>
       <c r="S10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="T10" s="5"/>
       <c r="U10" s="5"/>
@@ -1671,7 +1659,7 @@
         <v>3</v>
       </c>
       <c r="Y10" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z10" t="s">
         <v>3</v>
@@ -1703,13 +1691,13 @@
     </row>
     <row r="11" spans="1:34">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="B11" t="s">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
         <v>3</v>
@@ -1718,10 +1706,10 @@
         <v>4</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G11" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H11" s="2">
         <v>1</v>
@@ -1730,13 +1718,13 @@
         <v>7</v>
       </c>
       <c r="J11" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="K11" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="L11" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="M11" t="s">
         <v>8</v>
@@ -1771,7 +1759,7 @@
         <v>3</v>
       </c>
       <c r="Y11" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z11" t="s">
         <v>3</v>
@@ -1809,7 +1797,7 @@
         <v>47</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D12" t="s">
         <v>3</v>
@@ -1857,7 +1845,7 @@
         <v>0.000</v>
       </c>
       <c r="S12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T12" s="5"/>
       <c r="U12" s="5"/>
@@ -1871,7 +1859,7 @@
         <v>3</v>
       </c>
       <c r="Y12" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z12" t="s">
         <v>3</v>
@@ -1903,13 +1891,13 @@
     </row>
     <row r="13" spans="1:34">
       <c r="A13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" t="s">
         <v>50</v>
       </c>
-      <c r="B13" t="s">
-        <v>47</v>
-      </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D13" t="s">
         <v>3</v>
@@ -1918,10 +1906,10 @@
         <v>4</v>
       </c>
       <c r="F13" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="G13" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="H13" s="2">
         <v>1</v>
@@ -1930,13 +1918,13 @@
         <v>7</v>
       </c>
       <c r="J13" s="3">
-        <v>1.5</v>
+        <v>1.0</v>
       </c>
       <c r="K13" s="3">
-        <v>1.5</v>
+        <v>1.0</v>
       </c>
       <c r="L13" s="3">
-        <v>1.5</v>
+        <v>1.0</v>
       </c>
       <c r="M13" t="s">
         <v>8</v>
@@ -1957,7 +1945,7 @@
         <v>0.000</v>
       </c>
       <c r="S13" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="T13" s="5"/>
       <c r="U13" s="5"/>
@@ -1971,7 +1959,7 @@
         <v>3</v>
       </c>
       <c r="Y13" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z13" t="s">
         <v>3</v>
@@ -2003,13 +1991,13 @@
     </row>
     <row r="14" spans="1:34">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B14" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="D14" t="s">
         <v>3</v>
@@ -2018,10 +2006,10 @@
         <v>4</v>
       </c>
       <c r="F14" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G14" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H14" s="2">
         <v>1</v>
@@ -2030,13 +2018,13 @@
         <v>7</v>
       </c>
       <c r="J14" s="3">
-        <v>1.5</v>
+        <v>3.0</v>
       </c>
       <c r="K14" s="3">
-        <v>1.5</v>
+        <v>3.0</v>
       </c>
       <c r="L14" s="3">
-        <v>1.5</v>
+        <v>3.0</v>
       </c>
       <c r="M14" t="s">
         <v>8</v>
@@ -2057,7 +2045,7 @@
         <v>0.000</v>
       </c>
       <c r="S14" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="T14" s="5"/>
       <c r="U14" s="5"/>
@@ -2071,7 +2059,7 @@
         <v>3</v>
       </c>
       <c r="Y14" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z14" t="s">
         <v>3</v>
@@ -2103,13 +2091,13 @@
     </row>
     <row r="15" spans="1:34">
       <c r="A15" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B15" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D15" t="s">
         <v>3</v>
@@ -2118,10 +2106,10 @@
         <v>4</v>
       </c>
       <c r="F15" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="G15" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="H15" s="2">
         <v>1</v>
@@ -2130,13 +2118,13 @@
         <v>7</v>
       </c>
       <c r="J15" s="3">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="K15" s="3">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="L15" s="3">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="M15" t="s">
         <v>8</v>
@@ -2157,7 +2145,7 @@
         <v>0.000</v>
       </c>
       <c r="S15" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="T15" s="5"/>
       <c r="U15" s="5"/>
@@ -2171,7 +2159,7 @@
         <v>3</v>
       </c>
       <c r="Y15" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z15" t="s">
         <v>3</v>
@@ -2203,13 +2191,13 @@
     </row>
     <row r="16" spans="1:34">
       <c r="A16" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B16" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C16" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D16" t="s">
         <v>3</v>
@@ -2218,10 +2206,10 @@
         <v>4</v>
       </c>
       <c r="F16" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="G16" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H16" s="2">
         <v>1</v>
@@ -2230,13 +2218,13 @@
         <v>7</v>
       </c>
       <c r="J16" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="K16" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="L16" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="M16" t="s">
         <v>8</v>
@@ -2257,7 +2245,7 @@
         <v>0.000</v>
       </c>
       <c r="S16" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="T16" s="5"/>
       <c r="U16" s="5"/>
@@ -2271,7 +2259,7 @@
         <v>3</v>
       </c>
       <c r="Y16" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z16" t="s">
         <v>3</v>
@@ -2303,13 +2291,13 @@
     </row>
     <row r="17" spans="1:34">
       <c r="A17" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B17" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C17" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D17" t="s">
         <v>3</v>
@@ -2318,10 +2306,10 @@
         <v>4</v>
       </c>
       <c r="F17" t="s">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="G17" t="s">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="H17" s="2">
         <v>1</v>
@@ -2330,13 +2318,13 @@
         <v>7</v>
       </c>
       <c r="J17" s="3">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="K17" s="3">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="L17" s="3">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="M17" t="s">
         <v>8</v>
@@ -2357,7 +2345,7 @@
         <v>0.000</v>
       </c>
       <c r="S17" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="T17" s="5"/>
       <c r="U17" s="5"/>
@@ -2371,7 +2359,7 @@
         <v>3</v>
       </c>
       <c r="Y17" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z17" t="s">
         <v>3</v>
@@ -2403,13 +2391,13 @@
     </row>
     <row r="18" spans="1:34">
       <c r="A18" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C18" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D18" t="s">
         <v>3</v>
@@ -2418,10 +2406,10 @@
         <v>4</v>
       </c>
       <c r="F18" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="G18" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="H18" s="2">
         <v>1</v>
@@ -2430,13 +2418,13 @@
         <v>7</v>
       </c>
       <c r="J18" s="3">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="K18" s="3">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="L18" s="3">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="M18" t="s">
         <v>8</v>
@@ -2457,7 +2445,7 @@
         <v>0.000</v>
       </c>
       <c r="S18" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="T18" s="5"/>
       <c r="U18" s="5"/>
@@ -2471,7 +2459,7 @@
         <v>3</v>
       </c>
       <c r="Y18" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z18" t="s">
         <v>3</v>
@@ -2503,13 +2491,13 @@
     </row>
     <row r="19" spans="1:34">
       <c r="A19" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B19" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D19" t="s">
         <v>3</v>
@@ -2518,10 +2506,10 @@
         <v>4</v>
       </c>
       <c r="F19" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="G19" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="H19" s="2">
         <v>1</v>
@@ -2530,13 +2518,13 @@
         <v>7</v>
       </c>
       <c r="J19" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="K19" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="L19" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="M19" t="s">
         <v>8</v>
@@ -2557,7 +2545,7 @@
         <v>0.000</v>
       </c>
       <c r="S19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T19" s="5"/>
       <c r="U19" s="5"/>
@@ -2571,7 +2559,7 @@
         <v>3</v>
       </c>
       <c r="Y19" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z19" t="s">
         <v>3</v>
@@ -2603,13 +2591,13 @@
     </row>
     <row r="20" spans="1:34">
       <c r="A20" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B20" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="D20" t="s">
         <v>3</v>
@@ -2618,10 +2606,10 @@
         <v>4</v>
       </c>
       <c r="F20" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G20" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="H20" s="2">
         <v>1</v>
@@ -2630,13 +2618,13 @@
         <v>7</v>
       </c>
       <c r="J20" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="K20" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="L20" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="M20" t="s">
         <v>8</v>
@@ -2657,7 +2645,7 @@
         <v>0.000</v>
       </c>
       <c r="S20" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="T20" s="5"/>
       <c r="U20" s="5"/>
@@ -2671,7 +2659,7 @@
         <v>3</v>
       </c>
       <c r="Y20" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z20" t="s">
         <v>3</v>
@@ -2703,13 +2691,13 @@
     </row>
     <row r="21" spans="1:34">
       <c r="A21" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B21" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C21" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D21" t="s">
         <v>3</v>
@@ -2718,10 +2706,10 @@
         <v>4</v>
       </c>
       <c r="F21" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="G21" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="H21" s="2">
         <v>1</v>
@@ -2730,13 +2718,13 @@
         <v>7</v>
       </c>
       <c r="J21" s="3">
-        <v>1.5</v>
+        <v>1.0</v>
       </c>
       <c r="K21" s="3">
-        <v>1.5</v>
+        <v>1.0</v>
       </c>
       <c r="L21" s="3">
-        <v>1.5</v>
+        <v>1.0</v>
       </c>
       <c r="M21" t="s">
         <v>8</v>
@@ -2757,7 +2745,7 @@
         <v>0.000</v>
       </c>
       <c r="S21" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="T21" s="5"/>
       <c r="U21" s="5"/>
@@ -2771,7 +2759,7 @@
         <v>3</v>
       </c>
       <c r="Y21" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z21" t="s">
         <v>3</v>
@@ -2803,13 +2791,13 @@
     </row>
     <row r="22" spans="1:34">
       <c r="A22" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B22" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="D22" t="s">
         <v>3</v>
@@ -2818,10 +2806,10 @@
         <v>4</v>
       </c>
       <c r="F22" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G22" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H22" s="2">
         <v>1</v>
@@ -2830,13 +2818,13 @@
         <v>7</v>
       </c>
       <c r="J22" s="3">
-        <v>1.5</v>
+        <v>3.0</v>
       </c>
       <c r="K22" s="3">
-        <v>1.5</v>
+        <v>3.0</v>
       </c>
       <c r="L22" s="3">
-        <v>1.5</v>
+        <v>3.0</v>
       </c>
       <c r="M22" t="s">
         <v>8</v>
@@ -2857,7 +2845,7 @@
         <v>0.000</v>
       </c>
       <c r="S22" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="T22" s="5"/>
       <c r="U22" s="5"/>
@@ -2871,7 +2859,7 @@
         <v>3</v>
       </c>
       <c r="Y22" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z22" t="s">
         <v>3</v>
@@ -2903,13 +2891,13 @@
     </row>
     <row r="23" spans="1:34">
       <c r="A23" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B23" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="C23" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="D23" t="s">
         <v>3</v>
@@ -2918,10 +2906,10 @@
         <v>4</v>
       </c>
       <c r="F23" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="G23" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="H23" s="2">
         <v>1</v>
@@ -2930,13 +2918,13 @@
         <v>7</v>
       </c>
       <c r="J23" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="K23" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="L23" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="M23" t="s">
         <v>8</v>
@@ -2957,7 +2945,7 @@
         <v>0.000</v>
       </c>
       <c r="S23" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="T23" s="5"/>
       <c r="U23" s="5"/>
@@ -2971,7 +2959,7 @@
         <v>3</v>
       </c>
       <c r="Y23" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z23" t="s">
         <v>3</v>
@@ -3003,13 +2991,13 @@
     </row>
     <row r="24" spans="1:34">
       <c r="A24" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B24" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="C24" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="D24" t="s">
         <v>3</v>
@@ -3018,10 +3006,10 @@
         <v>4</v>
       </c>
       <c r="F24" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G24" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="H24" s="2">
         <v>1</v>
@@ -3030,13 +3018,13 @@
         <v>7</v>
       </c>
       <c r="J24" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="K24" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="L24" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="M24" t="s">
         <v>8</v>
@@ -3057,7 +3045,7 @@
         <v>0.000</v>
       </c>
       <c r="S24" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="T24" s="5"/>
       <c r="U24" s="5"/>
@@ -3071,7 +3059,7 @@
         <v>3</v>
       </c>
       <c r="Y24" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z24" t="s">
         <v>3</v>
@@ -3103,13 +3091,13 @@
     </row>
     <row r="25" spans="1:34">
       <c r="A25" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B25" t="s">
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="D25" t="s">
         <v>3</v>
@@ -3118,10 +3106,10 @@
         <v>4</v>
       </c>
       <c r="F25" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="G25" t="s">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="H25" s="2">
         <v>1</v>
@@ -3130,13 +3118,13 @@
         <v>7</v>
       </c>
       <c r="J25" s="3">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="K25" s="3">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="L25" s="3">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="M25" t="s">
         <v>8</v>
@@ -3157,7 +3145,7 @@
         <v>0.000</v>
       </c>
       <c r="S25" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="T25" s="5"/>
       <c r="U25" s="5"/>
@@ -3171,7 +3159,7 @@
         <v>3</v>
       </c>
       <c r="Y25" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z25" t="s">
         <v>3</v>
@@ -3203,13 +3191,13 @@
     </row>
     <row r="26" spans="1:34">
       <c r="A26" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B26" t="s">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="C26" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="D26" t="s">
         <v>3</v>
@@ -3218,10 +3206,10 @@
         <v>4</v>
       </c>
       <c r="F26" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="G26" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="H26" s="2">
         <v>1</v>
@@ -3230,13 +3218,13 @@
         <v>7</v>
       </c>
       <c r="J26" s="3">
-        <v>3.0</v>
+        <v>1.5</v>
       </c>
       <c r="K26" s="3">
-        <v>3.0</v>
+        <v>1.5</v>
       </c>
       <c r="L26" s="3">
-        <v>3.0</v>
+        <v>1.5</v>
       </c>
       <c r="M26" t="s">
         <v>8</v>
@@ -3257,7 +3245,7 @@
         <v>0.000</v>
       </c>
       <c r="S26" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="T26" s="5"/>
       <c r="U26" s="5"/>
@@ -3271,7 +3259,7 @@
         <v>3</v>
       </c>
       <c r="Y26" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z26" t="s">
         <v>3</v>
@@ -3303,13 +3291,13 @@
     </row>
     <row r="27" spans="1:34">
       <c r="A27" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B27" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C27" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D27" t="s">
         <v>3</v>
@@ -3318,10 +3306,10 @@
         <v>4</v>
       </c>
       <c r="F27" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G27" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="H27" s="2">
         <v>1</v>
@@ -3357,7 +3345,7 @@
         <v>0.000</v>
       </c>
       <c r="S27" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="T27" s="5"/>
       <c r="U27" s="5"/>
@@ -3371,7 +3359,7 @@
         <v>3</v>
       </c>
       <c r="Y27" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z27" t="s">
         <v>3</v>
@@ -3406,10 +3394,10 @@
         <v>77</v>
       </c>
       <c r="B28" t="s">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="C28" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="D28" t="s">
         <v>3</v>
@@ -3418,10 +3406,10 @@
         <v>4</v>
       </c>
       <c r="F28" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="G28" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="H28" s="2">
         <v>1</v>
@@ -3430,13 +3418,13 @@
         <v>7</v>
       </c>
       <c r="J28" s="3">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="K28" s="3">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="L28" s="3">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="M28" t="s">
         <v>8</v>
@@ -3457,7 +3445,7 @@
         <v>0.000</v>
       </c>
       <c r="S28" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="T28" s="5"/>
       <c r="U28" s="5"/>
@@ -3471,7 +3459,7 @@
         <v>3</v>
       </c>
       <c r="Y28" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z28" t="s">
         <v>3</v>
@@ -3503,13 +3491,13 @@
     </row>
     <row r="29" spans="1:34">
       <c r="A29" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B29" t="s">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="C29" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="D29" t="s">
         <v>3</v>
@@ -3518,10 +3506,10 @@
         <v>4</v>
       </c>
       <c r="F29" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="G29" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="H29" s="2">
         <v>1</v>
@@ -3530,13 +3518,13 @@
         <v>7</v>
       </c>
       <c r="J29" s="3">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="K29" s="3">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="L29" s="3">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="M29" t="s">
         <v>8</v>
@@ -3557,7 +3545,7 @@
         <v>0.000</v>
       </c>
       <c r="S29" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="T29" s="5"/>
       <c r="U29" s="5"/>
@@ -3571,7 +3559,7 @@
         <v>3</v>
       </c>
       <c r="Y29" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z29" t="s">
         <v>3</v>
@@ -3603,13 +3591,13 @@
     </row>
     <row r="30" spans="1:34">
       <c r="A30" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B30" t="s">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="C30" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="D30" t="s">
         <v>3</v>
@@ -3618,10 +3606,10 @@
         <v>4</v>
       </c>
       <c r="F30" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="G30" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="H30" s="2">
         <v>1</v>
@@ -3630,13 +3618,13 @@
         <v>7</v>
       </c>
       <c r="J30" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="K30" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="L30" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="M30" t="s">
         <v>8</v>
@@ -3657,7 +3645,7 @@
         <v>0.000</v>
       </c>
       <c r="S30" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="T30" s="5"/>
       <c r="U30" s="5"/>
@@ -3671,7 +3659,7 @@
         <v>3</v>
       </c>
       <c r="Y30" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z30" t="s">
         <v>3</v>
@@ -3703,13 +3691,13 @@
     </row>
     <row r="31" spans="1:34">
       <c r="A31" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B31" t="s">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="C31" t="s">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="D31" t="s">
         <v>3</v>
@@ -3718,10 +3706,10 @@
         <v>4</v>
       </c>
       <c r="F31" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="G31" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="H31" s="2">
         <v>1</v>
@@ -3757,7 +3745,7 @@
         <v>0.000</v>
       </c>
       <c r="S31" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="T31" s="5"/>
       <c r="U31" s="5"/>
@@ -3771,7 +3759,7 @@
         <v>3</v>
       </c>
       <c r="Y31" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z31" t="s">
         <v>3</v>
@@ -3806,10 +3794,10 @@
         <v>82</v>
       </c>
       <c r="B32" t="s">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="C32" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D32" t="s">
         <v>3</v>
@@ -3818,10 +3806,10 @@
         <v>4</v>
       </c>
       <c r="F32" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G32" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H32" s="2">
         <v>1</v>
@@ -3830,13 +3818,13 @@
         <v>7</v>
       </c>
       <c r="J32" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="K32" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="L32" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="M32" t="s">
         <v>8</v>
@@ -3857,7 +3845,7 @@
         <v>0.000</v>
       </c>
       <c r="S32" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="T32" s="5"/>
       <c r="U32" s="5"/>
@@ -3871,7 +3859,7 @@
         <v>3</v>
       </c>
       <c r="Y32" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z32" t="s">
         <v>3</v>
@@ -3903,13 +3891,13 @@
     </row>
     <row r="33" spans="1:34">
       <c r="A33" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B33" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="D33" t="s">
         <v>3</v>
@@ -3918,10 +3906,10 @@
         <v>4</v>
       </c>
       <c r="F33" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="G33" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="H33" s="2">
         <v>1</v>
@@ -3930,13 +3918,13 @@
         <v>7</v>
       </c>
       <c r="J33" s="3">
-        <v>1.0</v>
+        <v>1.5</v>
       </c>
       <c r="K33" s="3">
-        <v>1.0</v>
+        <v>1.5</v>
       </c>
       <c r="L33" s="3">
-        <v>1.0</v>
+        <v>1.5</v>
       </c>
       <c r="M33" t="s">
         <v>8</v>
@@ -3957,7 +3945,7 @@
         <v>0.000</v>
       </c>
       <c r="S33" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="T33" s="5"/>
       <c r="U33" s="5"/>
@@ -3971,7 +3959,7 @@
         <v>3</v>
       </c>
       <c r="Y33" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z33" t="s">
         <v>3</v>
@@ -4003,13 +3991,13 @@
     </row>
     <row r="34" spans="1:34">
       <c r="A34" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B34" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C34" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="D34" t="s">
         <v>3</v>
@@ -4018,10 +4006,10 @@
         <v>4</v>
       </c>
       <c r="F34" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="G34" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="H34" s="2">
         <v>1</v>
@@ -4030,13 +4018,13 @@
         <v>7</v>
       </c>
       <c r="J34" s="3">
-        <v>3.0</v>
+        <v>1.5</v>
       </c>
       <c r="K34" s="3">
-        <v>3.0</v>
+        <v>1.5</v>
       </c>
       <c r="L34" s="3">
-        <v>3.0</v>
+        <v>1.5</v>
       </c>
       <c r="M34" t="s">
         <v>8</v>
@@ -4057,7 +4045,7 @@
         <v>0.000</v>
       </c>
       <c r="S34" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="T34" s="5"/>
       <c r="U34" s="5"/>
@@ -4071,7 +4059,7 @@
         <v>3</v>
       </c>
       <c r="Y34" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z34" t="s">
         <v>3</v>
@@ -4103,13 +4091,13 @@
     </row>
     <row r="35" spans="1:34">
       <c r="A35" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B35" t="s">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="C35" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="D35" t="s">
         <v>3</v>
@@ -4118,10 +4106,10 @@
         <v>4</v>
       </c>
       <c r="F35" t="s">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="G35" t="s">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="H35" s="2">
         <v>1</v>
@@ -4130,13 +4118,13 @@
         <v>7</v>
       </c>
       <c r="J35" s="3">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="K35" s="3">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="L35" s="3">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="M35" t="s">
         <v>8</v>
@@ -4157,7 +4145,7 @@
         <v>0.000</v>
       </c>
       <c r="S35" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="T35" s="5"/>
       <c r="U35" s="5"/>
@@ -4171,7 +4159,7 @@
         <v>3</v>
       </c>
       <c r="Y35" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z35" t="s">
         <v>3</v>
@@ -4203,13 +4191,13 @@
     </row>
     <row r="36" spans="1:34">
       <c r="A36" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B36" t="s">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="C36" t="s">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="D36" t="s">
         <v>3</v>
@@ -4218,10 +4206,10 @@
         <v>4</v>
       </c>
       <c r="F36" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="G36" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="H36" s="2">
         <v>1</v>
@@ -4230,13 +4218,13 @@
         <v>7</v>
       </c>
       <c r="J36" s="3">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="K36" s="3">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="L36" s="3">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="M36" t="s">
         <v>8</v>
@@ -4257,7 +4245,7 @@
         <v>0.000</v>
       </c>
       <c r="S36" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T36" s="5"/>
       <c r="U36" s="5"/>
@@ -4271,7 +4259,7 @@
         <v>3</v>
       </c>
       <c r="Y36" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z36" t="s">
         <v>3</v>
@@ -4303,13 +4291,13 @@
     </row>
     <row r="37" spans="1:34">
       <c r="A37" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B37" t="s">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="C37" t="s">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="D37" t="s">
         <v>3</v>
@@ -4318,10 +4306,10 @@
         <v>4</v>
       </c>
       <c r="F37" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="G37" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="H37" s="2">
         <v>1</v>
@@ -4330,13 +4318,13 @@
         <v>7</v>
       </c>
       <c r="J37" s="3">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="K37" s="3">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="L37" s="3">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="M37" t="s">
         <v>8</v>
@@ -4357,7 +4345,7 @@
         <v>0.000</v>
       </c>
       <c r="S37" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="T37" s="5"/>
       <c r="U37" s="5"/>
@@ -4371,7 +4359,7 @@
         <v>3</v>
       </c>
       <c r="Y37" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z37" t="s">
         <v>3</v>
@@ -4403,13 +4391,13 @@
     </row>
     <row r="38" spans="1:34">
       <c r="A38" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B38" t="s">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="C38" t="s">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="D38" t="s">
         <v>3</v>
@@ -4418,10 +4406,10 @@
         <v>4</v>
       </c>
       <c r="F38" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="G38" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H38" s="2">
         <v>1</v>
@@ -4430,13 +4418,13 @@
         <v>7</v>
       </c>
       <c r="J38" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="K38" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="L38" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="M38" t="s">
         <v>8</v>
@@ -4457,7 +4445,7 @@
         <v>0.000</v>
       </c>
       <c r="S38" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="T38" s="5"/>
       <c r="U38" s="5"/>
@@ -4471,7 +4459,7 @@
         <v>3</v>
       </c>
       <c r="Y38" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z38" t="s">
         <v>3</v>
@@ -4503,13 +4491,13 @@
     </row>
     <row r="39" spans="1:34">
       <c r="A39" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B39" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C39" t="s">
-        <v>97</v>
+        <v>18</v>
       </c>
       <c r="D39" t="s">
         <v>3</v>
@@ -4518,10 +4506,10 @@
         <v>4</v>
       </c>
       <c r="F39" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="G39" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H39" s="2">
         <v>1</v>
@@ -4530,13 +4518,13 @@
         <v>7</v>
       </c>
       <c r="J39" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="K39" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="L39" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="M39" t="s">
         <v>8</v>
@@ -4557,7 +4545,7 @@
         <v>0.000</v>
       </c>
       <c r="S39" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="T39" s="5"/>
       <c r="U39" s="5"/>
@@ -4571,7 +4559,7 @@
         <v>3</v>
       </c>
       <c r="Y39" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z39" t="s">
         <v>3</v>
@@ -4603,13 +4591,13 @@
     </row>
     <row r="40" spans="1:34">
       <c r="A40" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B40" t="s">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="C40" t="s">
-        <v>99</v>
+        <v>44</v>
       </c>
       <c r="D40" t="s">
         <v>3</v>
@@ -4618,10 +4606,10 @@
         <v>4</v>
       </c>
       <c r="F40" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G40" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H40" s="2">
         <v>1</v>
@@ -4630,13 +4618,13 @@
         <v>7</v>
       </c>
       <c r="J40" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="K40" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="L40" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="M40" t="s">
         <v>8</v>
@@ -4657,7 +4645,7 @@
         <v>0.000</v>
       </c>
       <c r="S40" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="T40" s="5"/>
       <c r="U40" s="5"/>
@@ -4671,7 +4659,7 @@
         <v>3</v>
       </c>
       <c r="Y40" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z40" t="s">
         <v>3</v>
@@ -4703,13 +4691,13 @@
     </row>
     <row r="41" spans="1:34">
       <c r="A41" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B41" t="s">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="C41" t="s">
-        <v>102</v>
+        <v>44</v>
       </c>
       <c r="D41" t="s">
         <v>3</v>
@@ -4757,7 +4745,7 @@
         <v>0.000</v>
       </c>
       <c r="S41" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="T41" s="5"/>
       <c r="U41" s="5"/>
@@ -4771,7 +4759,7 @@
         <v>3</v>
       </c>
       <c r="Y41" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z41" t="s">
         <v>3</v>
@@ -4803,13 +4791,13 @@
     </row>
     <row r="42" spans="1:34">
       <c r="A42" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B42" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="C42" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="D42" t="s">
         <v>3</v>
@@ -4857,7 +4845,7 @@
         <v>0.000</v>
       </c>
       <c r="S42" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="T42" s="5"/>
       <c r="U42" s="5"/>
@@ -4871,7 +4859,7 @@
         <v>3</v>
       </c>
       <c r="Y42" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z42" t="s">
         <v>3</v>
@@ -4903,13 +4891,13 @@
     </row>
     <row r="43" spans="1:34">
       <c r="A43" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B43" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="C43" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="D43" t="s">
         <v>3</v>
@@ -4918,10 +4906,10 @@
         <v>4</v>
       </c>
       <c r="F43" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G43" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H43" s="2">
         <v>1</v>
@@ -4930,13 +4918,13 @@
         <v>7</v>
       </c>
       <c r="J43" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="K43" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="L43" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="M43" t="s">
         <v>8</v>
@@ -4957,7 +4945,7 @@
         <v>0.000</v>
       </c>
       <c r="S43" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="T43" s="5"/>
       <c r="U43" s="5"/>
@@ -4971,7 +4959,7 @@
         <v>3</v>
       </c>
       <c r="Y43" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z43" t="s">
         <v>3</v>
@@ -5003,13 +4991,13 @@
     </row>
     <row r="44" spans="1:34">
       <c r="A44" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B44" t="s">
-        <v>27</v>
+        <v>104</v>
       </c>
       <c r="C44" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="D44" t="s">
         <v>3</v>
@@ -5057,7 +5045,7 @@
         <v>0.000</v>
       </c>
       <c r="S44" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="T44" s="5"/>
       <c r="U44" s="5"/>
@@ -5071,7 +5059,7 @@
         <v>3</v>
       </c>
       <c r="Y44" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z44" t="s">
         <v>3</v>
@@ -5106,10 +5094,10 @@
         <v>106</v>
       </c>
       <c r="B45" t="s">
-        <v>30</v>
+        <v>104</v>
       </c>
       <c r="C45" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="D45" t="s">
         <v>3</v>
@@ -5118,10 +5106,10 @@
         <v>4</v>
       </c>
       <c r="F45" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="G45" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="H45" s="2">
         <v>1</v>
@@ -5130,13 +5118,13 @@
         <v>7</v>
       </c>
       <c r="J45" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="K45" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="L45" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="M45" t="s">
         <v>8</v>
@@ -5157,7 +5145,7 @@
         <v>0.000</v>
       </c>
       <c r="S45" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="T45" s="5"/>
       <c r="U45" s="5"/>
@@ -5171,7 +5159,7 @@
         <v>3</v>
       </c>
       <c r="Y45" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z45" t="s">
         <v>3</v>
@@ -5203,13 +5191,13 @@
     </row>
     <row r="46" spans="1:34">
       <c r="A46" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B46" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C46" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D46" t="s">
         <v>3</v>
@@ -5257,7 +5245,7 @@
         <v>0.000</v>
       </c>
       <c r="S46" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="T46" s="5"/>
       <c r="U46" s="5"/>
@@ -5271,7 +5259,7 @@
         <v>3</v>
       </c>
       <c r="Y46" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z46" t="s">
         <v>3</v>
@@ -5303,13 +5291,13 @@
     </row>
     <row r="47" spans="1:34">
       <c r="A47" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B47" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="C47" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="D47" t="s">
         <v>3</v>
@@ -5357,7 +5345,7 @@
         <v>0.000</v>
       </c>
       <c r="S47" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="T47" s="5"/>
       <c r="U47" s="5"/>
@@ -5371,7 +5359,7 @@
         <v>3</v>
       </c>
       <c r="Y47" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z47" t="s">
         <v>3</v>
@@ -5403,13 +5391,13 @@
     </row>
     <row r="48" spans="1:34">
       <c r="A48" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B48" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="C48" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="D48" t="s">
         <v>3</v>
@@ -5457,7 +5445,7 @@
         <v>0.000</v>
       </c>
       <c r="S48" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="T48" s="5"/>
       <c r="U48" s="5"/>
@@ -5471,7 +5459,7 @@
         <v>3</v>
       </c>
       <c r="Y48" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z48" t="s">
         <v>3</v>
@@ -5503,13 +5491,13 @@
     </row>
     <row r="49" spans="1:34">
       <c r="A49" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B49" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C49" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="D49" t="s">
         <v>3</v>
@@ -5518,10 +5506,10 @@
         <v>4</v>
       </c>
       <c r="F49" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="G49" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="H49" s="2">
         <v>1</v>
@@ -5530,13 +5518,13 @@
         <v>7</v>
       </c>
       <c r="J49" s="3">
-        <v>1.0</v>
+        <v>1.5</v>
       </c>
       <c r="K49" s="3">
-        <v>1.0</v>
+        <v>1.5</v>
       </c>
       <c r="L49" s="3">
-        <v>1.0</v>
+        <v>1.5</v>
       </c>
       <c r="M49" t="s">
         <v>8</v>
@@ -5557,7 +5545,7 @@
         <v>0.000</v>
       </c>
       <c r="S49" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="T49" s="5"/>
       <c r="U49" s="5"/>
@@ -5571,7 +5559,7 @@
         <v>3</v>
       </c>
       <c r="Y49" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z49" t="s">
         <v>3</v>
@@ -5606,10 +5594,10 @@
         <v>116</v>
       </c>
       <c r="B50" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C50" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="D50" t="s">
         <v>3</v>
@@ -5618,10 +5606,10 @@
         <v>4</v>
       </c>
       <c r="F50" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="G50" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="H50" s="2">
         <v>1</v>
@@ -5630,13 +5618,13 @@
         <v>7</v>
       </c>
       <c r="J50" s="3">
-        <v>3.0</v>
+        <v>1.5</v>
       </c>
       <c r="K50" s="3">
-        <v>3.0</v>
+        <v>1.5</v>
       </c>
       <c r="L50" s="3">
-        <v>3.0</v>
+        <v>1.5</v>
       </c>
       <c r="M50" t="s">
         <v>8</v>
@@ -5657,7 +5645,7 @@
         <v>0.000</v>
       </c>
       <c r="S50" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="T50" s="5"/>
       <c r="U50" s="5"/>
@@ -5671,7 +5659,7 @@
         <v>3</v>
       </c>
       <c r="Y50" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z50" t="s">
         <v>3</v>
@@ -5703,13 +5691,13 @@
     </row>
     <row r="51" spans="1:34">
       <c r="A51" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B51" t="s">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="C51" t="s">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="D51" t="s">
         <v>3</v>
@@ -5718,10 +5706,10 @@
         <v>4</v>
       </c>
       <c r="F51" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="G51" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H51" s="2">
         <v>1</v>
@@ -5730,13 +5718,13 @@
         <v>7</v>
       </c>
       <c r="J51" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="K51" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="L51" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="M51" t="s">
         <v>8</v>
@@ -5771,7 +5759,7 @@
         <v>3</v>
       </c>
       <c r="Y51" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z51" t="s">
         <v>3</v>
@@ -5803,13 +5791,13 @@
     </row>
     <row r="52" spans="1:34">
       <c r="A52" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B52" t="s">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="C52" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="D52" t="s">
         <v>3</v>
@@ -5818,10 +5806,10 @@
         <v>4</v>
       </c>
       <c r="F52" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G52" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H52" s="2">
         <v>1</v>
@@ -5830,13 +5818,13 @@
         <v>7</v>
       </c>
       <c r="J52" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="K52" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="L52" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="M52" t="s">
         <v>8</v>
@@ -5857,7 +5845,7 @@
         <v>0.000</v>
       </c>
       <c r="S52" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="T52" s="5"/>
       <c r="U52" s="5"/>
@@ -5871,7 +5859,7 @@
         <v>3</v>
       </c>
       <c r="Y52" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z52" t="s">
         <v>3</v>
@@ -5903,13 +5891,13 @@
     </row>
     <row r="53" spans="1:34">
       <c r="A53" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B53" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="C53" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="D53" t="s">
         <v>3</v>
@@ -5957,7 +5945,7 @@
         <v>0.000</v>
       </c>
       <c r="S53" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="T53" s="5"/>
       <c r="U53" s="5"/>
@@ -5971,7 +5959,7 @@
         <v>3</v>
       </c>
       <c r="Y53" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z53" t="s">
         <v>3</v>
@@ -6003,13 +5991,13 @@
     </row>
     <row r="54" spans="1:34">
       <c r="A54" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B54" t="s">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="C54" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D54" t="s">
         <v>3</v>
@@ -6057,7 +6045,7 @@
         <v>0.000</v>
       </c>
       <c r="S54" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="T54" s="5"/>
       <c r="U54" s="5"/>
@@ -6071,7 +6059,7 @@
         <v>3</v>
       </c>
       <c r="Y54" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z54" t="s">
         <v>3</v>
@@ -6103,13 +6091,13 @@
     </row>
     <row r="55" spans="1:34">
       <c r="A55" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B55" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="C55" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D55" t="s">
         <v>3</v>
@@ -6157,7 +6145,7 @@
         <v>0.000</v>
       </c>
       <c r="S55" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="T55" s="5"/>
       <c r="U55" s="5"/>
@@ -6171,7 +6159,7 @@
         <v>3</v>
       </c>
       <c r="Y55" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z55" t="s">
         <v>3</v>
@@ -6203,13 +6191,13 @@
     </row>
     <row r="56" spans="1:34">
       <c r="A56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B56" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="C56" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D56" t="s">
         <v>3</v>
@@ -6257,7 +6245,7 @@
         <v>0.000</v>
       </c>
       <c r="S56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T56" s="5"/>
       <c r="U56" s="5"/>
@@ -6271,7 +6259,7 @@
         <v>3</v>
       </c>
       <c r="Y56" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z56" t="s">
         <v>3</v>
@@ -6303,13 +6291,13 @@
     </row>
     <row r="57" spans="1:34">
       <c r="A57" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B57" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C57" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="D57" t="s">
         <v>3</v>
@@ -6318,10 +6306,10 @@
         <v>4</v>
       </c>
       <c r="F57" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="G57" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="H57" s="2">
         <v>1</v>
@@ -6330,13 +6318,13 @@
         <v>7</v>
       </c>
       <c r="J57" s="3">
-        <v>1.0</v>
+        <v>1.5</v>
       </c>
       <c r="K57" s="3">
-        <v>1.0</v>
+        <v>1.5</v>
       </c>
       <c r="L57" s="3">
-        <v>1.0</v>
+        <v>1.5</v>
       </c>
       <c r="M57" t="s">
         <v>8</v>
@@ -6357,7 +6345,7 @@
         <v>0.000</v>
       </c>
       <c r="S57" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="T57" s="5"/>
       <c r="U57" s="5"/>
@@ -6371,7 +6359,7 @@
         <v>3</v>
       </c>
       <c r="Y57" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z57" t="s">
         <v>3</v>
@@ -6403,13 +6391,13 @@
     </row>
     <row r="58" spans="1:34">
       <c r="A58" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B58" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C58" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="D58" t="s">
         <v>3</v>
@@ -6418,10 +6406,10 @@
         <v>4</v>
       </c>
       <c r="F58" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="G58" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="H58" s="2">
         <v>1</v>
@@ -6430,13 +6418,13 @@
         <v>7</v>
       </c>
       <c r="J58" s="3">
-        <v>3.0</v>
+        <v>1.5</v>
       </c>
       <c r="K58" s="3">
-        <v>3.0</v>
+        <v>1.5</v>
       </c>
       <c r="L58" s="3">
-        <v>3.0</v>
+        <v>1.5</v>
       </c>
       <c r="M58" t="s">
         <v>8</v>
@@ -6457,7 +6445,7 @@
         <v>0.000</v>
       </c>
       <c r="S58" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="T58" s="5"/>
       <c r="U58" s="5"/>
@@ -6471,7 +6459,7 @@
         <v>3</v>
       </c>
       <c r="Y58" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z58" t="s">
         <v>3</v>
@@ -6503,13 +6491,13 @@
     </row>
     <row r="59" spans="1:34">
       <c r="A59" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B59" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C59" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="D59" t="s">
         <v>3</v>
@@ -6518,10 +6506,10 @@
         <v>4</v>
       </c>
       <c r="F59" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="G59" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H59" s="2">
         <v>1</v>
@@ -6530,13 +6518,13 @@
         <v>7</v>
       </c>
       <c r="J59" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="K59" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="L59" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="M59" t="s">
         <v>8</v>
@@ -6557,7 +6545,7 @@
         <v>0.000</v>
       </c>
       <c r="S59" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="T59" s="5"/>
       <c r="U59" s="5"/>
@@ -6571,7 +6559,7 @@
         <v>3</v>
       </c>
       <c r="Y59" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z59" t="s">
         <v>3</v>
@@ -6603,13 +6591,13 @@
     </row>
     <row r="60" spans="1:34">
       <c r="A60" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="B60" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C60" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="D60" t="s">
         <v>3</v>
@@ -6618,10 +6606,10 @@
         <v>4</v>
       </c>
       <c r="F60" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G60" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H60" s="2">
         <v>1</v>
@@ -6630,13 +6618,13 @@
         <v>7</v>
       </c>
       <c r="J60" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="K60" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="L60" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="M60" t="s">
         <v>8</v>
@@ -6657,7 +6645,7 @@
         <v>0.000</v>
       </c>
       <c r="S60" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="T60" s="5"/>
       <c r="U60" s="5"/>
@@ -6671,7 +6659,7 @@
         <v>3</v>
       </c>
       <c r="Y60" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z60" t="s">
         <v>3</v>
@@ -6703,13 +6691,13 @@
     </row>
     <row r="61" spans="1:34">
       <c r="A61" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B61" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="C61" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D61" t="s">
         <v>3</v>
@@ -6757,7 +6745,7 @@
         <v>0.000</v>
       </c>
       <c r="S61" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="T61" s="5"/>
       <c r="U61" s="5"/>
@@ -6771,7 +6759,7 @@
         <v>3</v>
       </c>
       <c r="Y61" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Z61" t="s">
         <v>3</v>
@@ -6798,406 +6786,6 @@
         <v>3</v>
       </c>
       <c r="AH61" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="62" spans="1:34">
-      <c r="A62" t="s">
-        <v>136</v>
-      </c>
-      <c r="B62" t="s">
-        <v>47</v>
-      </c>
-      <c r="C62" t="s">
-        <v>48</v>
-      </c>
-      <c r="D62" t="s">
-        <v>3</v>
-      </c>
-      <c r="E62" t="s">
-        <v>4</v>
-      </c>
-      <c r="F62" t="s">
-        <v>19</v>
-      </c>
-      <c r="G62" t="s">
-        <v>20</v>
-      </c>
-      <c r="H62" s="2">
-        <v>1</v>
-      </c>
-      <c r="I62" t="s">
-        <v>7</v>
-      </c>
-      <c r="J62" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="K62" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="L62" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="M62" t="s">
-        <v>8</v>
-      </c>
-      <c r="N62" s="2">
-        <v>0</v>
-      </c>
-      <c r="O62" s="2">
-        <v>0</v>
-      </c>
-      <c r="P62" s="4">
-        <v>0.000</v>
-      </c>
-      <c r="Q62" s="4">
-        <v>0.000</v>
-      </c>
-      <c r="R62" s="4">
-        <v>0.000</v>
-      </c>
-      <c r="S62" t="s">
-        <v>137</v>
-      </c>
-      <c r="T62" s="5"/>
-      <c r="U62" s="5"/>
-      <c r="V62" t="s">
-        <v>10</v>
-      </c>
-      <c r="W62" t="s">
-        <v>3</v>
-      </c>
-      <c r="X62" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y62" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z62" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA62" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB62" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC62" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD62" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE62" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF62" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG62" t="s">
-        <v>3</v>
-      </c>
-      <c r="AH62" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63" spans="1:34">
-      <c r="A63" t="s">
-        <v>138</v>
-      </c>
-      <c r="B63" t="s">
-        <v>17</v>
-      </c>
-      <c r="C63" t="s">
-        <v>18</v>
-      </c>
-      <c r="D63" t="s">
-        <v>3</v>
-      </c>
-      <c r="E63" t="s">
-        <v>4</v>
-      </c>
-      <c r="F63" t="s">
-        <v>19</v>
-      </c>
-      <c r="G63" t="s">
-        <v>20</v>
-      </c>
-      <c r="H63" s="2">
-        <v>1</v>
-      </c>
-      <c r="I63" t="s">
-        <v>7</v>
-      </c>
-      <c r="J63" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="K63" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="L63" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="M63" t="s">
-        <v>8</v>
-      </c>
-      <c r="N63" s="2">
-        <v>0</v>
-      </c>
-      <c r="O63" s="2">
-        <v>0</v>
-      </c>
-      <c r="P63" s="4">
-        <v>0.000</v>
-      </c>
-      <c r="Q63" s="4">
-        <v>0.000</v>
-      </c>
-      <c r="R63" s="4">
-        <v>0.000</v>
-      </c>
-      <c r="S63" t="s">
-        <v>139</v>
-      </c>
-      <c r="T63" s="5"/>
-      <c r="U63" s="5"/>
-      <c r="V63" t="s">
-        <v>10</v>
-      </c>
-      <c r="W63" t="s">
-        <v>3</v>
-      </c>
-      <c r="X63" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y63" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z63" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA63" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB63" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC63" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD63" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE63" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF63" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG63" t="s">
-        <v>3</v>
-      </c>
-      <c r="AH63" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="64" spans="1:34">
-      <c r="A64" t="s">
-        <v>140</v>
-      </c>
-      <c r="B64" t="s">
-        <v>17</v>
-      </c>
-      <c r="C64" t="s">
-        <v>18</v>
-      </c>
-      <c r="D64" t="s">
-        <v>3</v>
-      </c>
-      <c r="E64" t="s">
-        <v>4</v>
-      </c>
-      <c r="F64" t="s">
-        <v>19</v>
-      </c>
-      <c r="G64" t="s">
-        <v>20</v>
-      </c>
-      <c r="H64" s="2">
-        <v>1</v>
-      </c>
-      <c r="I64" t="s">
-        <v>7</v>
-      </c>
-      <c r="J64" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="K64" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="L64" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="M64" t="s">
-        <v>8</v>
-      </c>
-      <c r="N64" s="2">
-        <v>0</v>
-      </c>
-      <c r="O64" s="2">
-        <v>0</v>
-      </c>
-      <c r="P64" s="4">
-        <v>0.000</v>
-      </c>
-      <c r="Q64" s="4">
-        <v>0.000</v>
-      </c>
-      <c r="R64" s="4">
-        <v>0.000</v>
-      </c>
-      <c r="S64" t="s">
-        <v>141</v>
-      </c>
-      <c r="T64" s="5"/>
-      <c r="U64" s="5"/>
-      <c r="V64" t="s">
-        <v>10</v>
-      </c>
-      <c r="W64" t="s">
-        <v>3</v>
-      </c>
-      <c r="X64" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y64" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z64" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA64" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB64" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC64" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD64" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE64" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF64" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG64" t="s">
-        <v>3</v>
-      </c>
-      <c r="AH64" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="65" spans="1:34">
-      <c r="A65" t="s">
-        <v>142</v>
-      </c>
-      <c r="B65" t="s">
-        <v>17</v>
-      </c>
-      <c r="C65" t="s">
-        <v>18</v>
-      </c>
-      <c r="D65" t="s">
-        <v>3</v>
-      </c>
-      <c r="E65" t="s">
-        <v>4</v>
-      </c>
-      <c r="F65" t="s">
-        <v>19</v>
-      </c>
-      <c r="G65" t="s">
-        <v>20</v>
-      </c>
-      <c r="H65" s="2">
-        <v>1</v>
-      </c>
-      <c r="I65" t="s">
-        <v>7</v>
-      </c>
-      <c r="J65" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="K65" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="L65" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="M65" t="s">
-        <v>8</v>
-      </c>
-      <c r="N65" s="2">
-        <v>0</v>
-      </c>
-      <c r="O65" s="2">
-        <v>0</v>
-      </c>
-      <c r="P65" s="4">
-        <v>0.000</v>
-      </c>
-      <c r="Q65" s="4">
-        <v>0.000</v>
-      </c>
-      <c r="R65" s="4">
-        <v>0.000</v>
-      </c>
-      <c r="S65" t="s">
-        <v>143</v>
-      </c>
-      <c r="T65" s="5"/>
-      <c r="U65" s="5"/>
-      <c r="V65" t="s">
-        <v>10</v>
-      </c>
-      <c r="W65" t="s">
-        <v>3</v>
-      </c>
-      <c r="X65" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y65" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z65" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA65" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB65" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC65" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD65" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE65" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF65" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG65" t="s">
-        <v>3</v>
-      </c>
-      <c r="AH65" t="s">
         <v>3</v>
       </c>
     </row>

--- a/Newdata/成品報工.XLSX
+++ b/Newdata/成品報工.XLSX
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1414" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1552" uniqueCount="184">
   <si>
     <t>100003438</t>
   </si>
@@ -166,6 +166,27 @@
     <t>7</t>
   </si>
   <si>
+    <t>0210</t>
+  </si>
+  <si>
+    <t>1394060</t>
+  </si>
+  <si>
+    <t>0220</t>
+  </si>
+  <si>
+    <t>1394061</t>
+  </si>
+  <si>
+    <t>0230</t>
+  </si>
+  <si>
+    <t>1394062</t>
+  </si>
+  <si>
+    <t>100003482</t>
+  </si>
+  <si>
     <t>0200</t>
   </si>
   <si>
@@ -175,30 +196,6 @@
     <t>旋臂座介面座清潔</t>
   </si>
   <si>
-    <t>1394059</t>
-  </si>
-  <si>
-    <t>0210</t>
-  </si>
-  <si>
-    <t>1394060</t>
-  </si>
-  <si>
-    <t>0220</t>
-  </si>
-  <si>
-    <t>1394061</t>
-  </si>
-  <si>
-    <t>0230</t>
-  </si>
-  <si>
-    <t>1394062</t>
-  </si>
-  <si>
-    <t>100003482</t>
-  </si>
-  <si>
     <t>1394413</t>
   </si>
   <si>
@@ -431,6 +428,39 @@
   </si>
   <si>
     <t>1433230</t>
+  </si>
+  <si>
+    <t>100003553</t>
+  </si>
+  <si>
+    <t>1436359</t>
+  </si>
+  <si>
+    <t>1436360</t>
+  </si>
+  <si>
+    <t>1436361</t>
+  </si>
+  <si>
+    <t>1436362</t>
+  </si>
+  <si>
+    <t>100003554</t>
+  </si>
+  <si>
+    <t>1436473</t>
+  </si>
+  <si>
+    <t>100003555</t>
+  </si>
+  <si>
+    <t>1436573</t>
+  </si>
+  <si>
+    <t>100003556</t>
+  </si>
+  <si>
+    <t>1437074</t>
   </si>
   <si>
     <t>訂單</t>
@@ -646,7 +676,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AH61"/>
+  <dimension ref="A1:AH67"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="11" customWidth="1"/>
@@ -687,106 +717,106 @@
   <sheetData>
     <row r="1" spans="1:34">
       <c r="A1" s="1" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="Q1" s="6" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="R1" s="6" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
     </row>
     <row r="2" spans="1:34">
@@ -1906,10 +1936,10 @@
         <v>4</v>
       </c>
       <c r="F13" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="G13" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="H13" s="2">
         <v>1</v>
@@ -1918,13 +1948,13 @@
         <v>7</v>
       </c>
       <c r="J13" s="3">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="K13" s="3">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="L13" s="3">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="M13" t="s">
         <v>8</v>
@@ -1945,7 +1975,7 @@
         <v>0.000</v>
       </c>
       <c r="S13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T13" s="5"/>
       <c r="U13" s="5"/>
@@ -1997,7 +2027,7 @@
         <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D14" t="s">
         <v>3</v>
@@ -2006,10 +2036,10 @@
         <v>4</v>
       </c>
       <c r="F14" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G14" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H14" s="2">
         <v>1</v>
@@ -2018,13 +2048,13 @@
         <v>7</v>
       </c>
       <c r="J14" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="K14" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="L14" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="M14" t="s">
         <v>8</v>
@@ -2045,7 +2075,7 @@
         <v>0.000</v>
       </c>
       <c r="S14" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="T14" s="5"/>
       <c r="U14" s="5"/>
@@ -2097,7 +2127,7 @@
         <v>50</v>
       </c>
       <c r="C15" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D15" t="s">
         <v>3</v>
@@ -2106,10 +2136,10 @@
         <v>4</v>
       </c>
       <c r="F15" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G15" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H15" s="2">
         <v>1</v>
@@ -2145,7 +2175,7 @@
         <v>0.000</v>
       </c>
       <c r="S15" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="T15" s="5"/>
       <c r="U15" s="5"/>
@@ -2191,13 +2221,13 @@
     </row>
     <row r="16" spans="1:34">
       <c r="A16" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="B16" t="s">
         <v>50</v>
       </c>
       <c r="C16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D16" t="s">
         <v>3</v>
@@ -2206,10 +2236,10 @@
         <v>4</v>
       </c>
       <c r="F16" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="G16" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="H16" s="2">
         <v>1</v>
@@ -2218,13 +2248,13 @@
         <v>7</v>
       </c>
       <c r="J16" s="3">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="K16" s="3">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="L16" s="3">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="M16" t="s">
         <v>8</v>
@@ -2245,7 +2275,7 @@
         <v>0.000</v>
       </c>
       <c r="S16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="T16" s="5"/>
       <c r="U16" s="5"/>
@@ -2291,7 +2321,7 @@
     </row>
     <row r="17" spans="1:34">
       <c r="A17" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B17" t="s">
         <v>50</v>
@@ -2306,10 +2336,10 @@
         <v>4</v>
       </c>
       <c r="F17" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="G17" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="H17" s="2">
         <v>1</v>
@@ -2318,13 +2348,13 @@
         <v>7</v>
       </c>
       <c r="J17" s="3">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="K17" s="3">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="L17" s="3">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="M17" t="s">
         <v>8</v>
@@ -2391,13 +2421,13 @@
     </row>
     <row r="18" spans="1:34">
       <c r="A18" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B18" t="s">
         <v>50</v>
       </c>
       <c r="C18" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D18" t="s">
         <v>3</v>
@@ -2406,10 +2436,10 @@
         <v>4</v>
       </c>
       <c r="F18" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G18" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H18" s="2">
         <v>1</v>
@@ -2418,13 +2448,13 @@
         <v>7</v>
       </c>
       <c r="J18" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="K18" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="L18" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="M18" t="s">
         <v>8</v>
@@ -2491,13 +2521,13 @@
     </row>
     <row r="19" spans="1:34">
       <c r="A19" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B19" t="s">
         <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D19" t="s">
         <v>3</v>
@@ -2506,10 +2536,10 @@
         <v>4</v>
       </c>
       <c r="F19" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G19" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H19" s="2">
         <v>1</v>
@@ -2591,13 +2621,13 @@
     </row>
     <row r="20" spans="1:34">
       <c r="A20" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B20" t="s">
         <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" t="s">
         <v>3</v>
@@ -2606,10 +2636,10 @@
         <v>4</v>
       </c>
       <c r="F20" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="G20" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="H20" s="2">
         <v>1</v>
@@ -2618,13 +2648,13 @@
         <v>7</v>
       </c>
       <c r="J20" s="3">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="K20" s="3">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="L20" s="3">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="M20" t="s">
         <v>8</v>
@@ -2645,7 +2675,7 @@
         <v>0.000</v>
       </c>
       <c r="S20" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="T20" s="5"/>
       <c r="U20" s="5"/>
@@ -2691,7 +2721,7 @@
     </row>
     <row r="21" spans="1:34">
       <c r="A21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B21" t="s">
         <v>50</v>
@@ -2706,10 +2736,10 @@
         <v>4</v>
       </c>
       <c r="F21" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="G21" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="H21" s="2">
         <v>1</v>
@@ -2718,13 +2748,13 @@
         <v>7</v>
       </c>
       <c r="J21" s="3">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="K21" s="3">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="L21" s="3">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="M21" t="s">
         <v>8</v>
@@ -2791,13 +2821,13 @@
     </row>
     <row r="22" spans="1:34">
       <c r="A22" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B22" t="s">
         <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D22" t="s">
         <v>3</v>
@@ -2806,10 +2836,10 @@
         <v>4</v>
       </c>
       <c r="F22" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G22" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H22" s="2">
         <v>1</v>
@@ -2818,13 +2848,13 @@
         <v>7</v>
       </c>
       <c r="J22" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="K22" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="L22" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="M22" t="s">
         <v>8</v>
@@ -2891,13 +2921,13 @@
     </row>
     <row r="23" spans="1:34">
       <c r="A23" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B23" t="s">
         <v>50</v>
       </c>
       <c r="C23" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D23" t="s">
         <v>3</v>
@@ -2906,10 +2936,10 @@
         <v>4</v>
       </c>
       <c r="F23" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G23" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H23" s="2">
         <v>1</v>
@@ -2991,13 +3021,13 @@
     </row>
     <row r="24" spans="1:34">
       <c r="A24" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B24" t="s">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>59</v>
+        <v>2</v>
       </c>
       <c r="D24" t="s">
         <v>3</v>
@@ -3006,10 +3036,10 @@
         <v>4</v>
       </c>
       <c r="F24" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="G24" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="H24" s="2">
         <v>1</v>
@@ -3045,7 +3075,7 @@
         <v>0.000</v>
       </c>
       <c r="S24" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="T24" s="5"/>
       <c r="U24" s="5"/>
@@ -3091,13 +3121,13 @@
     </row>
     <row r="25" spans="1:34">
       <c r="A25" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B25" t="s">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="C25" t="s">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="D25" t="s">
         <v>3</v>
@@ -3106,10 +3136,10 @@
         <v>4</v>
       </c>
       <c r="F25" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="G25" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H25" s="2">
         <v>1</v>
@@ -3118,13 +3148,13 @@
         <v>7</v>
       </c>
       <c r="J25" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="K25" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="L25" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="M25" t="s">
         <v>8</v>
@@ -3145,7 +3175,7 @@
         <v>0.000</v>
       </c>
       <c r="S25" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T25" s="5"/>
       <c r="U25" s="5"/>
@@ -3191,13 +3221,13 @@
     </row>
     <row r="26" spans="1:34">
       <c r="A26" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B26" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="C26" t="s">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="D26" t="s">
         <v>3</v>
@@ -3206,10 +3236,10 @@
         <v>4</v>
       </c>
       <c r="F26" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G26" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H26" s="2">
         <v>1</v>
@@ -3218,13 +3248,13 @@
         <v>7</v>
       </c>
       <c r="J26" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="K26" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="L26" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="M26" t="s">
         <v>8</v>
@@ -3291,13 +3321,13 @@
     </row>
     <row r="27" spans="1:34">
       <c r="A27" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B27" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="C27" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="D27" t="s">
         <v>3</v>
@@ -3306,10 +3336,10 @@
         <v>4</v>
       </c>
       <c r="F27" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="G27" t="s">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="H27" s="2">
         <v>1</v>
@@ -3318,13 +3348,13 @@
         <v>7</v>
       </c>
       <c r="J27" s="3">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="K27" s="3">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="L27" s="3">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="M27" t="s">
         <v>8</v>
@@ -3345,7 +3375,7 @@
         <v>0.000</v>
       </c>
       <c r="S27" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T27" s="5"/>
       <c r="U27" s="5"/>
@@ -3391,7 +3421,7 @@
     </row>
     <row r="28" spans="1:34">
       <c r="A28" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B28" t="s">
         <v>50</v>
@@ -3406,10 +3436,10 @@
         <v>4</v>
       </c>
       <c r="F28" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="G28" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="H28" s="2">
         <v>1</v>
@@ -3418,13 +3448,13 @@
         <v>7</v>
       </c>
       <c r="J28" s="3">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="K28" s="3">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="L28" s="3">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="M28" t="s">
         <v>8</v>
@@ -3491,13 +3521,13 @@
     </row>
     <row r="29" spans="1:34">
       <c r="A29" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B29" t="s">
         <v>50</v>
       </c>
       <c r="C29" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D29" t="s">
         <v>3</v>
@@ -3506,10 +3536,10 @@
         <v>4</v>
       </c>
       <c r="F29" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G29" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H29" s="2">
         <v>1</v>
@@ -3518,13 +3548,13 @@
         <v>7</v>
       </c>
       <c r="J29" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="K29" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="L29" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="M29" t="s">
         <v>8</v>
@@ -3591,13 +3621,13 @@
     </row>
     <row r="30" spans="1:34">
       <c r="A30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B30" t="s">
         <v>50</v>
       </c>
       <c r="C30" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D30" t="s">
         <v>3</v>
@@ -3606,10 +3636,10 @@
         <v>4</v>
       </c>
       <c r="F30" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G30" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H30" s="2">
         <v>1</v>
@@ -3691,13 +3721,13 @@
     </row>
     <row r="31" spans="1:34">
       <c r="A31" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B31" t="s">
         <v>50</v>
       </c>
       <c r="C31" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="D31" t="s">
         <v>3</v>
@@ -3706,10 +3736,10 @@
         <v>4</v>
       </c>
       <c r="F31" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="G31" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="H31" s="2">
         <v>1</v>
@@ -3718,13 +3748,13 @@
         <v>7</v>
       </c>
       <c r="J31" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="K31" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="L31" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="M31" t="s">
         <v>8</v>
@@ -3745,7 +3775,7 @@
         <v>0.000</v>
       </c>
       <c r="S31" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T31" s="5"/>
       <c r="U31" s="5"/>
@@ -3791,10 +3821,10 @@
     </row>
     <row r="32" spans="1:34">
       <c r="A32" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B32" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="C32" t="s">
         <v>18</v>
@@ -3845,7 +3875,7 @@
         <v>0.000</v>
       </c>
       <c r="S32" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="T32" s="5"/>
       <c r="U32" s="5"/>
@@ -3891,7 +3921,7 @@
     </row>
     <row r="33" spans="1:34">
       <c r="A33" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B33" t="s">
         <v>17</v>
@@ -3945,7 +3975,7 @@
         <v>0.000</v>
       </c>
       <c r="S33" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="T33" s="5"/>
       <c r="U33" s="5"/>
@@ -3991,13 +4021,13 @@
     </row>
     <row r="34" spans="1:34">
       <c r="A34" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B34" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="C34" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="D34" t="s">
         <v>3</v>
@@ -4006,10 +4036,10 @@
         <v>4</v>
       </c>
       <c r="F34" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="G34" t="s">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="H34" s="2">
         <v>1</v>
@@ -4018,13 +4048,13 @@
         <v>7</v>
       </c>
       <c r="J34" s="3">
-        <v>1.5</v>
+        <v>1.0</v>
       </c>
       <c r="K34" s="3">
-        <v>1.5</v>
+        <v>1.0</v>
       </c>
       <c r="L34" s="3">
-        <v>1.5</v>
+        <v>1.0</v>
       </c>
       <c r="M34" t="s">
         <v>8</v>
@@ -4045,7 +4075,7 @@
         <v>0.000</v>
       </c>
       <c r="S34" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T34" s="5"/>
       <c r="U34" s="5"/>
@@ -4091,7 +4121,7 @@
     </row>
     <row r="35" spans="1:34">
       <c r="A35" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B35" t="s">
         <v>50</v>
@@ -4106,10 +4136,10 @@
         <v>4</v>
       </c>
       <c r="F35" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="G35" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="H35" s="2">
         <v>1</v>
@@ -4118,13 +4148,13 @@
         <v>7</v>
       </c>
       <c r="J35" s="3">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="K35" s="3">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="L35" s="3">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="M35" t="s">
         <v>8</v>
@@ -4191,13 +4221,13 @@
     </row>
     <row r="36" spans="1:34">
       <c r="A36" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B36" t="s">
         <v>50</v>
       </c>
       <c r="C36" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D36" t="s">
         <v>3</v>
@@ -4206,10 +4236,10 @@
         <v>4</v>
       </c>
       <c r="F36" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G36" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H36" s="2">
         <v>1</v>
@@ -4218,13 +4248,13 @@
         <v>7</v>
       </c>
       <c r="J36" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="K36" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="L36" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="M36" t="s">
         <v>8</v>
@@ -4291,13 +4321,13 @@
     </row>
     <row r="37" spans="1:34">
       <c r="A37" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B37" t="s">
         <v>50</v>
       </c>
       <c r="C37" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D37" t="s">
         <v>3</v>
@@ -4306,10 +4336,10 @@
         <v>4</v>
       </c>
       <c r="F37" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G37" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H37" s="2">
         <v>1</v>
@@ -4391,13 +4421,13 @@
     </row>
     <row r="38" spans="1:34">
       <c r="A38" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B38" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="C38" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="D38" t="s">
         <v>3</v>
@@ -4406,10 +4436,10 @@
         <v>4</v>
       </c>
       <c r="F38" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="G38" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="H38" s="2">
         <v>1</v>
@@ -4418,13 +4448,13 @@
         <v>7</v>
       </c>
       <c r="J38" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="K38" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="L38" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="M38" t="s">
         <v>8</v>
@@ -4445,7 +4475,7 @@
         <v>0.000</v>
       </c>
       <c r="S38" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="T38" s="5"/>
       <c r="U38" s="5"/>
@@ -4491,13 +4521,13 @@
     </row>
     <row r="39" spans="1:34">
       <c r="A39" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B39" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="C39" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="D39" t="s">
         <v>3</v>
@@ -4545,7 +4575,7 @@
         <v>0.000</v>
       </c>
       <c r="S39" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="T39" s="5"/>
       <c r="U39" s="5"/>
@@ -4591,7 +4621,7 @@
     </row>
     <row r="40" spans="1:34">
       <c r="A40" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B40" t="s">
         <v>40</v>
@@ -4645,7 +4675,7 @@
         <v>0.000</v>
       </c>
       <c r="S40" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="T40" s="5"/>
       <c r="U40" s="5"/>
@@ -4691,7 +4721,7 @@
     </row>
     <row r="41" spans="1:34">
       <c r="A41" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B41" t="s">
         <v>40</v>
@@ -4745,7 +4775,7 @@
         <v>0.000</v>
       </c>
       <c r="S41" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T41" s="5"/>
       <c r="U41" s="5"/>
@@ -4791,7 +4821,7 @@
     </row>
     <row r="42" spans="1:34">
       <c r="A42" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B42" t="s">
         <v>40</v>
@@ -4845,7 +4875,7 @@
         <v>0.000</v>
       </c>
       <c r="S42" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T42" s="5"/>
       <c r="U42" s="5"/>
@@ -4891,13 +4921,13 @@
     </row>
     <row r="43" spans="1:34">
       <c r="A43" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B43" t="s">
-        <v>40</v>
+        <v>103</v>
       </c>
       <c r="C43" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D43" t="s">
         <v>3</v>
@@ -4945,7 +4975,7 @@
         <v>0.000</v>
       </c>
       <c r="S43" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="T43" s="5"/>
       <c r="U43" s="5"/>
@@ -4991,10 +5021,10 @@
     </row>
     <row r="44" spans="1:34">
       <c r="A44" t="s">
+        <v>105</v>
+      </c>
+      <c r="B44" t="s">
         <v>103</v>
-      </c>
-      <c r="B44" t="s">
-        <v>104</v>
       </c>
       <c r="C44" t="s">
         <v>41</v>
@@ -5045,7 +5075,7 @@
         <v>0.000</v>
       </c>
       <c r="S44" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T44" s="5"/>
       <c r="U44" s="5"/>
@@ -5091,13 +5121,13 @@
     </row>
     <row r="45" spans="1:34">
       <c r="A45" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B45" t="s">
-        <v>104</v>
+        <v>40</v>
       </c>
       <c r="C45" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D45" t="s">
         <v>3</v>
@@ -5145,7 +5175,7 @@
         <v>0.000</v>
       </c>
       <c r="S45" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T45" s="5"/>
       <c r="U45" s="5"/>
@@ -5191,13 +5221,13 @@
     </row>
     <row r="46" spans="1:34">
       <c r="A46" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B46" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="C46" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="D46" t="s">
         <v>3</v>
@@ -5245,7 +5275,7 @@
         <v>0.000</v>
       </c>
       <c r="S46" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T46" s="5"/>
       <c r="U46" s="5"/>
@@ -5291,7 +5321,7 @@
     </row>
     <row r="47" spans="1:34">
       <c r="A47" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B47" t="s">
         <v>17</v>
@@ -5345,7 +5375,7 @@
         <v>0.000</v>
       </c>
       <c r="S47" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="T47" s="5"/>
       <c r="U47" s="5"/>
@@ -5391,7 +5421,7 @@
     </row>
     <row r="48" spans="1:34">
       <c r="A48" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B48" t="s">
         <v>17</v>
@@ -5445,7 +5475,7 @@
         <v>0.000</v>
       </c>
       <c r="S48" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="T48" s="5"/>
       <c r="U48" s="5"/>
@@ -5491,7 +5521,7 @@
     </row>
     <row r="49" spans="1:34">
       <c r="A49" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B49" t="s">
         <v>17</v>
@@ -5545,7 +5575,7 @@
         <v>0.000</v>
       </c>
       <c r="S49" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="T49" s="5"/>
       <c r="U49" s="5"/>
@@ -5591,13 +5621,13 @@
     </row>
     <row r="50" spans="1:34">
       <c r="A50" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B50" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="C50" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="D50" t="s">
         <v>3</v>
@@ -5645,7 +5675,7 @@
         <v>0.000</v>
       </c>
       <c r="S50" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="T50" s="5"/>
       <c r="U50" s="5"/>
@@ -5691,7 +5721,7 @@
     </row>
     <row r="51" spans="1:34">
       <c r="A51" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B51" t="s">
         <v>40</v>
@@ -5745,7 +5775,7 @@
         <v>0.000</v>
       </c>
       <c r="S51" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="T51" s="5"/>
       <c r="U51" s="5"/>
@@ -5791,7 +5821,7 @@
     </row>
     <row r="52" spans="1:34">
       <c r="A52" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B52" t="s">
         <v>40</v>
@@ -5845,7 +5875,7 @@
         <v>0.000</v>
       </c>
       <c r="S52" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="T52" s="5"/>
       <c r="U52" s="5"/>
@@ -5891,7 +5921,7 @@
     </row>
     <row r="53" spans="1:34">
       <c r="A53" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B53" t="s">
         <v>40</v>
@@ -5945,7 +5975,7 @@
         <v>0.000</v>
       </c>
       <c r="S53" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="T53" s="5"/>
       <c r="U53" s="5"/>
@@ -5991,13 +6021,13 @@
     </row>
     <row r="54" spans="1:34">
       <c r="A54" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B54" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="C54" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D54" t="s">
         <v>3</v>
@@ -6045,7 +6075,7 @@
         <v>0.000</v>
       </c>
       <c r="S54" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="T54" s="5"/>
       <c r="U54" s="5"/>
@@ -6091,13 +6121,13 @@
     </row>
     <row r="55" spans="1:34">
       <c r="A55" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B55" t="s">
         <v>17</v>
       </c>
       <c r="C55" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D55" t="s">
         <v>3</v>
@@ -6145,7 +6175,7 @@
         <v>0.000</v>
       </c>
       <c r="S55" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="T55" s="5"/>
       <c r="U55" s="5"/>
@@ -6191,13 +6221,13 @@
     </row>
     <row r="56" spans="1:34">
       <c r="A56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B56" t="s">
         <v>17</v>
       </c>
       <c r="C56" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D56" t="s">
         <v>3</v>
@@ -6245,7 +6275,7 @@
         <v>0.000</v>
       </c>
       <c r="S56" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="T56" s="5"/>
       <c r="U56" s="5"/>
@@ -6291,13 +6321,13 @@
     </row>
     <row r="57" spans="1:34">
       <c r="A57" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B57" t="s">
         <v>17</v>
       </c>
       <c r="C57" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D57" t="s">
         <v>3</v>
@@ -6345,7 +6375,7 @@
         <v>0.000</v>
       </c>
       <c r="S57" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="T57" s="5"/>
       <c r="U57" s="5"/>
@@ -6391,13 +6421,13 @@
     </row>
     <row r="58" spans="1:34">
       <c r="A58" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B58" t="s">
         <v>17</v>
       </c>
       <c r="C58" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D58" t="s">
         <v>3</v>
@@ -6445,7 +6475,7 @@
         <v>0.000</v>
       </c>
       <c r="S58" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="T58" s="5"/>
       <c r="U58" s="5"/>
@@ -6491,13 +6521,13 @@
     </row>
     <row r="59" spans="1:34">
       <c r="A59" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B59" t="s">
         <v>17</v>
       </c>
       <c r="C59" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D59" t="s">
         <v>3</v>
@@ -6545,7 +6575,7 @@
         <v>0.000</v>
       </c>
       <c r="S59" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="T59" s="5"/>
       <c r="U59" s="5"/>
@@ -6591,13 +6621,13 @@
     </row>
     <row r="60" spans="1:34">
       <c r="A60" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B60" t="s">
         <v>17</v>
       </c>
       <c r="C60" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D60" t="s">
         <v>3</v>
@@ -6645,7 +6675,7 @@
         <v>0.000</v>
       </c>
       <c r="S60" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="T60" s="5"/>
       <c r="U60" s="5"/>
@@ -6691,13 +6721,13 @@
     </row>
     <row r="61" spans="1:34">
       <c r="A61" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B61" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="C61" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="D61" t="s">
         <v>3</v>
@@ -6706,10 +6736,10 @@
         <v>4</v>
       </c>
       <c r="F61" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="G61" t="s">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="H61" s="2">
         <v>1</v>
@@ -6718,13 +6748,13 @@
         <v>7</v>
       </c>
       <c r="J61" s="3">
-        <v>1.5</v>
+        <v>1.0</v>
       </c>
       <c r="K61" s="3">
-        <v>1.5</v>
+        <v>1.0</v>
       </c>
       <c r="L61" s="3">
-        <v>1.5</v>
+        <v>1.0</v>
       </c>
       <c r="M61" t="s">
         <v>8</v>
@@ -6745,7 +6775,7 @@
         <v>0.000</v>
       </c>
       <c r="S61" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="T61" s="5"/>
       <c r="U61" s="5"/>
@@ -6786,6 +6816,606 @@
         <v>3</v>
       </c>
       <c r="AH61" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:34">
+      <c r="A62" t="s">
+        <v>139</v>
+      </c>
+      <c r="B62" t="s">
+        <v>50</v>
+      </c>
+      <c r="C62" t="s">
+        <v>58</v>
+      </c>
+      <c r="D62" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" t="s">
+        <v>4</v>
+      </c>
+      <c r="F62" t="s">
+        <v>24</v>
+      </c>
+      <c r="G62" t="s">
+        <v>25</v>
+      </c>
+      <c r="H62" s="2">
+        <v>1</v>
+      </c>
+      <c r="I62" t="s">
+        <v>7</v>
+      </c>
+      <c r="J62" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="K62" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L62" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="M62" t="s">
+        <v>8</v>
+      </c>
+      <c r="N62" s="2">
+        <v>0</v>
+      </c>
+      <c r="O62" s="2">
+        <v>0</v>
+      </c>
+      <c r="P62" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="Q62" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="R62" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="S62" t="s">
+        <v>141</v>
+      </c>
+      <c r="T62" s="5"/>
+      <c r="U62" s="5"/>
+      <c r="V62" t="s">
+        <v>10</v>
+      </c>
+      <c r="W62" t="s">
+        <v>3</v>
+      </c>
+      <c r="X62" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y62" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z62" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA62" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB62" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC62" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD62" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE62" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF62" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG62" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH62" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:34">
+      <c r="A63" t="s">
+        <v>139</v>
+      </c>
+      <c r="B63" t="s">
+        <v>50</v>
+      </c>
+      <c r="C63" t="s">
+        <v>51</v>
+      </c>
+      <c r="D63" t="s">
+        <v>3</v>
+      </c>
+      <c r="E63" t="s">
+        <v>4</v>
+      </c>
+      <c r="F63" t="s">
+        <v>28</v>
+      </c>
+      <c r="G63" t="s">
+        <v>29</v>
+      </c>
+      <c r="H63" s="2">
+        <v>1</v>
+      </c>
+      <c r="I63" t="s">
+        <v>7</v>
+      </c>
+      <c r="J63" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="K63" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L63" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="M63" t="s">
+        <v>8</v>
+      </c>
+      <c r="N63" s="2">
+        <v>0</v>
+      </c>
+      <c r="O63" s="2">
+        <v>0</v>
+      </c>
+      <c r="P63" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="Q63" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="R63" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="S63" t="s">
+        <v>142</v>
+      </c>
+      <c r="T63" s="5"/>
+      <c r="U63" s="5"/>
+      <c r="V63" t="s">
+        <v>10</v>
+      </c>
+      <c r="W63" t="s">
+        <v>3</v>
+      </c>
+      <c r="X63" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y63" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z63" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA63" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB63" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC63" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD63" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE63" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF63" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG63" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH63" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:34">
+      <c r="A64" t="s">
+        <v>139</v>
+      </c>
+      <c r="B64" t="s">
+        <v>50</v>
+      </c>
+      <c r="C64" t="s">
+        <v>53</v>
+      </c>
+      <c r="D64" t="s">
+        <v>3</v>
+      </c>
+      <c r="E64" t="s">
+        <v>4</v>
+      </c>
+      <c r="F64" t="s">
+        <v>32</v>
+      </c>
+      <c r="G64" t="s">
+        <v>33</v>
+      </c>
+      <c r="H64" s="2">
+        <v>1</v>
+      </c>
+      <c r="I64" t="s">
+        <v>7</v>
+      </c>
+      <c r="J64" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="K64" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L64" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="M64" t="s">
+        <v>8</v>
+      </c>
+      <c r="N64" s="2">
+        <v>0</v>
+      </c>
+      <c r="O64" s="2">
+        <v>0</v>
+      </c>
+      <c r="P64" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="Q64" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="R64" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="S64" t="s">
+        <v>143</v>
+      </c>
+      <c r="T64" s="5"/>
+      <c r="U64" s="5"/>
+      <c r="V64" t="s">
+        <v>10</v>
+      </c>
+      <c r="W64" t="s">
+        <v>3</v>
+      </c>
+      <c r="X64" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y64" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z64" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA64" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB64" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC64" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD64" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE64" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF64" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG64" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH64" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:34">
+      <c r="A65" t="s">
+        <v>144</v>
+      </c>
+      <c r="B65" t="s">
+        <v>40</v>
+      </c>
+      <c r="C65" t="s">
+        <v>44</v>
+      </c>
+      <c r="D65" t="s">
+        <v>3</v>
+      </c>
+      <c r="E65" t="s">
+        <v>4</v>
+      </c>
+      <c r="F65" t="s">
+        <v>19</v>
+      </c>
+      <c r="G65" t="s">
+        <v>20</v>
+      </c>
+      <c r="H65" s="2">
+        <v>1</v>
+      </c>
+      <c r="I65" t="s">
+        <v>7</v>
+      </c>
+      <c r="J65" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="K65" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="L65" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="M65" t="s">
+        <v>8</v>
+      </c>
+      <c r="N65" s="2">
+        <v>0</v>
+      </c>
+      <c r="O65" s="2">
+        <v>0</v>
+      </c>
+      <c r="P65" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="Q65" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="R65" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="S65" t="s">
+        <v>145</v>
+      </c>
+      <c r="T65" s="5"/>
+      <c r="U65" s="5"/>
+      <c r="V65" t="s">
+        <v>10</v>
+      </c>
+      <c r="W65" t="s">
+        <v>3</v>
+      </c>
+      <c r="X65" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y65" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z65" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA65" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB65" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC65" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD65" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE65" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF65" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG65" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH65" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:34">
+      <c r="A66" t="s">
+        <v>146</v>
+      </c>
+      <c r="B66" t="s">
+        <v>40</v>
+      </c>
+      <c r="C66" t="s">
+        <v>44</v>
+      </c>
+      <c r="D66" t="s">
+        <v>3</v>
+      </c>
+      <c r="E66" t="s">
+        <v>4</v>
+      </c>
+      <c r="F66" t="s">
+        <v>19</v>
+      </c>
+      <c r="G66" t="s">
+        <v>20</v>
+      </c>
+      <c r="H66" s="2">
+        <v>1</v>
+      </c>
+      <c r="I66" t="s">
+        <v>7</v>
+      </c>
+      <c r="J66" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="K66" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="L66" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="M66" t="s">
+        <v>8</v>
+      </c>
+      <c r="N66" s="2">
+        <v>0</v>
+      </c>
+      <c r="O66" s="2">
+        <v>0</v>
+      </c>
+      <c r="P66" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="Q66" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="R66" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="S66" t="s">
+        <v>147</v>
+      </c>
+      <c r="T66" s="5"/>
+      <c r="U66" s="5"/>
+      <c r="V66" t="s">
+        <v>10</v>
+      </c>
+      <c r="W66" t="s">
+        <v>3</v>
+      </c>
+      <c r="X66" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y66" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z66" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA66" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB66" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC66" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD66" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE66" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF66" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG66" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH66" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:34">
+      <c r="A67" t="s">
+        <v>148</v>
+      </c>
+      <c r="B67" t="s">
+        <v>40</v>
+      </c>
+      <c r="C67" t="s">
+        <v>44</v>
+      </c>
+      <c r="D67" t="s">
+        <v>3</v>
+      </c>
+      <c r="E67" t="s">
+        <v>4</v>
+      </c>
+      <c r="F67" t="s">
+        <v>19</v>
+      </c>
+      <c r="G67" t="s">
+        <v>20</v>
+      </c>
+      <c r="H67" s="2">
+        <v>1</v>
+      </c>
+      <c r="I67" t="s">
+        <v>7</v>
+      </c>
+      <c r="J67" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="K67" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="L67" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="M67" t="s">
+        <v>8</v>
+      </c>
+      <c r="N67" s="2">
+        <v>0</v>
+      </c>
+      <c r="O67" s="2">
+        <v>0</v>
+      </c>
+      <c r="P67" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="Q67" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="R67" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="S67" t="s">
+        <v>149</v>
+      </c>
+      <c r="T67" s="5"/>
+      <c r="U67" s="5"/>
+      <c r="V67" t="s">
+        <v>10</v>
+      </c>
+      <c r="W67" t="s">
+        <v>3</v>
+      </c>
+      <c r="X67" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y67" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z67" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA67" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB67" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC67" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD67" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE67" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF67" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG67" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH67" t="s">
         <v>3</v>
       </c>
     </row>

--- a/Newdata/成品報工.XLSX
+++ b/Newdata/成品報工.XLSX
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1552" uniqueCount="184">
-  <si>
-    <t>100003438</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1667" uniqueCount="232">
+  <si>
+    <t>100003496</t>
   </si>
   <si>
     <t>0</t>
@@ -40,7 +40,7 @@
     <t>PP01</t>
   </si>
   <si>
-    <t>1377318</t>
+    <t>1403784</t>
   </si>
   <si>
     <t>REL</t>
@@ -58,10 +58,10 @@
     <t>主軸馬達安裝</t>
   </si>
   <si>
-    <t>1377329</t>
-  </si>
-  <si>
-    <t>100003449</t>
+    <t>1403794</t>
+  </si>
+  <si>
+    <t>100003508</t>
   </si>
   <si>
     <t>6</t>
@@ -76,13 +76,88 @@
     <t>馬達動平衡校正</t>
   </si>
   <si>
-    <t>1379722</t>
-  </si>
-  <si>
-    <t>100003451</t>
-  </si>
-  <si>
-    <t>0394</t>
+    <t>1414691</t>
+  </si>
+  <si>
+    <t>100003534</t>
+  </si>
+  <si>
+    <t>1429824</t>
+  </si>
+  <si>
+    <t>100003535</t>
+  </si>
+  <si>
+    <t>1430037</t>
+  </si>
+  <si>
+    <t>100003536</t>
+  </si>
+  <si>
+    <t>1430250</t>
+  </si>
+  <si>
+    <t>100003537</t>
+  </si>
+  <si>
+    <t>1430463</t>
+  </si>
+  <si>
+    <t>100003543</t>
+  </si>
+  <si>
+    <t>0200</t>
+  </si>
+  <si>
+    <t>1432135</t>
+  </si>
+  <si>
+    <t>100003544</t>
+  </si>
+  <si>
+    <t>1432354</t>
+  </si>
+  <si>
+    <t>100003545</t>
+  </si>
+  <si>
+    <t>1432573</t>
+  </si>
+  <si>
+    <t>100003546</t>
+  </si>
+  <si>
+    <t>1432792</t>
+  </si>
+  <si>
+    <t>100003547</t>
+  </si>
+  <si>
+    <t>1433011</t>
+  </si>
+  <si>
+    <t>100003548</t>
+  </si>
+  <si>
+    <t>1433230</t>
+  </si>
+  <si>
+    <t>100003553</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>0190</t>
+  </si>
+  <si>
+    <t>1540003</t>
+  </si>
+  <si>
+    <t>旋臂座介面座清潔</t>
+  </si>
+  <si>
+    <t>1436359</t>
   </si>
   <si>
     <t>1540009</t>
@@ -91,10 +166,10 @@
     <t>旋臂組清潔除漆</t>
   </si>
   <si>
-    <t>1380249</t>
-  </si>
-  <si>
-    <t>0396</t>
+    <t>1436360</t>
+  </si>
+  <si>
+    <t>0210</t>
   </si>
   <si>
     <t>1540010</t>
@@ -103,10 +178,10 @@
     <t>旋臂零組件組裝</t>
   </si>
   <si>
-    <t>1380250</t>
-  </si>
-  <si>
-    <t>0398</t>
+    <t>1436361</t>
+  </si>
+  <si>
+    <t>0220</t>
   </si>
   <si>
     <t>1540008</t>
@@ -115,352 +190,421 @@
     <t>油電系統組裝</t>
   </si>
   <si>
-    <t>1380251</t>
-  </si>
-  <si>
-    <t>100003470</t>
-  </si>
-  <si>
-    <t>1387952</t>
-  </si>
-  <si>
-    <t>100003471</t>
-  </si>
-  <si>
-    <t>1388157</t>
-  </si>
-  <si>
-    <t>100003473</t>
+    <t>1436362</t>
+  </si>
+  <si>
+    <t>100003559</t>
+  </si>
+  <si>
+    <t>1439653</t>
+  </si>
+  <si>
+    <t>1439654</t>
+  </si>
+  <si>
+    <t>1439655</t>
+  </si>
+  <si>
+    <t>0230</t>
+  </si>
+  <si>
+    <t>1439656</t>
+  </si>
+  <si>
+    <t>100003560</t>
+  </si>
+  <si>
+    <t>0270</t>
+  </si>
+  <si>
+    <t>3050001</t>
+  </si>
+  <si>
+    <t>刀庫安裝</t>
+  </si>
+  <si>
+    <t>1439868</t>
+  </si>
+  <si>
+    <t>0850</t>
+  </si>
+  <si>
+    <t>3050007</t>
+  </si>
+  <si>
+    <t>刀庫調整</t>
+  </si>
+  <si>
+    <t>1439911</t>
+  </si>
+  <si>
+    <t>0860</t>
+  </si>
+  <si>
+    <t>3050002</t>
+  </si>
+  <si>
+    <t>刀庫合刀作業</t>
+  </si>
+  <si>
+    <t>1439912</t>
+  </si>
+  <si>
+    <t>0170</t>
+  </si>
+  <si>
+    <t>1439974</t>
+  </si>
+  <si>
+    <t>100003562</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>1560007</t>
+  </si>
+  <si>
+    <t>頭倉底座組清潔</t>
+  </si>
+  <si>
+    <t>1440639</t>
+  </si>
+  <si>
+    <t>1560008</t>
+  </si>
+  <si>
+    <t>頭倉定位水平校正</t>
+  </si>
+  <si>
+    <t>1440640</t>
+  </si>
+  <si>
+    <t>0240</t>
+  </si>
+  <si>
+    <t>1560009</t>
+  </si>
+  <si>
+    <t>零組件清潔裝配</t>
+  </si>
+  <si>
+    <t>1440641</t>
+  </si>
+  <si>
+    <t>0250</t>
+  </si>
+  <si>
+    <t>1560010</t>
+  </si>
+  <si>
+    <t>馬達座精度磨配</t>
+  </si>
+  <si>
+    <t>1440642</t>
+  </si>
+  <si>
+    <t>0260</t>
+  </si>
+  <si>
+    <t>1560011</t>
+  </si>
+  <si>
+    <t>軸承座精度磨配</t>
+  </si>
+  <si>
+    <t>1440643</t>
+  </si>
+  <si>
+    <t>1560012</t>
+  </si>
+  <si>
+    <t>進給座精度磨配</t>
+  </si>
+  <si>
+    <t>1440644</t>
+  </si>
+  <si>
+    <t>0280</t>
+  </si>
+  <si>
+    <t>1560013</t>
+  </si>
+  <si>
+    <t>頭倉打PIN作業</t>
+  </si>
+  <si>
+    <t>1440645</t>
+  </si>
+  <si>
+    <t>0290</t>
+  </si>
+  <si>
+    <t>1560014</t>
+  </si>
+  <si>
+    <t>角度頭倉機構裝配</t>
+  </si>
+  <si>
+    <t>1440646</t>
+  </si>
+  <si>
+    <t>0300</t>
+  </si>
+  <si>
+    <t>1560015</t>
+  </si>
+  <si>
+    <t>鈑金系統裝配</t>
+  </si>
+  <si>
+    <t>1440647</t>
+  </si>
+  <si>
+    <t>1560016</t>
+  </si>
+  <si>
+    <t>伸縮護蓋裝配</t>
+  </si>
+  <si>
+    <t>1440648</t>
+  </si>
+  <si>
+    <t>0320</t>
+  </si>
+  <si>
+    <t>1560017</t>
+  </si>
+  <si>
+    <t>周邊裝配及防銹</t>
+  </si>
+  <si>
+    <t>1440649</t>
+  </si>
+  <si>
+    <t>100003563</t>
+  </si>
+  <si>
+    <t>0670</t>
+  </si>
+  <si>
+    <t>1442779</t>
+  </si>
+  <si>
+    <t>100003564</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>0010</t>
+  </si>
+  <si>
+    <t>1442594</t>
+  </si>
+  <si>
+    <t>100003568</t>
+  </si>
+  <si>
+    <t>0281</t>
+  </si>
+  <si>
+    <t>1443844</t>
+  </si>
+  <si>
+    <t>100003572</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>0190</t>
-  </si>
-  <si>
-    <t>1390304</t>
-  </si>
-  <si>
-    <t>100003474</t>
-  </si>
-  <si>
-    <t>0170</t>
-  </si>
-  <si>
-    <t>1390405</t>
-  </si>
-  <si>
-    <t>100003475</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>1390493</t>
-  </si>
-  <si>
-    <t>100003481</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>0210</t>
-  </si>
-  <si>
-    <t>1394060</t>
-  </si>
-  <si>
-    <t>0220</t>
-  </si>
-  <si>
-    <t>1394061</t>
-  </si>
-  <si>
-    <t>0230</t>
-  </si>
-  <si>
-    <t>1394062</t>
-  </si>
-  <si>
-    <t>100003482</t>
-  </si>
-  <si>
-    <t>0200</t>
-  </si>
-  <si>
-    <t>1540003</t>
-  </si>
-  <si>
-    <t>旋臂座介面座清潔</t>
-  </si>
-  <si>
-    <t>1394413</t>
-  </si>
-  <si>
-    <t>1394414</t>
-  </si>
-  <si>
-    <t>1394415</t>
-  </si>
-  <si>
-    <t>1394416</t>
-  </si>
-  <si>
-    <t>100003483</t>
-  </si>
-  <si>
-    <t>1394767</t>
-  </si>
-  <si>
-    <t>1394768</t>
-  </si>
-  <si>
-    <t>1394769</t>
-  </si>
-  <si>
-    <t>1394770</t>
-  </si>
-  <si>
-    <t>100003496</t>
-  </si>
-  <si>
-    <t>1403784</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>0340</t>
-  </si>
-  <si>
-    <t>1403788</t>
-  </si>
-  <si>
-    <t>1403794</t>
-  </si>
-  <si>
-    <t>100003504</t>
-  </si>
-  <si>
-    <t>1407414</t>
-  </si>
-  <si>
-    <t>1407415</t>
-  </si>
-  <si>
-    <t>1407416</t>
-  </si>
-  <si>
-    <t>1407417</t>
-  </si>
-  <si>
-    <t>100003507</t>
-  </si>
-  <si>
-    <t>1411454</t>
-  </si>
-  <si>
-    <t>100003508</t>
-  </si>
-  <si>
-    <t>1414691</t>
-  </si>
-  <si>
-    <t>100003509</t>
-  </si>
-  <si>
-    <t>1414896</t>
-  </si>
-  <si>
-    <t>100003510</t>
-  </si>
-  <si>
-    <t>1415194</t>
-  </si>
-  <si>
-    <t>1415195</t>
-  </si>
-  <si>
-    <t>1415196</t>
-  </si>
-  <si>
-    <t>1415197</t>
-  </si>
-  <si>
-    <t>100003515</t>
-  </si>
-  <si>
-    <t>1416109</t>
-  </si>
-  <si>
-    <t>100003521</t>
-  </si>
-  <si>
-    <t>1422599</t>
-  </si>
-  <si>
-    <t>100003522</t>
-  </si>
-  <si>
-    <t>1422700</t>
-  </si>
-  <si>
-    <t>100003523</t>
-  </si>
-  <si>
-    <t>1426157</t>
-  </si>
-  <si>
-    <t>100003524</t>
-  </si>
-  <si>
-    <t>1426254</t>
-  </si>
-  <si>
-    <t>100003525</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>1426821</t>
-  </si>
-  <si>
-    <t>100003526</t>
-  </si>
-  <si>
-    <t>1427454</t>
-  </si>
-  <si>
-    <t>100003527</t>
-  </si>
-  <si>
-    <t>1428430</t>
-  </si>
-  <si>
-    <t>100003534</t>
-  </si>
-  <si>
-    <t>1429824</t>
-  </si>
-  <si>
-    <t>100003535</t>
-  </si>
-  <si>
-    <t>1430037</t>
-  </si>
-  <si>
-    <t>100003536</t>
-  </si>
-  <si>
-    <t>1430250</t>
-  </si>
-  <si>
-    <t>100003537</t>
-  </si>
-  <si>
-    <t>1430463</t>
-  </si>
-  <si>
-    <t>100003538</t>
-  </si>
-  <si>
-    <t>1431484</t>
-  </si>
-  <si>
-    <t>100003539</t>
-  </si>
-  <si>
-    <t>1431584</t>
-  </si>
-  <si>
-    <t>100003540</t>
-  </si>
-  <si>
-    <t>1431684</t>
-  </si>
-  <si>
-    <t>100003541</t>
-  </si>
-  <si>
-    <t>1431777</t>
-  </si>
-  <si>
-    <t>100003542</t>
-  </si>
-  <si>
-    <t>1431916</t>
-  </si>
-  <si>
-    <t>100003543</t>
-  </si>
-  <si>
-    <t>1432135</t>
-  </si>
-  <si>
-    <t>100003544</t>
-  </si>
-  <si>
-    <t>1432354</t>
-  </si>
-  <si>
-    <t>100003545</t>
-  </si>
-  <si>
-    <t>1432573</t>
-  </si>
-  <si>
-    <t>100003546</t>
-  </si>
-  <si>
-    <t>1432792</t>
-  </si>
-  <si>
-    <t>100003547</t>
-  </si>
-  <si>
-    <t>1433011</t>
-  </si>
-  <si>
-    <t>100003548</t>
-  </si>
-  <si>
-    <t>1433230</t>
-  </si>
-  <si>
-    <t>100003553</t>
-  </si>
-  <si>
-    <t>1436359</t>
-  </si>
-  <si>
-    <t>1436360</t>
-  </si>
-  <si>
-    <t>1436361</t>
-  </si>
-  <si>
-    <t>1436362</t>
-  </si>
-  <si>
-    <t>100003554</t>
-  </si>
-  <si>
-    <t>1436473</t>
-  </si>
-  <si>
-    <t>100003555</t>
-  </si>
-  <si>
-    <t>1436573</t>
-  </si>
-  <si>
-    <t>100003556</t>
-  </si>
-  <si>
-    <t>1437074</t>
+    <t>1444654</t>
+  </si>
+  <si>
+    <t>100003573</t>
+  </si>
+  <si>
+    <t>1444858</t>
+  </si>
+  <si>
+    <t>100003574</t>
+  </si>
+  <si>
+    <t>1445062</t>
+  </si>
+  <si>
+    <t>100003578</t>
+  </si>
+  <si>
+    <t>1445878</t>
+  </si>
+  <si>
+    <t>100003579</t>
+  </si>
+  <si>
+    <t>1446082</t>
+  </si>
+  <si>
+    <t>100003580</t>
+  </si>
+  <si>
+    <t>1446286</t>
+  </si>
+  <si>
+    <t>100003585</t>
+  </si>
+  <si>
+    <t>1449017</t>
+  </si>
+  <si>
+    <t>100003587</t>
+  </si>
+  <si>
+    <t>1453060</t>
+  </si>
+  <si>
+    <t>100003590</t>
+  </si>
+  <si>
+    <t>1453659</t>
+  </si>
+  <si>
+    <t>100003593</t>
+  </si>
+  <si>
+    <t>1453959</t>
+  </si>
+  <si>
+    <t>100003595</t>
+  </si>
+  <si>
+    <t>1457817</t>
+  </si>
+  <si>
+    <t>100003596</t>
+  </si>
+  <si>
+    <t>1457917</t>
+  </si>
+  <si>
+    <t>100003597</t>
+  </si>
+  <si>
+    <t>1458017</t>
+  </si>
+  <si>
+    <t>100003598</t>
+  </si>
+  <si>
+    <t>1458117</t>
+  </si>
+  <si>
+    <t>100003599</t>
+  </si>
+  <si>
+    <t>1458217</t>
+  </si>
+  <si>
+    <t>100003600</t>
+  </si>
+  <si>
+    <t>1458348</t>
+  </si>
+  <si>
+    <t>100003601</t>
+  </si>
+  <si>
+    <t>1458428</t>
+  </si>
+  <si>
+    <t>100003602</t>
+  </si>
+  <si>
+    <t>1458741</t>
+  </si>
+  <si>
+    <t>100003603</t>
+  </si>
+  <si>
+    <t>1458945</t>
+  </si>
+  <si>
+    <t>100003604</t>
+  </si>
+  <si>
+    <t>1459035</t>
+  </si>
+  <si>
+    <t>100003606</t>
+  </si>
+  <si>
+    <t>1460616</t>
+  </si>
+  <si>
+    <t>100003607</t>
+  </si>
+  <si>
+    <t>1461381</t>
+  </si>
+  <si>
+    <t>100003608</t>
+  </si>
+  <si>
+    <t>1461469</t>
+  </si>
+  <si>
+    <t>100003609</t>
+  </si>
+  <si>
+    <t>1461569</t>
+  </si>
+  <si>
+    <t>100003610</t>
+  </si>
+  <si>
+    <t>1461670</t>
+  </si>
+  <si>
+    <t>100003612</t>
+  </si>
+  <si>
+    <t>1463036</t>
+  </si>
+  <si>
+    <t>100003614</t>
+  </si>
+  <si>
+    <t>1463491</t>
+  </si>
+  <si>
+    <t>100003616</t>
+  </si>
+  <si>
+    <t>1465072</t>
+  </si>
+  <si>
+    <t>100003617</t>
+  </si>
+  <si>
+    <t>1466583</t>
+  </si>
+  <si>
+    <t>100003618</t>
+  </si>
+  <si>
+    <t>1466683</t>
+  </si>
+  <si>
+    <t>100003619</t>
+  </si>
+  <si>
+    <t>1466783</t>
+  </si>
+  <si>
+    <t>100003621</t>
+  </si>
+  <si>
+    <t>1469385</t>
   </si>
   <si>
     <t>訂單</t>
@@ -676,7 +820,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AH67"/>
+  <dimension ref="A1:AH72"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="11" customWidth="1"/>
@@ -717,106 +861,106 @@
   <sheetData>
     <row r="1" spans="1:34">
       <c r="A1" s="1" t="s">
-        <v>150</v>
+        <v>198</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>151</v>
+        <v>199</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>152</v>
+        <v>200</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>153</v>
+        <v>201</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>154</v>
+        <v>202</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>155</v>
+        <v>203</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>156</v>
+        <v>204</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>157</v>
+        <v>205</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>158</v>
+        <v>206</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>159</v>
+        <v>207</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>160</v>
+        <v>208</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>161</v>
+        <v>209</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>162</v>
+        <v>210</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>163</v>
+        <v>211</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>164</v>
+        <v>212</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>165</v>
+        <v>213</v>
       </c>
       <c r="Q1" s="6" t="s">
-        <v>166</v>
+        <v>214</v>
       </c>
       <c r="R1" s="6" t="s">
-        <v>167</v>
+        <v>215</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>168</v>
+        <v>216</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>169</v>
+        <v>217</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>170</v>
+        <v>218</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>171</v>
+        <v>219</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>172</v>
+        <v>220</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>173</v>
+        <v>221</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>174</v>
+        <v>222</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>175</v>
+        <v>223</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>176</v>
+        <v>224</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>177</v>
+        <v>225</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>178</v>
+        <v>226</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>179</v>
+        <v>227</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>180</v>
+        <v>228</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>181</v>
+        <v>229</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>182</v>
+        <v>230</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>183</v>
+        <v>231</v>
       </c>
     </row>
     <row r="2" spans="1:34">
@@ -1127,7 +1271,7 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
         <v>3</v>
@@ -1136,10 +1280,10 @@
         <v>4</v>
       </c>
       <c r="F5" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G5" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H5" s="2">
         <v>1</v>
@@ -1148,13 +1292,13 @@
         <v>7</v>
       </c>
       <c r="J5" s="3">
-        <v>3.0</v>
+        <v>1.5</v>
       </c>
       <c r="K5" s="3">
-        <v>3.0</v>
+        <v>1.5</v>
       </c>
       <c r="L5" s="3">
-        <v>3.0</v>
+        <v>1.5</v>
       </c>
       <c r="M5" t="s">
         <v>8</v>
@@ -1175,7 +1319,7 @@
         <v>0.000</v>
       </c>
       <c r="S5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="T5" s="5"/>
       <c r="U5" s="5"/>
@@ -1221,13 +1365,13 @@
     </row>
     <row r="6" spans="1:34">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s">
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
         <v>3</v>
@@ -1236,10 +1380,10 @@
         <v>4</v>
       </c>
       <c r="F6" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G6" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="H6" s="2">
         <v>1</v>
@@ -1248,13 +1392,13 @@
         <v>7</v>
       </c>
       <c r="J6" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="K6" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="L6" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="M6" t="s">
         <v>8</v>
@@ -1275,7 +1419,7 @@
         <v>0.000</v>
       </c>
       <c r="S6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="T6" s="5"/>
       <c r="U6" s="5"/>
@@ -1321,13 +1465,13 @@
     </row>
     <row r="7" spans="1:34">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B7" t="s">
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="D7" t="s">
         <v>3</v>
@@ -1336,10 +1480,10 @@
         <v>4</v>
       </c>
       <c r="F7" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="G7" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="H7" s="2">
         <v>1</v>
@@ -1348,13 +1492,13 @@
         <v>7</v>
       </c>
       <c r="J7" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="K7" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="L7" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="M7" t="s">
         <v>8</v>
@@ -1375,7 +1519,7 @@
         <v>0.000</v>
       </c>
       <c r="S7" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="T7" s="5"/>
       <c r="U7" s="5"/>
@@ -1421,7 +1565,7 @@
     </row>
     <row r="8" spans="1:34">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
         <v>17</v>
@@ -1475,7 +1619,7 @@
         <v>0.000</v>
       </c>
       <c r="S8" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="T8" s="5"/>
       <c r="U8" s="5"/>
@@ -1521,13 +1665,13 @@
     </row>
     <row r="9" spans="1:34">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
         <v>3</v>
@@ -1575,7 +1719,7 @@
         <v>0.000</v>
       </c>
       <c r="S9" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="T9" s="5"/>
       <c r="U9" s="5"/>
@@ -1621,13 +1765,13 @@
     </row>
     <row r="10" spans="1:34">
       <c r="A10" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="D10" t="s">
         <v>3</v>
@@ -1675,7 +1819,7 @@
         <v>0.000</v>
       </c>
       <c r="S10" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="T10" s="5"/>
       <c r="U10" s="5"/>
@@ -1721,13 +1865,13 @@
     </row>
     <row r="11" spans="1:34">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s">
         <v>3</v>
@@ -1775,7 +1919,7 @@
         <v>0.000</v>
       </c>
       <c r="S11" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="T11" s="5"/>
       <c r="U11" s="5"/>
@@ -1821,13 +1965,13 @@
     </row>
     <row r="12" spans="1:34">
       <c r="A12" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B12" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D12" t="s">
         <v>3</v>
@@ -1875,7 +2019,7 @@
         <v>0.000</v>
       </c>
       <c r="S12" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="T12" s="5"/>
       <c r="U12" s="5"/>
@@ -1921,13 +2065,13 @@
     </row>
     <row r="13" spans="1:34">
       <c r="A13" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D13" t="s">
         <v>3</v>
@@ -1936,10 +2080,10 @@
         <v>4</v>
       </c>
       <c r="F13" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G13" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H13" s="2">
         <v>1</v>
@@ -1948,13 +2092,13 @@
         <v>7</v>
       </c>
       <c r="J13" s="3">
-        <v>3.0</v>
+        <v>1.5</v>
       </c>
       <c r="K13" s="3">
-        <v>3.0</v>
+        <v>1.5</v>
       </c>
       <c r="L13" s="3">
-        <v>3.0</v>
+        <v>1.5</v>
       </c>
       <c r="M13" t="s">
         <v>8</v>
@@ -1975,7 +2119,7 @@
         <v>0.000</v>
       </c>
       <c r="S13" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="T13" s="5"/>
       <c r="U13" s="5"/>
@@ -2021,13 +2165,13 @@
     </row>
     <row r="14" spans="1:34">
       <c r="A14" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B14" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="D14" t="s">
         <v>3</v>
@@ -2036,10 +2180,10 @@
         <v>4</v>
       </c>
       <c r="F14" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G14" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="H14" s="2">
         <v>1</v>
@@ -2048,13 +2192,13 @@
         <v>7</v>
       </c>
       <c r="J14" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="K14" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="L14" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="M14" t="s">
         <v>8</v>
@@ -2075,7 +2219,7 @@
         <v>0.000</v>
       </c>
       <c r="S14" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="T14" s="5"/>
       <c r="U14" s="5"/>
@@ -2121,13 +2265,13 @@
     </row>
     <row r="15" spans="1:34">
       <c r="A15" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B15" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="D15" t="s">
         <v>3</v>
@@ -2136,10 +2280,10 @@
         <v>4</v>
       </c>
       <c r="F15" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="G15" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="H15" s="2">
         <v>1</v>
@@ -2148,13 +2292,13 @@
         <v>7</v>
       </c>
       <c r="J15" s="3">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="K15" s="3">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="L15" s="3">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="M15" t="s">
         <v>8</v>
@@ -2175,7 +2319,7 @@
         <v>0.000</v>
       </c>
       <c r="S15" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="T15" s="5"/>
       <c r="U15" s="5"/>
@@ -2221,13 +2365,13 @@
     </row>
     <row r="16" spans="1:34">
       <c r="A16" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="D16" t="s">
         <v>3</v>
@@ -2236,10 +2380,10 @@
         <v>4</v>
       </c>
       <c r="F16" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="G16" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H16" s="2">
         <v>1</v>
@@ -2248,13 +2392,13 @@
         <v>7</v>
       </c>
       <c r="J16" s="3">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="K16" s="3">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="L16" s="3">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="M16" t="s">
         <v>8</v>
@@ -2275,7 +2419,7 @@
         <v>0.000</v>
       </c>
       <c r="S16" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="T16" s="5"/>
       <c r="U16" s="5"/>
@@ -2321,13 +2465,13 @@
     </row>
     <row r="17" spans="1:34">
       <c r="A17" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="B17" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D17" t="s">
         <v>3</v>
@@ -2336,10 +2480,10 @@
         <v>4</v>
       </c>
       <c r="F17" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="G17" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="H17" s="2">
         <v>1</v>
@@ -2348,13 +2492,13 @@
         <v>7</v>
       </c>
       <c r="J17" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="K17" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="L17" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="M17" t="s">
         <v>8</v>
@@ -2375,7 +2519,7 @@
         <v>0.000</v>
       </c>
       <c r="S17" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="T17" s="5"/>
       <c r="U17" s="5"/>
@@ -2421,13 +2565,13 @@
     </row>
     <row r="18" spans="1:34">
       <c r="A18" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="B18" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C18" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D18" t="s">
         <v>3</v>
@@ -2436,10 +2580,10 @@
         <v>4</v>
       </c>
       <c r="F18" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="G18" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="H18" s="2">
         <v>1</v>
@@ -2475,7 +2619,7 @@
         <v>0.000</v>
       </c>
       <c r="S18" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="T18" s="5"/>
       <c r="U18" s="5"/>
@@ -2521,13 +2665,13 @@
     </row>
     <row r="19" spans="1:34">
       <c r="A19" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B19" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C19" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="D19" t="s">
         <v>3</v>
@@ -2536,10 +2680,10 @@
         <v>4</v>
       </c>
       <c r="F19" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="G19" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="H19" s="2">
         <v>1</v>
@@ -2548,13 +2692,13 @@
         <v>7</v>
       </c>
       <c r="J19" s="3">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="K19" s="3">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="L19" s="3">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="M19" t="s">
         <v>8</v>
@@ -2575,7 +2719,7 @@
         <v>0.000</v>
       </c>
       <c r="S19" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="T19" s="5"/>
       <c r="U19" s="5"/>
@@ -2621,13 +2765,13 @@
     </row>
     <row r="20" spans="1:34">
       <c r="A20" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B20" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C20" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D20" t="s">
         <v>3</v>
@@ -2636,10 +2780,10 @@
         <v>4</v>
       </c>
       <c r="F20" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="G20" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H20" s="2">
         <v>1</v>
@@ -2648,13 +2792,13 @@
         <v>7</v>
       </c>
       <c r="J20" s="3">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="K20" s="3">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="L20" s="3">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="M20" t="s">
         <v>8</v>
@@ -2675,7 +2819,7 @@
         <v>0.000</v>
       </c>
       <c r="S20" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="T20" s="5"/>
       <c r="U20" s="5"/>
@@ -2721,13 +2865,13 @@
     </row>
     <row r="21" spans="1:34">
       <c r="A21" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B21" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C21" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D21" t="s">
         <v>3</v>
@@ -2736,10 +2880,10 @@
         <v>4</v>
       </c>
       <c r="F21" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="G21" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="H21" s="2">
         <v>1</v>
@@ -2748,13 +2892,13 @@
         <v>7</v>
       </c>
       <c r="J21" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="K21" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="L21" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="M21" t="s">
         <v>8</v>
@@ -2775,7 +2919,7 @@
         <v>0.000</v>
       </c>
       <c r="S21" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="T21" s="5"/>
       <c r="U21" s="5"/>
@@ -2821,13 +2965,13 @@
     </row>
     <row r="22" spans="1:34">
       <c r="A22" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B22" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C22" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="D22" t="s">
         <v>3</v>
@@ -2836,10 +2980,10 @@
         <v>4</v>
       </c>
       <c r="F22" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="G22" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="H22" s="2">
         <v>1</v>
@@ -2875,7 +3019,7 @@
         <v>0.000</v>
       </c>
       <c r="S22" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="T22" s="5"/>
       <c r="U22" s="5"/>
@@ -2921,13 +3065,13 @@
     </row>
     <row r="23" spans="1:34">
       <c r="A23" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B23" t="s">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D23" t="s">
         <v>3</v>
@@ -2936,10 +3080,10 @@
         <v>4</v>
       </c>
       <c r="F23" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="G23" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="H23" s="2">
         <v>1</v>
@@ -2975,7 +3119,7 @@
         <v>0.000</v>
       </c>
       <c r="S23" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="T23" s="5"/>
       <c r="U23" s="5"/>
@@ -3021,13 +3165,13 @@
     </row>
     <row r="24" spans="1:34">
       <c r="A24" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B24" t="s">
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>2</v>
+        <v>71</v>
       </c>
       <c r="D24" t="s">
         <v>3</v>
@@ -3036,10 +3180,10 @@
         <v>4</v>
       </c>
       <c r="F24" t="s">
-        <v>5</v>
+        <v>72</v>
       </c>
       <c r="G24" t="s">
-        <v>6</v>
+        <v>73</v>
       </c>
       <c r="H24" s="2">
         <v>1</v>
@@ -3075,7 +3219,7 @@
         <v>0.000</v>
       </c>
       <c r="S24" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="T24" s="5"/>
       <c r="U24" s="5"/>
@@ -3121,13 +3265,13 @@
     </row>
     <row r="25" spans="1:34">
       <c r="A25" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B25" t="s">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D25" t="s">
         <v>3</v>
@@ -3136,10 +3280,10 @@
         <v>4</v>
       </c>
       <c r="F25" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="G25" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="H25" s="2">
         <v>1</v>
@@ -3148,13 +3292,13 @@
         <v>7</v>
       </c>
       <c r="J25" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="K25" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="L25" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="M25" t="s">
         <v>8</v>
@@ -3175,7 +3319,7 @@
         <v>0.000</v>
       </c>
       <c r="S25" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="T25" s="5"/>
       <c r="U25" s="5"/>
@@ -3221,13 +3365,13 @@
     </row>
     <row r="26" spans="1:34">
       <c r="A26" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B26" t="s">
         <v>11</v>
       </c>
       <c r="C26" t="s">
-        <v>12</v>
+        <v>79</v>
       </c>
       <c r="D26" t="s">
         <v>3</v>
@@ -3236,10 +3380,10 @@
         <v>4</v>
       </c>
       <c r="F26" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G26" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H26" s="2">
         <v>1</v>
@@ -3248,13 +3392,13 @@
         <v>7</v>
       </c>
       <c r="J26" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="K26" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="L26" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="M26" t="s">
         <v>8</v>
@@ -3275,7 +3419,7 @@
         <v>0.000</v>
       </c>
       <c r="S26" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="T26" s="5"/>
       <c r="U26" s="5"/>
@@ -3321,13 +3465,13 @@
     </row>
     <row r="27" spans="1:34">
       <c r="A27" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B27" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="C27" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D27" t="s">
         <v>3</v>
@@ -3336,10 +3480,10 @@
         <v>4</v>
       </c>
       <c r="F27" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="G27" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="H27" s="2">
         <v>1</v>
@@ -3348,13 +3492,13 @@
         <v>7</v>
       </c>
       <c r="J27" s="3">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="K27" s="3">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="L27" s="3">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="M27" t="s">
         <v>8</v>
@@ -3375,7 +3519,7 @@
         <v>0.000</v>
       </c>
       <c r="S27" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="T27" s="5"/>
       <c r="U27" s="5"/>
@@ -3421,13 +3565,13 @@
     </row>
     <row r="28" spans="1:34">
       <c r="A28" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B28" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="C28" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="D28" t="s">
         <v>3</v>
@@ -3436,10 +3580,10 @@
         <v>4</v>
       </c>
       <c r="F28" t="s">
-        <v>24</v>
+        <v>86</v>
       </c>
       <c r="G28" t="s">
-        <v>25</v>
+        <v>87</v>
       </c>
       <c r="H28" s="2">
         <v>1</v>
@@ -3448,13 +3592,13 @@
         <v>7</v>
       </c>
       <c r="J28" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="K28" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="L28" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="M28" t="s">
         <v>8</v>
@@ -3475,7 +3619,7 @@
         <v>0.000</v>
       </c>
       <c r="S28" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="T28" s="5"/>
       <c r="U28" s="5"/>
@@ -3521,13 +3665,13 @@
     </row>
     <row r="29" spans="1:34">
       <c r="A29" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B29" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="C29" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="D29" t="s">
         <v>3</v>
@@ -3536,10 +3680,10 @@
         <v>4</v>
       </c>
       <c r="F29" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="G29" t="s">
-        <v>29</v>
+        <v>91</v>
       </c>
       <c r="H29" s="2">
         <v>1</v>
@@ -3575,7 +3719,7 @@
         <v>0.000</v>
       </c>
       <c r="S29" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="T29" s="5"/>
       <c r="U29" s="5"/>
@@ -3621,13 +3765,13 @@
     </row>
     <row r="30" spans="1:34">
       <c r="A30" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B30" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="C30" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="D30" t="s">
         <v>3</v>
@@ -3636,10 +3780,10 @@
         <v>4</v>
       </c>
       <c r="F30" t="s">
-        <v>32</v>
+        <v>94</v>
       </c>
       <c r="G30" t="s">
-        <v>33</v>
+        <v>95</v>
       </c>
       <c r="H30" s="2">
         <v>1</v>
@@ -3675,7 +3819,7 @@
         <v>0.000</v>
       </c>
       <c r="S30" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="T30" s="5"/>
       <c r="U30" s="5"/>
@@ -3724,10 +3868,10 @@
         <v>81</v>
       </c>
       <c r="B31" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="C31" t="s">
-        <v>18</v>
+        <v>97</v>
       </c>
       <c r="D31" t="s">
         <v>3</v>
@@ -3736,10 +3880,10 @@
         <v>4</v>
       </c>
       <c r="F31" t="s">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="G31" t="s">
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="H31" s="2">
         <v>1</v>
@@ -3748,13 +3892,13 @@
         <v>7</v>
       </c>
       <c r="J31" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="K31" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="L31" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="M31" t="s">
         <v>8</v>
@@ -3775,7 +3919,7 @@
         <v>0.000</v>
       </c>
       <c r="S31" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="T31" s="5"/>
       <c r="U31" s="5"/>
@@ -3821,13 +3965,13 @@
     </row>
     <row r="32" spans="1:34">
       <c r="A32" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B32" t="s">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c r="C32" t="s">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="D32" t="s">
         <v>3</v>
@@ -3836,10 +3980,10 @@
         <v>4</v>
       </c>
       <c r="F32" t="s">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="G32" t="s">
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="H32" s="2">
         <v>1</v>
@@ -3848,13 +3992,13 @@
         <v>7</v>
       </c>
       <c r="J32" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="K32" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="L32" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="M32" t="s">
         <v>8</v>
@@ -3875,7 +4019,7 @@
         <v>0.000</v>
       </c>
       <c r="S32" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="T32" s="5"/>
       <c r="U32" s="5"/>
@@ -3921,13 +4065,13 @@
     </row>
     <row r="33" spans="1:34">
       <c r="A33" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B33" t="s">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c r="C33" t="s">
-        <v>18</v>
+        <v>104</v>
       </c>
       <c r="D33" t="s">
         <v>3</v>
@@ -3936,10 +4080,10 @@
         <v>4</v>
       </c>
       <c r="F33" t="s">
-        <v>19</v>
+        <v>105</v>
       </c>
       <c r="G33" t="s">
-        <v>20</v>
+        <v>106</v>
       </c>
       <c r="H33" s="2">
         <v>1</v>
@@ -3948,13 +4092,13 @@
         <v>7</v>
       </c>
       <c r="J33" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="K33" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="L33" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="M33" t="s">
         <v>8</v>
@@ -3975,7 +4119,7 @@
         <v>0.000</v>
       </c>
       <c r="S33" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="T33" s="5"/>
       <c r="U33" s="5"/>
@@ -4021,13 +4165,13 @@
     </row>
     <row r="34" spans="1:34">
       <c r="A34" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B34" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="C34" t="s">
-        <v>58</v>
+        <v>108</v>
       </c>
       <c r="D34" t="s">
         <v>3</v>
@@ -4036,10 +4180,10 @@
         <v>4</v>
       </c>
       <c r="F34" t="s">
-        <v>59</v>
+        <v>109</v>
       </c>
       <c r="G34" t="s">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="H34" s="2">
         <v>1</v>
@@ -4048,13 +4192,13 @@
         <v>7</v>
       </c>
       <c r="J34" s="3">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="K34" s="3">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="L34" s="3">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="M34" t="s">
         <v>8</v>
@@ -4075,7 +4219,7 @@
         <v>0.000</v>
       </c>
       <c r="S34" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="T34" s="5"/>
       <c r="U34" s="5"/>
@@ -4121,13 +4265,13 @@
     </row>
     <row r="35" spans="1:34">
       <c r="A35" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B35" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="C35" t="s">
-        <v>51</v>
+        <v>112</v>
       </c>
       <c r="D35" t="s">
         <v>3</v>
@@ -4136,10 +4280,10 @@
         <v>4</v>
       </c>
       <c r="F35" t="s">
-        <v>24</v>
+        <v>113</v>
       </c>
       <c r="G35" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="H35" s="2">
         <v>1</v>
@@ -4148,13 +4292,13 @@
         <v>7</v>
       </c>
       <c r="J35" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="K35" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="L35" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="M35" t="s">
         <v>8</v>
@@ -4175,7 +4319,7 @@
         <v>0.000</v>
       </c>
       <c r="S35" t="s">
-        <v>89</v>
+        <v>115</v>
       </c>
       <c r="T35" s="5"/>
       <c r="U35" s="5"/>
@@ -4221,13 +4365,13 @@
     </row>
     <row r="36" spans="1:34">
       <c r="A36" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B36" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="C36" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="D36" t="s">
         <v>3</v>
@@ -4236,10 +4380,10 @@
         <v>4</v>
       </c>
       <c r="F36" t="s">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="G36" t="s">
-        <v>29</v>
+        <v>117</v>
       </c>
       <c r="H36" s="2">
         <v>1</v>
@@ -4275,7 +4419,7 @@
         <v>0.000</v>
       </c>
       <c r="S36" t="s">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="T36" s="5"/>
       <c r="U36" s="5"/>
@@ -4321,13 +4465,13 @@
     </row>
     <row r="37" spans="1:34">
       <c r="A37" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B37" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="C37" t="s">
-        <v>55</v>
+        <v>119</v>
       </c>
       <c r="D37" t="s">
         <v>3</v>
@@ -4336,10 +4480,10 @@
         <v>4</v>
       </c>
       <c r="F37" t="s">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="G37" t="s">
-        <v>33</v>
+        <v>121</v>
       </c>
       <c r="H37" s="2">
         <v>1</v>
@@ -4348,13 +4492,13 @@
         <v>7</v>
       </c>
       <c r="J37" s="3">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="K37" s="3">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="L37" s="3">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="M37" t="s">
         <v>8</v>
@@ -4375,7 +4519,7 @@
         <v>0.000</v>
       </c>
       <c r="S37" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="T37" s="5"/>
       <c r="U37" s="5"/>
@@ -4421,13 +4565,13 @@
     </row>
     <row r="38" spans="1:34">
       <c r="A38" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="B38" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>18</v>
+        <v>124</v>
       </c>
       <c r="D38" t="s">
         <v>3</v>
@@ -4436,10 +4580,10 @@
         <v>4</v>
       </c>
       <c r="F38" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="G38" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="H38" s="2">
         <v>1</v>
@@ -4448,13 +4592,13 @@
         <v>7</v>
       </c>
       <c r="J38" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="K38" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="L38" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="M38" t="s">
         <v>8</v>
@@ -4475,7 +4619,7 @@
         <v>0.000</v>
       </c>
       <c r="S38" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="T38" s="5"/>
       <c r="U38" s="5"/>
@@ -4521,13 +4665,13 @@
     </row>
     <row r="39" spans="1:34">
       <c r="A39" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="B39" t="s">
-        <v>40</v>
+        <v>127</v>
       </c>
       <c r="C39" t="s">
-        <v>44</v>
+        <v>128</v>
       </c>
       <c r="D39" t="s">
         <v>3</v>
@@ -4575,7 +4719,7 @@
         <v>0.000</v>
       </c>
       <c r="S39" t="s">
-        <v>95</v>
+        <v>129</v>
       </c>
       <c r="T39" s="5"/>
       <c r="U39" s="5"/>
@@ -4621,13 +4765,13 @@
     </row>
     <row r="40" spans="1:34">
       <c r="A40" t="s">
-        <v>96</v>
+        <v>130</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>44</v>
+        <v>131</v>
       </c>
       <c r="D40" t="s">
         <v>3</v>
@@ -4675,7 +4819,7 @@
         <v>0.000</v>
       </c>
       <c r="S40" t="s">
-        <v>97</v>
+        <v>132</v>
       </c>
       <c r="T40" s="5"/>
       <c r="U40" s="5"/>
@@ -4721,13 +4865,13 @@
     </row>
     <row r="41" spans="1:34">
       <c r="A41" t="s">
-        <v>98</v>
+        <v>133</v>
       </c>
       <c r="B41" t="s">
-        <v>40</v>
+        <v>134</v>
       </c>
       <c r="C41" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D41" t="s">
         <v>3</v>
@@ -4775,7 +4919,7 @@
         <v>0.000</v>
       </c>
       <c r="S41" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="T41" s="5"/>
       <c r="U41" s="5"/>
@@ -4821,13 +4965,13 @@
     </row>
     <row r="42" spans="1:34">
       <c r="A42" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="B42" t="s">
-        <v>40</v>
+        <v>134</v>
       </c>
       <c r="C42" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D42" t="s">
         <v>3</v>
@@ -4875,7 +5019,7 @@
         <v>0.000</v>
       </c>
       <c r="S42" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="T42" s="5"/>
       <c r="U42" s="5"/>
@@ -4921,13 +5065,13 @@
     </row>
     <row r="43" spans="1:34">
       <c r="A43" t="s">
-        <v>102</v>
+        <v>138</v>
       </c>
       <c r="B43" t="s">
-        <v>103</v>
+        <v>134</v>
       </c>
       <c r="C43" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D43" t="s">
         <v>3</v>
@@ -4975,7 +5119,7 @@
         <v>0.000</v>
       </c>
       <c r="S43" t="s">
-        <v>104</v>
+        <v>139</v>
       </c>
       <c r="T43" s="5"/>
       <c r="U43" s="5"/>
@@ -5021,13 +5165,13 @@
     </row>
     <row r="44" spans="1:34">
       <c r="A44" t="s">
-        <v>105</v>
+        <v>140</v>
       </c>
       <c r="B44" t="s">
-        <v>103</v>
+        <v>134</v>
       </c>
       <c r="C44" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D44" t="s">
         <v>3</v>
@@ -5075,7 +5219,7 @@
         <v>0.000</v>
       </c>
       <c r="S44" t="s">
-        <v>106</v>
+        <v>141</v>
       </c>
       <c r="T44" s="5"/>
       <c r="U44" s="5"/>
@@ -5121,13 +5265,13 @@
     </row>
     <row r="45" spans="1:34">
       <c r="A45" t="s">
-        <v>107</v>
+        <v>142</v>
       </c>
       <c r="B45" t="s">
-        <v>40</v>
+        <v>134</v>
       </c>
       <c r="C45" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D45" t="s">
         <v>3</v>
@@ -5175,7 +5319,7 @@
         <v>0.000</v>
       </c>
       <c r="S45" t="s">
-        <v>108</v>
+        <v>143</v>
       </c>
       <c r="T45" s="5"/>
       <c r="U45" s="5"/>
@@ -5221,13 +5365,13 @@
     </row>
     <row r="46" spans="1:34">
       <c r="A46" t="s">
-        <v>109</v>
+        <v>144</v>
       </c>
       <c r="B46" t="s">
-        <v>17</v>
+        <v>134</v>
       </c>
       <c r="C46" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="D46" t="s">
         <v>3</v>
@@ -5275,7 +5419,7 @@
         <v>0.000</v>
       </c>
       <c r="S46" t="s">
-        <v>110</v>
+        <v>145</v>
       </c>
       <c r="T46" s="5"/>
       <c r="U46" s="5"/>
@@ -5321,7 +5465,7 @@
     </row>
     <row r="47" spans="1:34">
       <c r="A47" t="s">
-        <v>111</v>
+        <v>146</v>
       </c>
       <c r="B47" t="s">
         <v>17</v>
@@ -5375,7 +5519,7 @@
         <v>0.000</v>
       </c>
       <c r="S47" t="s">
-        <v>112</v>
+        <v>147</v>
       </c>
       <c r="T47" s="5"/>
       <c r="U47" s="5"/>
@@ -5421,13 +5565,13 @@
     </row>
     <row r="48" spans="1:34">
       <c r="A48" t="s">
-        <v>113</v>
+        <v>148</v>
       </c>
       <c r="B48" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="C48" t="s">
-        <v>18</v>
+        <v>79</v>
       </c>
       <c r="D48" t="s">
         <v>3</v>
@@ -5475,7 +5619,7 @@
         <v>0.000</v>
       </c>
       <c r="S48" t="s">
-        <v>114</v>
+        <v>149</v>
       </c>
       <c r="T48" s="5"/>
       <c r="U48" s="5"/>
@@ -5521,13 +5665,13 @@
     </row>
     <row r="49" spans="1:34">
       <c r="A49" t="s">
-        <v>115</v>
+        <v>150</v>
       </c>
       <c r="B49" t="s">
-        <v>17</v>
+        <v>134</v>
       </c>
       <c r="C49" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="D49" t="s">
         <v>3</v>
@@ -5575,7 +5719,7 @@
         <v>0.000</v>
       </c>
       <c r="S49" t="s">
-        <v>116</v>
+        <v>151</v>
       </c>
       <c r="T49" s="5"/>
       <c r="U49" s="5"/>
@@ -5621,13 +5765,13 @@
     </row>
     <row r="50" spans="1:34">
       <c r="A50" t="s">
-        <v>117</v>
+        <v>152</v>
       </c>
       <c r="B50" t="s">
-        <v>40</v>
+        <v>134</v>
       </c>
       <c r="C50" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="D50" t="s">
         <v>3</v>
@@ -5675,7 +5819,7 @@
         <v>0.000</v>
       </c>
       <c r="S50" t="s">
-        <v>118</v>
+        <v>153</v>
       </c>
       <c r="T50" s="5"/>
       <c r="U50" s="5"/>
@@ -5721,13 +5865,13 @@
     </row>
     <row r="51" spans="1:34">
       <c r="A51" t="s">
-        <v>119</v>
+        <v>154</v>
       </c>
       <c r="B51" t="s">
-        <v>40</v>
+        <v>134</v>
       </c>
       <c r="C51" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D51" t="s">
         <v>3</v>
@@ -5775,7 +5919,7 @@
         <v>0.000</v>
       </c>
       <c r="S51" t="s">
-        <v>120</v>
+        <v>155</v>
       </c>
       <c r="T51" s="5"/>
       <c r="U51" s="5"/>
@@ -5821,13 +5965,13 @@
     </row>
     <row r="52" spans="1:34">
       <c r="A52" t="s">
-        <v>121</v>
+        <v>156</v>
       </c>
       <c r="B52" t="s">
-        <v>40</v>
+        <v>134</v>
       </c>
       <c r="C52" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D52" t="s">
         <v>3</v>
@@ -5875,7 +6019,7 @@
         <v>0.000</v>
       </c>
       <c r="S52" t="s">
-        <v>122</v>
+        <v>157</v>
       </c>
       <c r="T52" s="5"/>
       <c r="U52" s="5"/>
@@ -5921,13 +6065,13 @@
     </row>
     <row r="53" spans="1:34">
       <c r="A53" t="s">
-        <v>123</v>
+        <v>158</v>
       </c>
       <c r="B53" t="s">
-        <v>40</v>
+        <v>134</v>
       </c>
       <c r="C53" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D53" t="s">
         <v>3</v>
@@ -5975,7 +6119,7 @@
         <v>0.000</v>
       </c>
       <c r="S53" t="s">
-        <v>124</v>
+        <v>159</v>
       </c>
       <c r="T53" s="5"/>
       <c r="U53" s="5"/>
@@ -6021,13 +6165,13 @@
     </row>
     <row r="54" spans="1:34">
       <c r="A54" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="B54" t="s">
-        <v>17</v>
+        <v>134</v>
       </c>
       <c r="C54" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="D54" t="s">
         <v>3</v>
@@ -6075,7 +6219,7 @@
         <v>0.000</v>
       </c>
       <c r="S54" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="T54" s="5"/>
       <c r="U54" s="5"/>
@@ -6121,13 +6265,13 @@
     </row>
     <row r="55" spans="1:34">
       <c r="A55" t="s">
-        <v>127</v>
+        <v>162</v>
       </c>
       <c r="B55" t="s">
-        <v>17</v>
+        <v>134</v>
       </c>
       <c r="C55" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="D55" t="s">
         <v>3</v>
@@ -6175,7 +6319,7 @@
         <v>0.000</v>
       </c>
       <c r="S55" t="s">
-        <v>128</v>
+        <v>163</v>
       </c>
       <c r="T55" s="5"/>
       <c r="U55" s="5"/>
@@ -6221,13 +6365,13 @@
     </row>
     <row r="56" spans="1:34">
       <c r="A56" t="s">
-        <v>129</v>
+        <v>164</v>
       </c>
       <c r="B56" t="s">
         <v>17</v>
       </c>
       <c r="C56" t="s">
-        <v>58</v>
+        <v>112</v>
       </c>
       <c r="D56" t="s">
         <v>3</v>
@@ -6275,7 +6419,7 @@
         <v>0.000</v>
       </c>
       <c r="S56" t="s">
-        <v>130</v>
+        <v>165</v>
       </c>
       <c r="T56" s="5"/>
       <c r="U56" s="5"/>
@@ -6321,13 +6465,13 @@
     </row>
     <row r="57" spans="1:34">
       <c r="A57" t="s">
-        <v>131</v>
+        <v>166</v>
       </c>
       <c r="B57" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="C57" t="s">
-        <v>58</v>
+        <v>128</v>
       </c>
       <c r="D57" t="s">
         <v>3</v>
@@ -6375,7 +6519,7 @@
         <v>0.000</v>
       </c>
       <c r="S57" t="s">
-        <v>132</v>
+        <v>167</v>
       </c>
       <c r="T57" s="5"/>
       <c r="U57" s="5"/>
@@ -6421,13 +6565,13 @@
     </row>
     <row r="58" spans="1:34">
       <c r="A58" t="s">
-        <v>133</v>
+        <v>168</v>
       </c>
       <c r="B58" t="s">
-        <v>17</v>
+        <v>134</v>
       </c>
       <c r="C58" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="D58" t="s">
         <v>3</v>
@@ -6475,7 +6619,7 @@
         <v>0.000</v>
       </c>
       <c r="S58" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="T58" s="5"/>
       <c r="U58" s="5"/>
@@ -6521,13 +6665,13 @@
     </row>
     <row r="59" spans="1:34">
       <c r="A59" t="s">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="B59" t="s">
-        <v>17</v>
+        <v>134</v>
       </c>
       <c r="C59" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="D59" t="s">
         <v>3</v>
@@ -6575,7 +6719,7 @@
         <v>0.000</v>
       </c>
       <c r="S59" t="s">
-        <v>136</v>
+        <v>171</v>
       </c>
       <c r="T59" s="5"/>
       <c r="U59" s="5"/>
@@ -6621,13 +6765,13 @@
     </row>
     <row r="60" spans="1:34">
       <c r="A60" t="s">
-        <v>137</v>
+        <v>172</v>
       </c>
       <c r="B60" t="s">
-        <v>17</v>
+        <v>134</v>
       </c>
       <c r="C60" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="D60" t="s">
         <v>3</v>
@@ -6675,7 +6819,7 @@
         <v>0.000</v>
       </c>
       <c r="S60" t="s">
-        <v>138</v>
+        <v>173</v>
       </c>
       <c r="T60" s="5"/>
       <c r="U60" s="5"/>
@@ -6721,13 +6865,13 @@
     </row>
     <row r="61" spans="1:34">
       <c r="A61" t="s">
-        <v>139</v>
+        <v>174</v>
       </c>
       <c r="B61" t="s">
-        <v>50</v>
+        <v>134</v>
       </c>
       <c r="C61" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D61" t="s">
         <v>3</v>
@@ -6736,10 +6880,10 @@
         <v>4</v>
       </c>
       <c r="F61" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="G61" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H61" s="2">
         <v>1</v>
@@ -6748,13 +6892,13 @@
         <v>7</v>
       </c>
       <c r="J61" s="3">
-        <v>1.0</v>
+        <v>1.5</v>
       </c>
       <c r="K61" s="3">
-        <v>1.0</v>
+        <v>1.5</v>
       </c>
       <c r="L61" s="3">
-        <v>1.0</v>
+        <v>1.5</v>
       </c>
       <c r="M61" t="s">
         <v>8</v>
@@ -6775,7 +6919,7 @@
         <v>0.000</v>
       </c>
       <c r="S61" t="s">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="T61" s="5"/>
       <c r="U61" s="5"/>
@@ -6821,13 +6965,13 @@
     </row>
     <row r="62" spans="1:34">
       <c r="A62" t="s">
-        <v>139</v>
+        <v>176</v>
       </c>
       <c r="B62" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="C62" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="D62" t="s">
         <v>3</v>
@@ -6836,10 +6980,10 @@
         <v>4</v>
       </c>
       <c r="F62" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G62" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H62" s="2">
         <v>1</v>
@@ -6848,13 +6992,13 @@
         <v>7</v>
       </c>
       <c r="J62" s="3">
-        <v>3.0</v>
+        <v>1.5</v>
       </c>
       <c r="K62" s="3">
-        <v>3.0</v>
+        <v>1.5</v>
       </c>
       <c r="L62" s="3">
-        <v>3.0</v>
+        <v>1.5</v>
       </c>
       <c r="M62" t="s">
         <v>8</v>
@@ -6875,7 +7019,7 @@
         <v>0.000</v>
       </c>
       <c r="S62" t="s">
-        <v>141</v>
+        <v>177</v>
       </c>
       <c r="T62" s="5"/>
       <c r="U62" s="5"/>
@@ -6921,13 +7065,13 @@
     </row>
     <row r="63" spans="1:34">
       <c r="A63" t="s">
-        <v>139</v>
+        <v>178</v>
       </c>
       <c r="B63" t="s">
-        <v>50</v>
+        <v>134</v>
       </c>
       <c r="C63" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="D63" t="s">
         <v>3</v>
@@ -6936,10 +7080,10 @@
         <v>4</v>
       </c>
       <c r="F63" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G63" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="H63" s="2">
         <v>1</v>
@@ -6948,13 +7092,13 @@
         <v>7</v>
       </c>
       <c r="J63" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="K63" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="L63" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="M63" t="s">
         <v>8</v>
@@ -6975,7 +7119,7 @@
         <v>0.000</v>
       </c>
       <c r="S63" t="s">
-        <v>142</v>
+        <v>179</v>
       </c>
       <c r="T63" s="5"/>
       <c r="U63" s="5"/>
@@ -7021,13 +7165,13 @@
     </row>
     <row r="64" spans="1:34">
       <c r="A64" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="B64" t="s">
-        <v>50</v>
+        <v>134</v>
       </c>
       <c r="C64" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D64" t="s">
         <v>3</v>
@@ -7036,10 +7180,10 @@
         <v>4</v>
       </c>
       <c r="F64" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="G64" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="H64" s="2">
         <v>1</v>
@@ -7048,13 +7192,13 @@
         <v>7</v>
       </c>
       <c r="J64" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="K64" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="L64" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="M64" t="s">
         <v>8</v>
@@ -7075,7 +7219,7 @@
         <v>0.000</v>
       </c>
       <c r="S64" t="s">
-        <v>143</v>
+        <v>181</v>
       </c>
       <c r="T64" s="5"/>
       <c r="U64" s="5"/>
@@ -7121,13 +7265,13 @@
     </row>
     <row r="65" spans="1:34">
       <c r="A65" t="s">
-        <v>144</v>
+        <v>182</v>
       </c>
       <c r="B65" t="s">
-        <v>40</v>
+        <v>134</v>
       </c>
       <c r="C65" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="D65" t="s">
         <v>3</v>
@@ -7175,7 +7319,7 @@
         <v>0.000</v>
       </c>
       <c r="S65" t="s">
-        <v>145</v>
+        <v>183</v>
       </c>
       <c r="T65" s="5"/>
       <c r="U65" s="5"/>
@@ -7221,13 +7365,13 @@
     </row>
     <row r="66" spans="1:34">
       <c r="A66" t="s">
-        <v>146</v>
+        <v>184</v>
       </c>
       <c r="B66" t="s">
-        <v>40</v>
+        <v>134</v>
       </c>
       <c r="C66" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="D66" t="s">
         <v>3</v>
@@ -7275,7 +7419,7 @@
         <v>0.000</v>
       </c>
       <c r="S66" t="s">
-        <v>147</v>
+        <v>185</v>
       </c>
       <c r="T66" s="5"/>
       <c r="U66" s="5"/>
@@ -7321,13 +7465,13 @@
     </row>
     <row r="67" spans="1:34">
       <c r="A67" t="s">
-        <v>148</v>
+        <v>186</v>
       </c>
       <c r="B67" t="s">
-        <v>40</v>
+        <v>134</v>
       </c>
       <c r="C67" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="D67" t="s">
         <v>3</v>
@@ -7375,7 +7519,7 @@
         <v>0.000</v>
       </c>
       <c r="S67" t="s">
-        <v>149</v>
+        <v>187</v>
       </c>
       <c r="T67" s="5"/>
       <c r="U67" s="5"/>
@@ -7416,6 +7560,506 @@
         <v>3</v>
       </c>
       <c r="AH67" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:34">
+      <c r="A68" t="s">
+        <v>188</v>
+      </c>
+      <c r="B68" t="s">
+        <v>134</v>
+      </c>
+      <c r="C68" t="s">
+        <v>79</v>
+      </c>
+      <c r="D68" t="s">
+        <v>3</v>
+      </c>
+      <c r="E68" t="s">
+        <v>4</v>
+      </c>
+      <c r="F68" t="s">
+        <v>19</v>
+      </c>
+      <c r="G68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H68" s="2">
+        <v>1</v>
+      </c>
+      <c r="I68" t="s">
+        <v>7</v>
+      </c>
+      <c r="J68" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="K68" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="L68" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="M68" t="s">
+        <v>8</v>
+      </c>
+      <c r="N68" s="2">
+        <v>0</v>
+      </c>
+      <c r="O68" s="2">
+        <v>0</v>
+      </c>
+      <c r="P68" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="Q68" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="R68" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="S68" t="s">
+        <v>189</v>
+      </c>
+      <c r="T68" s="5"/>
+      <c r="U68" s="5"/>
+      <c r="V68" t="s">
+        <v>10</v>
+      </c>
+      <c r="W68" t="s">
+        <v>3</v>
+      </c>
+      <c r="X68" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y68" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z68" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA68" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB68" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC68" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD68" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE68" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF68" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG68" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH68" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:34">
+      <c r="A69" t="s">
+        <v>190</v>
+      </c>
+      <c r="B69" t="s">
+        <v>134</v>
+      </c>
+      <c r="C69" t="s">
+        <v>79</v>
+      </c>
+      <c r="D69" t="s">
+        <v>3</v>
+      </c>
+      <c r="E69" t="s">
+        <v>4</v>
+      </c>
+      <c r="F69" t="s">
+        <v>19</v>
+      </c>
+      <c r="G69" t="s">
+        <v>20</v>
+      </c>
+      <c r="H69" s="2">
+        <v>1</v>
+      </c>
+      <c r="I69" t="s">
+        <v>7</v>
+      </c>
+      <c r="J69" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="K69" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="L69" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="M69" t="s">
+        <v>8</v>
+      </c>
+      <c r="N69" s="2">
+        <v>0</v>
+      </c>
+      <c r="O69" s="2">
+        <v>0</v>
+      </c>
+      <c r="P69" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="Q69" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="R69" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="S69" t="s">
+        <v>191</v>
+      </c>
+      <c r="T69" s="5"/>
+      <c r="U69" s="5"/>
+      <c r="V69" t="s">
+        <v>10</v>
+      </c>
+      <c r="W69" t="s">
+        <v>3</v>
+      </c>
+      <c r="X69" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y69" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z69" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA69" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB69" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC69" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD69" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE69" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF69" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG69" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH69" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:34">
+      <c r="A70" t="s">
+        <v>192</v>
+      </c>
+      <c r="B70" t="s">
+        <v>134</v>
+      </c>
+      <c r="C70" t="s">
+        <v>79</v>
+      </c>
+      <c r="D70" t="s">
+        <v>3</v>
+      </c>
+      <c r="E70" t="s">
+        <v>4</v>
+      </c>
+      <c r="F70" t="s">
+        <v>19</v>
+      </c>
+      <c r="G70" t="s">
+        <v>20</v>
+      </c>
+      <c r="H70" s="2">
+        <v>1</v>
+      </c>
+      <c r="I70" t="s">
+        <v>7</v>
+      </c>
+      <c r="J70" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="K70" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="L70" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="M70" t="s">
+        <v>8</v>
+      </c>
+      <c r="N70" s="2">
+        <v>0</v>
+      </c>
+      <c r="O70" s="2">
+        <v>0</v>
+      </c>
+      <c r="P70" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="Q70" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="R70" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="S70" t="s">
+        <v>193</v>
+      </c>
+      <c r="T70" s="5"/>
+      <c r="U70" s="5"/>
+      <c r="V70" t="s">
+        <v>10</v>
+      </c>
+      <c r="W70" t="s">
+        <v>3</v>
+      </c>
+      <c r="X70" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y70" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z70" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA70" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB70" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC70" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD70" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE70" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF70" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG70" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH70" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:34">
+      <c r="A71" t="s">
+        <v>194</v>
+      </c>
+      <c r="B71" t="s">
+        <v>134</v>
+      </c>
+      <c r="C71" t="s">
+        <v>79</v>
+      </c>
+      <c r="D71" t="s">
+        <v>3</v>
+      </c>
+      <c r="E71" t="s">
+        <v>4</v>
+      </c>
+      <c r="F71" t="s">
+        <v>19</v>
+      </c>
+      <c r="G71" t="s">
+        <v>20</v>
+      </c>
+      <c r="H71" s="2">
+        <v>1</v>
+      </c>
+      <c r="I71" t="s">
+        <v>7</v>
+      </c>
+      <c r="J71" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="K71" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="L71" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="M71" t="s">
+        <v>8</v>
+      </c>
+      <c r="N71" s="2">
+        <v>0</v>
+      </c>
+      <c r="O71" s="2">
+        <v>0</v>
+      </c>
+      <c r="P71" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="Q71" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="R71" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="S71" t="s">
+        <v>195</v>
+      </c>
+      <c r="T71" s="5"/>
+      <c r="U71" s="5"/>
+      <c r="V71" t="s">
+        <v>10</v>
+      </c>
+      <c r="W71" t="s">
+        <v>3</v>
+      </c>
+      <c r="X71" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y71" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z71" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA71" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB71" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC71" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD71" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE71" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF71" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG71" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH71" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:34">
+      <c r="A72" t="s">
+        <v>196</v>
+      </c>
+      <c r="B72" t="s">
+        <v>134</v>
+      </c>
+      <c r="C72" t="s">
+        <v>79</v>
+      </c>
+      <c r="D72" t="s">
+        <v>3</v>
+      </c>
+      <c r="E72" t="s">
+        <v>4</v>
+      </c>
+      <c r="F72" t="s">
+        <v>19</v>
+      </c>
+      <c r="G72" t="s">
+        <v>20</v>
+      </c>
+      <c r="H72" s="2">
+        <v>1</v>
+      </c>
+      <c r="I72" t="s">
+        <v>7</v>
+      </c>
+      <c r="J72" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="K72" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="L72" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="M72" t="s">
+        <v>8</v>
+      </c>
+      <c r="N72" s="2">
+        <v>0</v>
+      </c>
+      <c r="O72" s="2">
+        <v>0</v>
+      </c>
+      <c r="P72" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="Q72" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="R72" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="S72" t="s">
+        <v>197</v>
+      </c>
+      <c r="T72" s="5"/>
+      <c r="U72" s="5"/>
+      <c r="V72" t="s">
+        <v>10</v>
+      </c>
+      <c r="W72" t="s">
+        <v>3</v>
+      </c>
+      <c r="X72" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z72" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA72" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB72" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC72" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD72" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE72" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF72" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG72" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH72" t="s">
         <v>3</v>
       </c>
     </row>

--- a/Newdata/成品報工.XLSX
+++ b/Newdata/成品報工.XLSX
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1667" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1690" uniqueCount="234">
   <si>
     <t>100003496</t>
   </si>
@@ -605,6 +605,12 @@
   </si>
   <si>
     <t>1469385</t>
+  </si>
+  <si>
+    <t>100003622</t>
+  </si>
+  <si>
+    <t>1472369</t>
   </si>
   <si>
     <t>訂單</t>
@@ -820,7 +826,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AH72"/>
+  <dimension ref="A1:AH73"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="11" customWidth="1"/>
@@ -861,106 +867,106 @@
   <sheetData>
     <row r="1" spans="1:34">
       <c r="A1" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q1" s="6" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="R1" s="6" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:34">
@@ -8060,6 +8066,106 @@
         <v>3</v>
       </c>
       <c r="AH72" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:34">
+      <c r="A73" t="s">
+        <v>198</v>
+      </c>
+      <c r="B73" t="s">
+        <v>134</v>
+      </c>
+      <c r="C73" t="s">
+        <v>79</v>
+      </c>
+      <c r="D73" t="s">
+        <v>3</v>
+      </c>
+      <c r="E73" t="s">
+        <v>4</v>
+      </c>
+      <c r="F73" t="s">
+        <v>19</v>
+      </c>
+      <c r="G73" t="s">
+        <v>20</v>
+      </c>
+      <c r="H73" s="2">
+        <v>1</v>
+      </c>
+      <c r="I73" t="s">
+        <v>7</v>
+      </c>
+      <c r="J73" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="K73" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="L73" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="M73" t="s">
+        <v>8</v>
+      </c>
+      <c r="N73" s="2">
+        <v>0</v>
+      </c>
+      <c r="O73" s="2">
+        <v>0</v>
+      </c>
+      <c r="P73" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="Q73" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="R73" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="S73" t="s">
+        <v>199</v>
+      </c>
+      <c r="T73" s="5"/>
+      <c r="U73" s="5"/>
+      <c r="V73" t="s">
+        <v>10</v>
+      </c>
+      <c r="W73" t="s">
+        <v>3</v>
+      </c>
+      <c r="X73" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y73" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z73" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA73" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB73" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC73" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD73" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE73" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF73" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG73" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH73" t="s">
         <v>3</v>
       </c>
     </row>

--- a/Newdata/成品報工.XLSX
+++ b/Newdata/成品報工.XLSX
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1690" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1782" uniqueCount="246">
   <si>
     <t>100003496</t>
   </si>
@@ -193,84 +193,69 @@
     <t>1436362</t>
   </si>
   <si>
-    <t>100003559</t>
-  </si>
-  <si>
-    <t>1439653</t>
-  </si>
-  <si>
-    <t>1439654</t>
-  </si>
-  <si>
-    <t>1439655</t>
+    <t>100003560</t>
+  </si>
+  <si>
+    <t>0270</t>
+  </si>
+  <si>
+    <t>3050001</t>
+  </si>
+  <si>
+    <t>刀庫安裝</t>
+  </si>
+  <si>
+    <t>1439868</t>
+  </si>
+  <si>
+    <t>0850</t>
+  </si>
+  <si>
+    <t>3050007</t>
+  </si>
+  <si>
+    <t>刀庫調整</t>
+  </si>
+  <si>
+    <t>1439911</t>
+  </si>
+  <si>
+    <t>0860</t>
+  </si>
+  <si>
+    <t>3050002</t>
+  </si>
+  <si>
+    <t>刀庫合刀作業</t>
+  </si>
+  <si>
+    <t>1439912</t>
+  </si>
+  <si>
+    <t>0170</t>
+  </si>
+  <si>
+    <t>1439974</t>
+  </si>
+  <si>
+    <t>100003562</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>1560007</t>
+  </si>
+  <si>
+    <t>頭倉底座組清潔</t>
+  </si>
+  <si>
+    <t>1440639</t>
   </si>
   <si>
     <t>0230</t>
   </si>
   <si>
-    <t>1439656</t>
-  </si>
-  <si>
-    <t>100003560</t>
-  </si>
-  <si>
-    <t>0270</t>
-  </si>
-  <si>
-    <t>3050001</t>
-  </si>
-  <si>
-    <t>刀庫安裝</t>
-  </si>
-  <si>
-    <t>1439868</t>
-  </si>
-  <si>
-    <t>0850</t>
-  </si>
-  <si>
-    <t>3050007</t>
-  </si>
-  <si>
-    <t>刀庫調整</t>
-  </si>
-  <si>
-    <t>1439911</t>
-  </si>
-  <si>
-    <t>0860</t>
-  </si>
-  <si>
-    <t>3050002</t>
-  </si>
-  <si>
-    <t>刀庫合刀作業</t>
-  </si>
-  <si>
-    <t>1439912</t>
-  </si>
-  <si>
-    <t>0170</t>
-  </si>
-  <si>
-    <t>1439974</t>
-  </si>
-  <si>
-    <t>100003562</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>1560007</t>
-  </si>
-  <si>
-    <t>頭倉底座組清潔</t>
-  </si>
-  <si>
-    <t>1440639</t>
-  </si>
-  <si>
     <t>1560008</t>
   </si>
   <si>
@@ -412,24 +397,12 @@
     <t>1443844</t>
   </si>
   <si>
-    <t>100003572</t>
+    <t>100003574</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>1444654</t>
-  </si>
-  <si>
-    <t>100003573</t>
-  </si>
-  <si>
-    <t>1444858</t>
-  </si>
-  <si>
-    <t>100003574</t>
-  </si>
-  <si>
     <t>1445062</t>
   </si>
   <si>
@@ -611,6 +584,69 @@
   </si>
   <si>
     <t>1472369</t>
+  </si>
+  <si>
+    <t>100003625</t>
+  </si>
+  <si>
+    <t>1473665</t>
+  </si>
+  <si>
+    <t>100003626</t>
+  </si>
+  <si>
+    <t>1473765</t>
+  </si>
+  <si>
+    <t>100003627</t>
+  </si>
+  <si>
+    <t>1473865</t>
+  </si>
+  <si>
+    <t>100003628</t>
+  </si>
+  <si>
+    <t>1473965</t>
+  </si>
+  <si>
+    <t>100003629</t>
+  </si>
+  <si>
+    <t>1474065</t>
+  </si>
+  <si>
+    <t>100003630</t>
+  </si>
+  <si>
+    <t>1474165</t>
+  </si>
+  <si>
+    <t>100003631</t>
+  </si>
+  <si>
+    <t>1475227</t>
+  </si>
+  <si>
+    <t>CRTD</t>
+  </si>
+  <si>
+    <t>100003634</t>
+  </si>
+  <si>
+    <t>1476008</t>
+  </si>
+  <si>
+    <t>100003635</t>
+  </si>
+  <si>
+    <t>1476087</t>
+  </si>
+  <si>
+    <t>100003636</t>
+  </si>
+  <si>
+    <t>1476212</t>
   </si>
   <si>
     <t>訂單</t>
@@ -826,7 +862,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AH73"/>
+  <dimension ref="A1:AH77"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="11" customWidth="1"/>
@@ -867,106 +903,106 @@
   <sheetData>
     <row r="1" spans="1:34">
       <c r="A1" s="1" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="Q1" s="6" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="R1" s="6" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
     </row>
     <row r="2" spans="1:34">
@@ -2674,10 +2710,10 @@
         <v>60</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="D19" t="s">
         <v>3</v>
@@ -2686,10 +2722,10 @@
         <v>4</v>
       </c>
       <c r="F19" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="G19" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="H19" s="2">
         <v>1</v>
@@ -2698,13 +2734,13 @@
         <v>7</v>
       </c>
       <c r="J19" s="3">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="K19" s="3">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="L19" s="3">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="M19" t="s">
         <v>8</v>
@@ -2725,7 +2761,7 @@
         <v>0.000</v>
       </c>
       <c r="S19" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="T19" s="5"/>
       <c r="U19" s="5"/>
@@ -2774,10 +2810,10 @@
         <v>60</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="D20" t="s">
         <v>3</v>
@@ -2786,10 +2822,10 @@
         <v>4</v>
       </c>
       <c r="F20" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="G20" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="H20" s="2">
         <v>1</v>
@@ -2798,13 +2834,13 @@
         <v>7</v>
       </c>
       <c r="J20" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="K20" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="L20" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="M20" t="s">
         <v>8</v>
@@ -2825,7 +2861,7 @@
         <v>0.000</v>
       </c>
       <c r="S20" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="T20" s="5"/>
       <c r="U20" s="5"/>
@@ -2874,10 +2910,10 @@
         <v>60</v>
       </c>
       <c r="B21" t="s">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="D21" t="s">
         <v>3</v>
@@ -2886,10 +2922,10 @@
         <v>4</v>
       </c>
       <c r="F21" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="G21" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="H21" s="2">
         <v>1</v>
@@ -2925,7 +2961,7 @@
         <v>0.000</v>
       </c>
       <c r="S21" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="T21" s="5"/>
       <c r="U21" s="5"/>
@@ -2974,10 +3010,10 @@
         <v>60</v>
       </c>
       <c r="B22" t="s">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="C22" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="D22" t="s">
         <v>3</v>
@@ -2986,10 +3022,10 @@
         <v>4</v>
       </c>
       <c r="F22" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="G22" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="H22" s="2">
         <v>1</v>
@@ -2998,13 +3034,13 @@
         <v>7</v>
       </c>
       <c r="J22" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="K22" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="L22" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="M22" t="s">
         <v>8</v>
@@ -3025,7 +3061,7 @@
         <v>0.000</v>
       </c>
       <c r="S22" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="T22" s="5"/>
       <c r="U22" s="5"/>
@@ -3071,13 +3107,13 @@
     </row>
     <row r="23" spans="1:34">
       <c r="A23" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="B23" t="s">
-        <v>1</v>
+        <v>76</v>
       </c>
       <c r="C23" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="D23" t="s">
         <v>3</v>
@@ -3086,10 +3122,10 @@
         <v>4</v>
       </c>
       <c r="F23" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="G23" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="H23" s="2">
         <v>1</v>
@@ -3125,7 +3161,7 @@
         <v>0.000</v>
       </c>
       <c r="S23" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="T23" s="5"/>
       <c r="U23" s="5"/>
@@ -3171,13 +3207,13 @@
     </row>
     <row r="24" spans="1:34">
       <c r="A24" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="B24" t="s">
-        <v>1</v>
+        <v>76</v>
       </c>
       <c r="C24" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="D24" t="s">
         <v>3</v>
@@ -3186,10 +3222,10 @@
         <v>4</v>
       </c>
       <c r="F24" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="G24" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="H24" s="2">
         <v>1</v>
@@ -3225,7 +3261,7 @@
         <v>0.000</v>
       </c>
       <c r="S24" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="T24" s="5"/>
       <c r="U24" s="5"/>
@@ -3271,13 +3307,13 @@
     </row>
     <row r="25" spans="1:34">
       <c r="A25" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="B25" t="s">
-        <v>1</v>
+        <v>76</v>
       </c>
       <c r="C25" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="D25" t="s">
         <v>3</v>
@@ -3286,10 +3322,10 @@
         <v>4</v>
       </c>
       <c r="F25" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G25" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H25" s="2">
         <v>1</v>
@@ -3325,7 +3361,7 @@
         <v>0.000</v>
       </c>
       <c r="S25" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="T25" s="5"/>
       <c r="U25" s="5"/>
@@ -3371,13 +3407,13 @@
     </row>
     <row r="26" spans="1:34">
       <c r="A26" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="B26" t="s">
-        <v>11</v>
+        <v>76</v>
       </c>
       <c r="C26" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="D26" t="s">
         <v>3</v>
@@ -3386,10 +3422,10 @@
         <v>4</v>
       </c>
       <c r="F26" t="s">
-        <v>19</v>
+        <v>89</v>
       </c>
       <c r="G26" t="s">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="H26" s="2">
         <v>1</v>
@@ -3398,13 +3434,13 @@
         <v>7</v>
       </c>
       <c r="J26" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="K26" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="L26" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="M26" t="s">
         <v>8</v>
@@ -3425,7 +3461,7 @@
         <v>0.000</v>
       </c>
       <c r="S26" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="T26" s="5"/>
       <c r="U26" s="5"/>
@@ -3471,13 +3507,13 @@
     </row>
     <row r="27" spans="1:34">
       <c r="A27" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B27" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C27" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="D27" t="s">
         <v>3</v>
@@ -3486,10 +3522,10 @@
         <v>4</v>
       </c>
       <c r="F27" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="G27" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="H27" s="2">
         <v>1</v>
@@ -3525,7 +3561,7 @@
         <v>0.000</v>
       </c>
       <c r="S27" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="T27" s="5"/>
       <c r="U27" s="5"/>
@@ -3571,13 +3607,13 @@
     </row>
     <row r="28" spans="1:34">
       <c r="A28" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B28" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C28" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D28" t="s">
         <v>3</v>
@@ -3586,10 +3622,10 @@
         <v>4</v>
       </c>
       <c r="F28" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="G28" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="H28" s="2">
         <v>1</v>
@@ -3625,7 +3661,7 @@
         <v>0.000</v>
       </c>
       <c r="S28" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="T28" s="5"/>
       <c r="U28" s="5"/>
@@ -3671,13 +3707,13 @@
     </row>
     <row r="29" spans="1:34">
       <c r="A29" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B29" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C29" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="D29" t="s">
         <v>3</v>
@@ -3686,10 +3722,10 @@
         <v>4</v>
       </c>
       <c r="F29" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G29" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="H29" s="2">
         <v>1</v>
@@ -3725,7 +3761,7 @@
         <v>0.000</v>
       </c>
       <c r="S29" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="T29" s="5"/>
       <c r="U29" s="5"/>
@@ -3771,13 +3807,13 @@
     </row>
     <row r="30" spans="1:34">
       <c r="A30" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B30" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C30" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="D30" t="s">
         <v>3</v>
@@ -3786,10 +3822,10 @@
         <v>4</v>
       </c>
       <c r="F30" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="G30" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="H30" s="2">
         <v>1</v>
@@ -3825,7 +3861,7 @@
         <v>0.000</v>
       </c>
       <c r="S30" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="T30" s="5"/>
       <c r="U30" s="5"/>
@@ -3871,13 +3907,13 @@
     </row>
     <row r="31" spans="1:34">
       <c r="A31" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B31" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C31" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="D31" t="s">
         <v>3</v>
@@ -3886,10 +3922,10 @@
         <v>4</v>
       </c>
       <c r="F31" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="G31" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="H31" s="2">
         <v>1</v>
@@ -3925,7 +3961,7 @@
         <v>0.000</v>
       </c>
       <c r="S31" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="T31" s="5"/>
       <c r="U31" s="5"/>
@@ -3971,13 +4007,13 @@
     </row>
     <row r="32" spans="1:34">
       <c r="A32" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B32" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C32" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="D32" t="s">
         <v>3</v>
@@ -3986,10 +4022,10 @@
         <v>4</v>
       </c>
       <c r="F32" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="G32" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="H32" s="2">
         <v>1</v>
@@ -4025,7 +4061,7 @@
         <v>0.000</v>
       </c>
       <c r="S32" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="T32" s="5"/>
       <c r="U32" s="5"/>
@@ -4071,13 +4107,13 @@
     </row>
     <row r="33" spans="1:34">
       <c r="A33" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B33" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C33" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="D33" t="s">
         <v>3</v>
@@ -4086,10 +4122,10 @@
         <v>4</v>
       </c>
       <c r="F33" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="G33" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="H33" s="2">
         <v>1</v>
@@ -4098,13 +4134,13 @@
         <v>7</v>
       </c>
       <c r="J33" s="3">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="K33" s="3">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="L33" s="3">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="M33" t="s">
         <v>8</v>
@@ -4125,7 +4161,7 @@
         <v>0.000</v>
       </c>
       <c r="S33" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="T33" s="5"/>
       <c r="U33" s="5"/>
@@ -4171,13 +4207,13 @@
     </row>
     <row r="34" spans="1:34">
       <c r="A34" t="s">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="B34" t="s">
-        <v>82</v>
+        <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="D34" t="s">
         <v>3</v>
@@ -4186,10 +4222,10 @@
         <v>4</v>
       </c>
       <c r="F34" t="s">
-        <v>109</v>
+        <v>70</v>
       </c>
       <c r="G34" t="s">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="H34" s="2">
         <v>1</v>
@@ -4225,7 +4261,7 @@
         <v>0.000</v>
       </c>
       <c r="S34" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="T34" s="5"/>
       <c r="U34" s="5"/>
@@ -4271,13 +4307,13 @@
     </row>
     <row r="35" spans="1:34">
       <c r="A35" t="s">
-        <v>81</v>
+        <v>121</v>
       </c>
       <c r="B35" t="s">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="C35" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="D35" t="s">
         <v>3</v>
@@ -4286,10 +4322,10 @@
         <v>4</v>
       </c>
       <c r="F35" t="s">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="G35" t="s">
-        <v>114</v>
+        <v>20</v>
       </c>
       <c r="H35" s="2">
         <v>1</v>
@@ -4298,13 +4334,13 @@
         <v>7</v>
       </c>
       <c r="J35" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="K35" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="L35" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="M35" t="s">
         <v>8</v>
@@ -4325,7 +4361,7 @@
         <v>0.000</v>
       </c>
       <c r="S35" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="T35" s="5"/>
       <c r="U35" s="5"/>
@@ -4371,13 +4407,13 @@
     </row>
     <row r="36" spans="1:34">
       <c r="A36" t="s">
-        <v>81</v>
+        <v>125</v>
       </c>
       <c r="B36" t="s">
-        <v>82</v>
+        <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>18</v>
+        <v>126</v>
       </c>
       <c r="D36" t="s">
         <v>3</v>
@@ -4386,10 +4422,10 @@
         <v>4</v>
       </c>
       <c r="F36" t="s">
-        <v>116</v>
+        <v>19</v>
       </c>
       <c r="G36" t="s">
-        <v>117</v>
+        <v>20</v>
       </c>
       <c r="H36" s="2">
         <v>1</v>
@@ -4398,13 +4434,13 @@
         <v>7</v>
       </c>
       <c r="J36" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="K36" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="L36" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="M36" t="s">
         <v>8</v>
@@ -4425,7 +4461,7 @@
         <v>0.000</v>
       </c>
       <c r="S36" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="T36" s="5"/>
       <c r="U36" s="5"/>
@@ -4471,13 +4507,13 @@
     </row>
     <row r="37" spans="1:34">
       <c r="A37" t="s">
-        <v>81</v>
+        <v>128</v>
       </c>
       <c r="B37" t="s">
-        <v>82</v>
+        <v>129</v>
       </c>
       <c r="C37" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="D37" t="s">
         <v>3</v>
@@ -4486,10 +4522,10 @@
         <v>4</v>
       </c>
       <c r="F37" t="s">
-        <v>120</v>
+        <v>19</v>
       </c>
       <c r="G37" t="s">
-        <v>121</v>
+        <v>20</v>
       </c>
       <c r="H37" s="2">
         <v>1</v>
@@ -4498,13 +4534,13 @@
         <v>7</v>
       </c>
       <c r="J37" s="3">
-        <v>2.0</v>
+        <v>1.5</v>
       </c>
       <c r="K37" s="3">
-        <v>2.0</v>
+        <v>1.5</v>
       </c>
       <c r="L37" s="3">
-        <v>2.0</v>
+        <v>1.5</v>
       </c>
       <c r="M37" t="s">
         <v>8</v>
@@ -4525,7 +4561,7 @@
         <v>0.000</v>
       </c>
       <c r="S37" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="T37" s="5"/>
       <c r="U37" s="5"/>
@@ -4571,13 +4607,13 @@
     </row>
     <row r="38" spans="1:34">
       <c r="A38" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B38" t="s">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="C38" t="s">
-        <v>124</v>
+        <v>45</v>
       </c>
       <c r="D38" t="s">
         <v>3</v>
@@ -4586,10 +4622,10 @@
         <v>4</v>
       </c>
       <c r="F38" t="s">
-        <v>76</v>
+        <v>19</v>
       </c>
       <c r="G38" t="s">
-        <v>77</v>
+        <v>20</v>
       </c>
       <c r="H38" s="2">
         <v>1</v>
@@ -4598,13 +4634,13 @@
         <v>7</v>
       </c>
       <c r="J38" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="K38" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="L38" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="M38" t="s">
         <v>8</v>
@@ -4625,7 +4661,7 @@
         <v>0.000</v>
       </c>
       <c r="S38" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="T38" s="5"/>
       <c r="U38" s="5"/>
@@ -4671,13 +4707,13 @@
     </row>
     <row r="39" spans="1:34">
       <c r="A39" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B39" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C39" t="s">
-        <v>128</v>
+        <v>45</v>
       </c>
       <c r="D39" t="s">
         <v>3</v>
@@ -4725,7 +4761,7 @@
         <v>0.000</v>
       </c>
       <c r="S39" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="T39" s="5"/>
       <c r="U39" s="5"/>
@@ -4771,13 +4807,13 @@
     </row>
     <row r="40" spans="1:34">
       <c r="A40" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B40" t="s">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="C40" t="s">
-        <v>131</v>
+        <v>45</v>
       </c>
       <c r="D40" t="s">
         <v>3</v>
@@ -4825,7 +4861,7 @@
         <v>0.000</v>
       </c>
       <c r="S40" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="T40" s="5"/>
       <c r="U40" s="5"/>
@@ -4871,13 +4907,13 @@
     </row>
     <row r="41" spans="1:34">
       <c r="A41" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B41" t="s">
-        <v>134</v>
+        <v>17</v>
       </c>
       <c r="C41" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="D41" t="s">
         <v>3</v>
@@ -4925,7 +4961,7 @@
         <v>0.000</v>
       </c>
       <c r="S41" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="T41" s="5"/>
       <c r="U41" s="5"/>
@@ -4971,13 +5007,13 @@
     </row>
     <row r="42" spans="1:34">
       <c r="A42" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B42" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="C42" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="D42" t="s">
         <v>3</v>
@@ -5025,7 +5061,7 @@
         <v>0.000</v>
       </c>
       <c r="S42" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="T42" s="5"/>
       <c r="U42" s="5"/>
@@ -5071,10 +5107,10 @@
     </row>
     <row r="43" spans="1:34">
       <c r="A43" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B43" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C43" t="s">
         <v>45</v>
@@ -5125,7 +5161,7 @@
         <v>0.000</v>
       </c>
       <c r="S43" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="T43" s="5"/>
       <c r="U43" s="5"/>
@@ -5171,13 +5207,13 @@
     </row>
     <row r="44" spans="1:34">
       <c r="A44" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B44" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C44" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="D44" t="s">
         <v>3</v>
@@ -5225,7 +5261,7 @@
         <v>0.000</v>
       </c>
       <c r="S44" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="T44" s="5"/>
       <c r="U44" s="5"/>
@@ -5271,10 +5307,10 @@
     </row>
     <row r="45" spans="1:34">
       <c r="A45" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B45" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C45" t="s">
         <v>45</v>
@@ -5325,7 +5361,7 @@
         <v>0.000</v>
       </c>
       <c r="S45" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="T45" s="5"/>
       <c r="U45" s="5"/>
@@ -5371,10 +5407,10 @@
     </row>
     <row r="46" spans="1:34">
       <c r="A46" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B46" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C46" t="s">
         <v>45</v>
@@ -5425,7 +5461,7 @@
         <v>0.000</v>
       </c>
       <c r="S46" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="T46" s="5"/>
       <c r="U46" s="5"/>
@@ -5471,13 +5507,13 @@
     </row>
     <row r="47" spans="1:34">
       <c r="A47" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B47" t="s">
-        <v>17</v>
+        <v>129</v>
       </c>
       <c r="C47" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="D47" t="s">
         <v>3</v>
@@ -5525,7 +5561,7 @@
         <v>0.000</v>
       </c>
       <c r="S47" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="T47" s="5"/>
       <c r="U47" s="5"/>
@@ -5571,13 +5607,13 @@
     </row>
     <row r="48" spans="1:34">
       <c r="A48" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B48" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C48" t="s">
-        <v>79</v>
+        <v>45</v>
       </c>
       <c r="D48" t="s">
         <v>3</v>
@@ -5625,7 +5661,7 @@
         <v>0.000</v>
       </c>
       <c r="S48" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="T48" s="5"/>
       <c r="U48" s="5"/>
@@ -5671,10 +5707,10 @@
     </row>
     <row r="49" spans="1:34">
       <c r="A49" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B49" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C49" t="s">
         <v>45</v>
@@ -5725,7 +5761,7 @@
         <v>0.000</v>
       </c>
       <c r="S49" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="T49" s="5"/>
       <c r="U49" s="5"/>
@@ -5771,13 +5807,13 @@
     </row>
     <row r="50" spans="1:34">
       <c r="A50" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B50" t="s">
-        <v>134</v>
+        <v>17</v>
       </c>
       <c r="C50" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="D50" t="s">
         <v>3</v>
@@ -5825,7 +5861,7 @@
         <v>0.000</v>
       </c>
       <c r="S50" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="T50" s="5"/>
       <c r="U50" s="5"/>
@@ -5871,13 +5907,13 @@
     </row>
     <row r="51" spans="1:34">
       <c r="A51" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B51" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="C51" t="s">
-        <v>45</v>
+        <v>123</v>
       </c>
       <c r="D51" t="s">
         <v>3</v>
@@ -5925,7 +5961,7 @@
         <v>0.000</v>
       </c>
       <c r="S51" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="T51" s="5"/>
       <c r="U51" s="5"/>
@@ -5971,10 +6007,10 @@
     </row>
     <row r="52" spans="1:34">
       <c r="A52" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B52" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C52" t="s">
         <v>45</v>
@@ -6025,7 +6061,7 @@
         <v>0.000</v>
       </c>
       <c r="S52" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="T52" s="5"/>
       <c r="U52" s="5"/>
@@ -6071,10 +6107,10 @@
     </row>
     <row r="53" spans="1:34">
       <c r="A53" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B53" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C53" t="s">
         <v>45</v>
@@ -6125,7 +6161,7 @@
         <v>0.000</v>
       </c>
       <c r="S53" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="T53" s="5"/>
       <c r="U53" s="5"/>
@@ -6171,10 +6207,10 @@
     </row>
     <row r="54" spans="1:34">
       <c r="A54" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B54" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C54" t="s">
         <v>45</v>
@@ -6225,7 +6261,7 @@
         <v>0.000</v>
       </c>
       <c r="S54" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="T54" s="5"/>
       <c r="U54" s="5"/>
@@ -6271,10 +6307,10 @@
     </row>
     <row r="55" spans="1:34">
       <c r="A55" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B55" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C55" t="s">
         <v>45</v>
@@ -6325,7 +6361,7 @@
         <v>0.000</v>
       </c>
       <c r="S55" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="T55" s="5"/>
       <c r="U55" s="5"/>
@@ -6371,13 +6407,13 @@
     </row>
     <row r="56" spans="1:34">
       <c r="A56" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B56" t="s">
         <v>17</v>
       </c>
       <c r="C56" t="s">
-        <v>112</v>
+        <v>18</v>
       </c>
       <c r="D56" t="s">
         <v>3</v>
@@ -6425,7 +6461,7 @@
         <v>0.000</v>
       </c>
       <c r="S56" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="T56" s="5"/>
       <c r="U56" s="5"/>
@@ -6471,13 +6507,13 @@
     </row>
     <row r="57" spans="1:34">
       <c r="A57" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B57" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C57" t="s">
-        <v>128</v>
+        <v>73</v>
       </c>
       <c r="D57" t="s">
         <v>3</v>
@@ -6525,7 +6561,7 @@
         <v>0.000</v>
       </c>
       <c r="S57" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="T57" s="5"/>
       <c r="U57" s="5"/>
@@ -6571,13 +6607,13 @@
     </row>
     <row r="58" spans="1:34">
       <c r="A58" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B58" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C58" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="D58" t="s">
         <v>3</v>
@@ -6625,7 +6661,7 @@
         <v>0.000</v>
       </c>
       <c r="S58" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="T58" s="5"/>
       <c r="U58" s="5"/>
@@ -6671,13 +6707,13 @@
     </row>
     <row r="59" spans="1:34">
       <c r="A59" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B59" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C59" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="D59" t="s">
         <v>3</v>
@@ -6725,7 +6761,7 @@
         <v>0.000</v>
       </c>
       <c r="S59" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="T59" s="5"/>
       <c r="U59" s="5"/>
@@ -6771,13 +6807,13 @@
     </row>
     <row r="60" spans="1:34">
       <c r="A60" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B60" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C60" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="D60" t="s">
         <v>3</v>
@@ -6825,7 +6861,7 @@
         <v>0.000</v>
       </c>
       <c r="S60" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="T60" s="5"/>
       <c r="U60" s="5"/>
@@ -6871,13 +6907,13 @@
     </row>
     <row r="61" spans="1:34">
       <c r="A61" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B61" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C61" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="D61" t="s">
         <v>3</v>
@@ -6925,7 +6961,7 @@
         <v>0.000</v>
       </c>
       <c r="S61" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="T61" s="5"/>
       <c r="U61" s="5"/>
@@ -6971,13 +7007,13 @@
     </row>
     <row r="62" spans="1:34">
       <c r="A62" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B62" t="s">
-        <v>17</v>
+        <v>129</v>
       </c>
       <c r="C62" t="s">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="D62" t="s">
         <v>3</v>
@@ -7025,7 +7061,7 @@
         <v>0.000</v>
       </c>
       <c r="S62" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="T62" s="5"/>
       <c r="U62" s="5"/>
@@ -7071,13 +7107,13 @@
     </row>
     <row r="63" spans="1:34">
       <c r="A63" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B63" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C63" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D63" t="s">
         <v>3</v>
@@ -7125,7 +7161,7 @@
         <v>0.000</v>
       </c>
       <c r="S63" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="T63" s="5"/>
       <c r="U63" s="5"/>
@@ -7171,13 +7207,13 @@
     </row>
     <row r="64" spans="1:34">
       <c r="A64" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B64" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C64" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D64" t="s">
         <v>3</v>
@@ -7225,7 +7261,7 @@
         <v>0.000</v>
       </c>
       <c r="S64" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="T64" s="5"/>
       <c r="U64" s="5"/>
@@ -7271,13 +7307,13 @@
     </row>
     <row r="65" spans="1:34">
       <c r="A65" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B65" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C65" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D65" t="s">
         <v>3</v>
@@ -7325,7 +7361,7 @@
         <v>0.000</v>
       </c>
       <c r="S65" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="T65" s="5"/>
       <c r="U65" s="5"/>
@@ -7371,13 +7407,13 @@
     </row>
     <row r="66" spans="1:34">
       <c r="A66" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B66" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C66" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D66" t="s">
         <v>3</v>
@@ -7425,7 +7461,7 @@
         <v>0.000</v>
       </c>
       <c r="S66" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="T66" s="5"/>
       <c r="U66" s="5"/>
@@ -7471,13 +7507,13 @@
     </row>
     <row r="67" spans="1:34">
       <c r="A67" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B67" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C67" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D67" t="s">
         <v>3</v>
@@ -7525,7 +7561,7 @@
         <v>0.000</v>
       </c>
       <c r="S67" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="T67" s="5"/>
       <c r="U67" s="5"/>
@@ -7571,13 +7607,13 @@
     </row>
     <row r="68" spans="1:34">
       <c r="A68" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B68" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C68" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D68" t="s">
         <v>3</v>
@@ -7625,7 +7661,7 @@
         <v>0.000</v>
       </c>
       <c r="S68" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="T68" s="5"/>
       <c r="U68" s="5"/>
@@ -7671,13 +7707,13 @@
     </row>
     <row r="69" spans="1:34">
       <c r="A69" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B69" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C69" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D69" t="s">
         <v>3</v>
@@ -7725,7 +7761,7 @@
         <v>0.000</v>
       </c>
       <c r="S69" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="T69" s="5"/>
       <c r="U69" s="5"/>
@@ -7771,13 +7807,13 @@
     </row>
     <row r="70" spans="1:34">
       <c r="A70" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B70" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C70" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D70" t="s">
         <v>3</v>
@@ -7825,7 +7861,7 @@
         <v>0.000</v>
       </c>
       <c r="S70" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="T70" s="5"/>
       <c r="U70" s="5"/>
@@ -7871,13 +7907,13 @@
     </row>
     <row r="71" spans="1:34">
       <c r="A71" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B71" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C71" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D71" t="s">
         <v>3</v>
@@ -7925,7 +7961,7 @@
         <v>0.000</v>
       </c>
       <c r="S71" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="T71" s="5"/>
       <c r="U71" s="5"/>
@@ -7971,13 +8007,13 @@
     </row>
     <row r="72" spans="1:34">
       <c r="A72" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B72" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C72" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D72" t="s">
         <v>3</v>
@@ -8025,7 +8061,7 @@
         <v>0.000</v>
       </c>
       <c r="S72" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="T72" s="5"/>
       <c r="U72" s="5"/>
@@ -8071,13 +8107,13 @@
     </row>
     <row r="73" spans="1:34">
       <c r="A73" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B73" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C73" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D73" t="s">
         <v>3</v>
@@ -8125,7 +8161,7 @@
         <v>0.000</v>
       </c>
       <c r="S73" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="T73" s="5"/>
       <c r="U73" s="5"/>
@@ -8166,6 +8202,406 @@
         <v>3</v>
       </c>
       <c r="AH73" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:34">
+      <c r="A74" t="s">
+        <v>203</v>
+      </c>
+      <c r="B74" t="s">
+        <v>129</v>
+      </c>
+      <c r="C74" t="s">
+        <v>45</v>
+      </c>
+      <c r="D74" t="s">
+        <v>3</v>
+      </c>
+      <c r="E74" t="s">
+        <v>4</v>
+      </c>
+      <c r="F74" t="s">
+        <v>19</v>
+      </c>
+      <c r="G74" t="s">
+        <v>20</v>
+      </c>
+      <c r="H74" s="2">
+        <v>1</v>
+      </c>
+      <c r="I74" t="s">
+        <v>7</v>
+      </c>
+      <c r="J74" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="K74" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="L74" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="M74" t="s">
+        <v>8</v>
+      </c>
+      <c r="N74" s="2">
+        <v>0</v>
+      </c>
+      <c r="O74" s="2">
+        <v>0</v>
+      </c>
+      <c r="P74" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="Q74" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="R74" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="S74" t="s">
+        <v>204</v>
+      </c>
+      <c r="T74" s="5"/>
+      <c r="U74" s="5"/>
+      <c r="V74" t="s">
+        <v>205</v>
+      </c>
+      <c r="W74" t="s">
+        <v>3</v>
+      </c>
+      <c r="X74" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y74" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z74" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA74" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB74" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC74" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD74" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE74" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF74" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG74" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH74" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:34">
+      <c r="A75" t="s">
+        <v>206</v>
+      </c>
+      <c r="B75" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" t="s">
+        <v>18</v>
+      </c>
+      <c r="D75" t="s">
+        <v>3</v>
+      </c>
+      <c r="E75" t="s">
+        <v>4</v>
+      </c>
+      <c r="F75" t="s">
+        <v>19</v>
+      </c>
+      <c r="G75" t="s">
+        <v>20</v>
+      </c>
+      <c r="H75" s="2">
+        <v>1</v>
+      </c>
+      <c r="I75" t="s">
+        <v>7</v>
+      </c>
+      <c r="J75" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="K75" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="L75" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="M75" t="s">
+        <v>8</v>
+      </c>
+      <c r="N75" s="2">
+        <v>0</v>
+      </c>
+      <c r="O75" s="2">
+        <v>0</v>
+      </c>
+      <c r="P75" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="Q75" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="R75" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="S75" t="s">
+        <v>207</v>
+      </c>
+      <c r="T75" s="5"/>
+      <c r="U75" s="5"/>
+      <c r="V75" t="s">
+        <v>205</v>
+      </c>
+      <c r="W75" t="s">
+        <v>3</v>
+      </c>
+      <c r="X75" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y75" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z75" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA75" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB75" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC75" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD75" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE75" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF75" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG75" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH75" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:34">
+      <c r="A76" t="s">
+        <v>208</v>
+      </c>
+      <c r="B76" t="s">
+        <v>122</v>
+      </c>
+      <c r="C76" t="s">
+        <v>123</v>
+      </c>
+      <c r="D76" t="s">
+        <v>3</v>
+      </c>
+      <c r="E76" t="s">
+        <v>4</v>
+      </c>
+      <c r="F76" t="s">
+        <v>19</v>
+      </c>
+      <c r="G76" t="s">
+        <v>20</v>
+      </c>
+      <c r="H76" s="2">
+        <v>1</v>
+      </c>
+      <c r="I76" t="s">
+        <v>7</v>
+      </c>
+      <c r="J76" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="K76" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="L76" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="M76" t="s">
+        <v>8</v>
+      </c>
+      <c r="N76" s="2">
+        <v>0</v>
+      </c>
+      <c r="O76" s="2">
+        <v>0</v>
+      </c>
+      <c r="P76" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="Q76" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="R76" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="S76" t="s">
+        <v>209</v>
+      </c>
+      <c r="T76" s="5"/>
+      <c r="U76" s="5"/>
+      <c r="V76" t="s">
+        <v>205</v>
+      </c>
+      <c r="W76" t="s">
+        <v>3</v>
+      </c>
+      <c r="X76" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y76" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z76" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA76" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB76" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC76" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD76" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE76" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF76" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG76" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH76" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:34">
+      <c r="A77" t="s">
+        <v>210</v>
+      </c>
+      <c r="B77" t="s">
+        <v>129</v>
+      </c>
+      <c r="C77" t="s">
+        <v>45</v>
+      </c>
+      <c r="D77" t="s">
+        <v>3</v>
+      </c>
+      <c r="E77" t="s">
+        <v>4</v>
+      </c>
+      <c r="F77" t="s">
+        <v>19</v>
+      </c>
+      <c r="G77" t="s">
+        <v>20</v>
+      </c>
+      <c r="H77" s="2">
+        <v>1</v>
+      </c>
+      <c r="I77" t="s">
+        <v>7</v>
+      </c>
+      <c r="J77" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="K77" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="L77" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="M77" t="s">
+        <v>8</v>
+      </c>
+      <c r="N77" s="2">
+        <v>0</v>
+      </c>
+      <c r="O77" s="2">
+        <v>0</v>
+      </c>
+      <c r="P77" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="Q77" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="R77" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="S77" t="s">
+        <v>211</v>
+      </c>
+      <c r="T77" s="5"/>
+      <c r="U77" s="5"/>
+      <c r="V77" t="s">
+        <v>205</v>
+      </c>
+      <c r="W77" t="s">
+        <v>3</v>
+      </c>
+      <c r="X77" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y77" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z77" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA77" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB77" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC77" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD77" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE77" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF77" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG77" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH77" t="s">
         <v>3</v>
       </c>
     </row>

--- a/Newdata/成品報工.XLSX
+++ b/Newdata/成品報工.XLSX
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1782" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1667" uniqueCount="235">
   <si>
     <t>100003496</t>
   </si>
@@ -103,18 +103,12 @@
     <t>1430463</t>
   </si>
   <si>
-    <t>100003543</t>
+    <t>100003544</t>
   </si>
   <si>
     <t>0200</t>
   </si>
   <si>
-    <t>1432135</t>
-  </si>
-  <si>
-    <t>100003544</t>
-  </si>
-  <si>
     <t>1432354</t>
   </si>
   <si>
@@ -520,30 +514,12 @@
     <t>1461381</t>
   </si>
   <si>
-    <t>100003608</t>
-  </si>
-  <si>
-    <t>1461469</t>
-  </si>
-  <si>
-    <t>100003609</t>
-  </si>
-  <si>
-    <t>1461569</t>
-  </si>
-  <si>
     <t>100003610</t>
   </si>
   <si>
     <t>1461670</t>
   </si>
   <si>
-    <t>100003612</t>
-  </si>
-  <si>
-    <t>1463036</t>
-  </si>
-  <si>
     <t>100003614</t>
   </si>
   <si>
@@ -580,12 +556,6 @@
     <t>1469385</t>
   </si>
   <si>
-    <t>100003622</t>
-  </si>
-  <si>
-    <t>1472369</t>
-  </si>
-  <si>
     <t>100003625</t>
   </si>
   <si>
@@ -626,9 +596,6 @@
   </si>
   <si>
     <t>1475227</t>
-  </si>
-  <si>
-    <t>CRTD</t>
   </si>
   <si>
     <t>100003634</t>
@@ -862,7 +829,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AH77"/>
+  <dimension ref="A1:AH72"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="11" customWidth="1"/>
@@ -903,106 +870,106 @@
   <sheetData>
     <row r="1" spans="1:34">
       <c r="A1" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="L1" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="N1" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="O1" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="P1" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="Q1" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="R1" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="S1" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="T1" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="U1" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="V1" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="W1" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="Y1" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="Z1" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="AA1" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="AB1" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="AC1" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>234</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="2" spans="1:34">
@@ -2210,10 +2177,10 @@
         <v>41</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="C14" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="D14" t="s">
         <v>3</v>
@@ -2222,10 +2189,10 @@
         <v>4</v>
       </c>
       <c r="F14" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="G14" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="H14" s="2">
         <v>1</v>
@@ -2234,13 +2201,13 @@
         <v>7</v>
       </c>
       <c r="J14" s="3">
-        <v>1.5</v>
+        <v>1.0</v>
       </c>
       <c r="K14" s="3">
-        <v>1.5</v>
+        <v>1.0</v>
       </c>
       <c r="L14" s="3">
-        <v>1.5</v>
+        <v>1.0</v>
       </c>
       <c r="M14" t="s">
         <v>8</v>
@@ -2261,7 +2228,7 @@
         <v>0.000</v>
       </c>
       <c r="S14" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="T14" s="5"/>
       <c r="U14" s="5"/>
@@ -2307,13 +2274,13 @@
     </row>
     <row r="15" spans="1:34">
       <c r="A15" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C15" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="D15" t="s">
         <v>3</v>
@@ -2322,10 +2289,10 @@
         <v>4</v>
       </c>
       <c r="F15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H15" s="2">
         <v>1</v>
@@ -2334,13 +2301,13 @@
         <v>7</v>
       </c>
       <c r="J15" s="3">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="K15" s="3">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="L15" s="3">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="M15" t="s">
         <v>8</v>
@@ -2361,7 +2328,7 @@
         <v>0.000</v>
       </c>
       <c r="S15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="T15" s="5"/>
       <c r="U15" s="5"/>
@@ -2407,13 +2374,13 @@
     </row>
     <row r="16" spans="1:34">
       <c r="A16" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C16" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="D16" t="s">
         <v>3</v>
@@ -2422,10 +2389,10 @@
         <v>4</v>
       </c>
       <c r="F16" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H16" s="2">
         <v>1</v>
@@ -2434,13 +2401,13 @@
         <v>7</v>
       </c>
       <c r="J16" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="K16" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="L16" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="M16" t="s">
         <v>8</v>
@@ -2461,7 +2428,7 @@
         <v>0.000</v>
       </c>
       <c r="S16" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="T16" s="5"/>
       <c r="U16" s="5"/>
@@ -2507,13 +2474,13 @@
     </row>
     <row r="17" spans="1:34">
       <c r="A17" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C17" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D17" t="s">
         <v>3</v>
@@ -2522,10 +2489,10 @@
         <v>4</v>
       </c>
       <c r="F17" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G17" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H17" s="2">
         <v>1</v>
@@ -2561,7 +2528,7 @@
         <v>0.000</v>
       </c>
       <c r="S17" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T17" s="5"/>
       <c r="U17" s="5"/>
@@ -2607,13 +2574,13 @@
     </row>
     <row r="18" spans="1:34">
       <c r="A18" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D18" t="s">
         <v>3</v>
@@ -2622,10 +2589,10 @@
         <v>4</v>
       </c>
       <c r="F18" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G18" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H18" s="2">
         <v>1</v>
@@ -2661,7 +2628,7 @@
         <v>0.000</v>
       </c>
       <c r="S18" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="T18" s="5"/>
       <c r="U18" s="5"/>
@@ -2707,13 +2674,13 @@
     </row>
     <row r="19" spans="1:34">
       <c r="A19" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B19" t="s">
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D19" t="s">
         <v>3</v>
@@ -2722,10 +2689,10 @@
         <v>4</v>
       </c>
       <c r="F19" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G19" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H19" s="2">
         <v>1</v>
@@ -2761,7 +2728,7 @@
         <v>0.000</v>
       </c>
       <c r="S19" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="T19" s="5"/>
       <c r="U19" s="5"/>
@@ -2807,13 +2774,13 @@
     </row>
     <row r="20" spans="1:34">
       <c r="A20" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B20" t="s">
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D20" t="s">
         <v>3</v>
@@ -2822,10 +2789,10 @@
         <v>4</v>
       </c>
       <c r="F20" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G20" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H20" s="2">
         <v>1</v>
@@ -2861,7 +2828,7 @@
         <v>0.000</v>
       </c>
       <c r="S20" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="T20" s="5"/>
       <c r="U20" s="5"/>
@@ -2907,13 +2874,13 @@
     </row>
     <row r="21" spans="1:34">
       <c r="A21" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B21" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C21" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D21" t="s">
         <v>3</v>
@@ -2922,10 +2889,10 @@
         <v>4</v>
       </c>
       <c r="F21" t="s">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="G21" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="H21" s="2">
         <v>1</v>
@@ -2934,13 +2901,13 @@
         <v>7</v>
       </c>
       <c r="J21" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="K21" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="L21" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="M21" t="s">
         <v>8</v>
@@ -3007,13 +2974,13 @@
     </row>
     <row r="22" spans="1:34">
       <c r="A22" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="B22" t="s">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="C22" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="D22" t="s">
         <v>3</v>
@@ -3022,10 +2989,10 @@
         <v>4</v>
       </c>
       <c r="F22" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="G22" t="s">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="H22" s="2">
         <v>1</v>
@@ -3034,13 +3001,13 @@
         <v>7</v>
       </c>
       <c r="J22" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="K22" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="L22" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="M22" t="s">
         <v>8</v>
@@ -3061,7 +3028,7 @@
         <v>0.000</v>
       </c>
       <c r="S22" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="T22" s="5"/>
       <c r="U22" s="5"/>
@@ -3107,13 +3074,13 @@
     </row>
     <row r="23" spans="1:34">
       <c r="A23" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B23" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C23" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="D23" t="s">
         <v>3</v>
@@ -3122,10 +3089,10 @@
         <v>4</v>
       </c>
       <c r="F23" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G23" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H23" s="2">
         <v>1</v>
@@ -3161,7 +3128,7 @@
         <v>0.000</v>
       </c>
       <c r="S23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="T23" s="5"/>
       <c r="U23" s="5"/>
@@ -3207,13 +3174,13 @@
     </row>
     <row r="24" spans="1:34">
       <c r="A24" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B24" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C24" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D24" t="s">
         <v>3</v>
@@ -3222,10 +3189,10 @@
         <v>4</v>
       </c>
       <c r="F24" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G24" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H24" s="2">
         <v>1</v>
@@ -3261,7 +3228,7 @@
         <v>0.000</v>
       </c>
       <c r="S24" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="T24" s="5"/>
       <c r="U24" s="5"/>
@@ -3307,13 +3274,13 @@
     </row>
     <row r="25" spans="1:34">
       <c r="A25" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B25" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C25" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D25" t="s">
         <v>3</v>
@@ -3322,10 +3289,10 @@
         <v>4</v>
       </c>
       <c r="F25" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G25" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H25" s="2">
         <v>1</v>
@@ -3361,7 +3328,7 @@
         <v>0.000</v>
       </c>
       <c r="S25" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="T25" s="5"/>
       <c r="U25" s="5"/>
@@ -3407,13 +3374,13 @@
     </row>
     <row r="26" spans="1:34">
       <c r="A26" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B26" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C26" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D26" t="s">
         <v>3</v>
@@ -3422,10 +3389,10 @@
         <v>4</v>
       </c>
       <c r="F26" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G26" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H26" s="2">
         <v>1</v>
@@ -3461,7 +3428,7 @@
         <v>0.000</v>
       </c>
       <c r="S26" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="T26" s="5"/>
       <c r="U26" s="5"/>
@@ -3507,13 +3474,13 @@
     </row>
     <row r="27" spans="1:34">
       <c r="A27" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B27" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C27" t="s">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="D27" t="s">
         <v>3</v>
@@ -3522,10 +3489,10 @@
         <v>4</v>
       </c>
       <c r="F27" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G27" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H27" s="2">
         <v>1</v>
@@ -3561,7 +3528,7 @@
         <v>0.000</v>
       </c>
       <c r="S27" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T27" s="5"/>
       <c r="U27" s="5"/>
@@ -3607,13 +3574,13 @@
     </row>
     <row r="28" spans="1:34">
       <c r="A28" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B28" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C28" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="D28" t="s">
         <v>3</v>
@@ -3622,10 +3589,10 @@
         <v>4</v>
       </c>
       <c r="F28" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G28" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H28" s="2">
         <v>1</v>
@@ -3661,7 +3628,7 @@
         <v>0.000</v>
       </c>
       <c r="S28" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="T28" s="5"/>
       <c r="U28" s="5"/>
@@ -3707,13 +3674,13 @@
     </row>
     <row r="29" spans="1:34">
       <c r="A29" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B29" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C29" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D29" t="s">
         <v>3</v>
@@ -3722,10 +3689,10 @@
         <v>4</v>
       </c>
       <c r="F29" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G29" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H29" s="2">
         <v>1</v>
@@ -3761,7 +3728,7 @@
         <v>0.000</v>
       </c>
       <c r="S29" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="T29" s="5"/>
       <c r="U29" s="5"/>
@@ -3807,13 +3774,13 @@
     </row>
     <row r="30" spans="1:34">
       <c r="A30" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B30" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C30" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D30" t="s">
         <v>3</v>
@@ -3822,10 +3789,10 @@
         <v>4</v>
       </c>
       <c r="F30" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G30" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H30" s="2">
         <v>1</v>
@@ -3861,7 +3828,7 @@
         <v>0.000</v>
       </c>
       <c r="S30" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="T30" s="5"/>
       <c r="U30" s="5"/>
@@ -3907,13 +3874,13 @@
     </row>
     <row r="31" spans="1:34">
       <c r="A31" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B31" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C31" t="s">
-        <v>107</v>
+        <v>18</v>
       </c>
       <c r="D31" t="s">
         <v>3</v>
@@ -3922,10 +3889,10 @@
         <v>4</v>
       </c>
       <c r="F31" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G31" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H31" s="2">
         <v>1</v>
@@ -3961,7 +3928,7 @@
         <v>0.000</v>
       </c>
       <c r="S31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T31" s="5"/>
       <c r="U31" s="5"/>
@@ -4007,13 +3974,13 @@
     </row>
     <row r="32" spans="1:34">
       <c r="A32" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B32" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C32" t="s">
-        <v>18</v>
+        <v>112</v>
       </c>
       <c r="D32" t="s">
         <v>3</v>
@@ -4022,10 +3989,10 @@
         <v>4</v>
       </c>
       <c r="F32" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G32" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H32" s="2">
         <v>1</v>
@@ -4034,13 +4001,13 @@
         <v>7</v>
       </c>
       <c r="J32" s="3">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="K32" s="3">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="L32" s="3">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="M32" t="s">
         <v>8</v>
@@ -4061,7 +4028,7 @@
         <v>0.000</v>
       </c>
       <c r="S32" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="T32" s="5"/>
       <c r="U32" s="5"/>
@@ -4107,13 +4074,13 @@
     </row>
     <row r="33" spans="1:34">
       <c r="A33" t="s">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="B33" t="s">
-        <v>76</v>
+        <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D33" t="s">
         <v>3</v>
@@ -4122,10 +4089,10 @@
         <v>4</v>
       </c>
       <c r="F33" t="s">
-        <v>115</v>
+        <v>68</v>
       </c>
       <c r="G33" t="s">
-        <v>116</v>
+        <v>69</v>
       </c>
       <c r="H33" s="2">
         <v>1</v>
@@ -4134,13 +4101,13 @@
         <v>7</v>
       </c>
       <c r="J33" s="3">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="K33" s="3">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="L33" s="3">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="M33" t="s">
         <v>8</v>
@@ -4161,7 +4128,7 @@
         <v>0.000</v>
       </c>
       <c r="S33" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="T33" s="5"/>
       <c r="U33" s="5"/>
@@ -4207,13 +4174,13 @@
     </row>
     <row r="34" spans="1:34">
       <c r="A34" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B34" t="s">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="C34" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D34" t="s">
         <v>3</v>
@@ -4222,10 +4189,10 @@
         <v>4</v>
       </c>
       <c r="F34" t="s">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="G34" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="H34" s="2">
         <v>1</v>
@@ -4234,13 +4201,13 @@
         <v>7</v>
       </c>
       <c r="J34" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="K34" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="L34" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="M34" t="s">
         <v>8</v>
@@ -4261,7 +4228,7 @@
         <v>0.000</v>
       </c>
       <c r="S34" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="T34" s="5"/>
       <c r="U34" s="5"/>
@@ -4307,13 +4274,13 @@
     </row>
     <row r="35" spans="1:34">
       <c r="A35" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B35" t="s">
-        <v>122</v>
+        <v>1</v>
       </c>
       <c r="C35" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D35" t="s">
         <v>3</v>
@@ -4361,7 +4328,7 @@
         <v>0.000</v>
       </c>
       <c r="S35" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="T35" s="5"/>
       <c r="U35" s="5"/>
@@ -4407,13 +4374,13 @@
     </row>
     <row r="36" spans="1:34">
       <c r="A36" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B36" t="s">
-        <v>1</v>
+        <v>127</v>
       </c>
       <c r="C36" t="s">
-        <v>126</v>
+        <v>43</v>
       </c>
       <c r="D36" t="s">
         <v>3</v>
@@ -4461,7 +4428,7 @@
         <v>0.000</v>
       </c>
       <c r="S36" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="T36" s="5"/>
       <c r="U36" s="5"/>
@@ -4507,13 +4474,13 @@
     </row>
     <row r="37" spans="1:34">
       <c r="A37" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B37" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C37" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D37" t="s">
         <v>3</v>
@@ -4610,10 +4577,10 @@
         <v>131</v>
       </c>
       <c r="B38" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C38" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D38" t="s">
         <v>3</v>
@@ -4710,10 +4677,10 @@
         <v>133</v>
       </c>
       <c r="B39" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C39" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D39" t="s">
         <v>3</v>
@@ -4810,10 +4777,10 @@
         <v>135</v>
       </c>
       <c r="B40" t="s">
-        <v>129</v>
+        <v>17</v>
       </c>
       <c r="C40" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="D40" t="s">
         <v>3</v>
@@ -4910,10 +4877,10 @@
         <v>137</v>
       </c>
       <c r="B41" t="s">
-        <v>17</v>
+        <v>120</v>
       </c>
       <c r="C41" t="s">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="D41" t="s">
         <v>3</v>
@@ -5010,10 +4977,10 @@
         <v>139</v>
       </c>
       <c r="B42" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C42" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="D42" t="s">
         <v>3</v>
@@ -5110,10 +5077,10 @@
         <v>141</v>
       </c>
       <c r="B43" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C43" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="D43" t="s">
         <v>3</v>
@@ -5210,10 +5177,10 @@
         <v>143</v>
       </c>
       <c r="B44" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C44" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="D44" t="s">
         <v>3</v>
@@ -5310,10 +5277,10 @@
         <v>145</v>
       </c>
       <c r="B45" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C45" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D45" t="s">
         <v>3</v>
@@ -5410,10 +5377,10 @@
         <v>147</v>
       </c>
       <c r="B46" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C46" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D46" t="s">
         <v>3</v>
@@ -5510,10 +5477,10 @@
         <v>149</v>
       </c>
       <c r="B47" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C47" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D47" t="s">
         <v>3</v>
@@ -5610,10 +5577,10 @@
         <v>151</v>
       </c>
       <c r="B48" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C48" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D48" t="s">
         <v>3</v>
@@ -5710,10 +5677,10 @@
         <v>153</v>
       </c>
       <c r="B49" t="s">
-        <v>129</v>
+        <v>17</v>
       </c>
       <c r="C49" t="s">
-        <v>45</v>
+        <v>105</v>
       </c>
       <c r="D49" t="s">
         <v>3</v>
@@ -5810,10 +5777,10 @@
         <v>155</v>
       </c>
       <c r="B50" t="s">
-        <v>17</v>
+        <v>120</v>
       </c>
       <c r="C50" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="D50" t="s">
         <v>3</v>
@@ -5910,10 +5877,10 @@
         <v>157</v>
       </c>
       <c r="B51" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C51" t="s">
-        <v>123</v>
+        <v>43</v>
       </c>
       <c r="D51" t="s">
         <v>3</v>
@@ -6010,10 +5977,10 @@
         <v>159</v>
       </c>
       <c r="B52" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C52" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D52" t="s">
         <v>3</v>
@@ -6110,10 +6077,10 @@
         <v>161</v>
       </c>
       <c r="B53" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C53" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D53" t="s">
         <v>3</v>
@@ -6210,10 +6177,10 @@
         <v>163</v>
       </c>
       <c r="B54" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C54" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D54" t="s">
         <v>3</v>
@@ -6310,10 +6277,10 @@
         <v>165</v>
       </c>
       <c r="B55" t="s">
-        <v>129</v>
+        <v>17</v>
       </c>
       <c r="C55" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="D55" t="s">
         <v>3</v>
@@ -6410,10 +6377,10 @@
         <v>167</v>
       </c>
       <c r="B56" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="C56" t="s">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="D56" t="s">
         <v>3</v>
@@ -6510,10 +6477,10 @@
         <v>169</v>
       </c>
       <c r="B57" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C57" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D57" t="s">
         <v>3</v>
@@ -6610,10 +6577,10 @@
         <v>171</v>
       </c>
       <c r="B58" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C58" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D58" t="s">
         <v>3</v>
@@ -6710,10 +6677,10 @@
         <v>173</v>
       </c>
       <c r="B59" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C59" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D59" t="s">
         <v>3</v>
@@ -6810,10 +6777,10 @@
         <v>175</v>
       </c>
       <c r="B60" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C60" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D60" t="s">
         <v>3</v>
@@ -6910,10 +6877,10 @@
         <v>177</v>
       </c>
       <c r="B61" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C61" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D61" t="s">
         <v>3</v>
@@ -7010,10 +6977,10 @@
         <v>179</v>
       </c>
       <c r="B62" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C62" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D62" t="s">
         <v>3</v>
@@ -7110,10 +7077,10 @@
         <v>181</v>
       </c>
       <c r="B63" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C63" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D63" t="s">
         <v>3</v>
@@ -7210,10 +7177,10 @@
         <v>183</v>
       </c>
       <c r="B64" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C64" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D64" t="s">
         <v>3</v>
@@ -7310,10 +7277,10 @@
         <v>185</v>
       </c>
       <c r="B65" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C65" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D65" t="s">
         <v>3</v>
@@ -7410,10 +7377,10 @@
         <v>187</v>
       </c>
       <c r="B66" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C66" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D66" t="s">
         <v>3</v>
@@ -7510,10 +7477,10 @@
         <v>189</v>
       </c>
       <c r="B67" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D67" t="s">
         <v>3</v>
@@ -7610,10 +7577,10 @@
         <v>191</v>
       </c>
       <c r="B68" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D68" t="s">
         <v>3</v>
@@ -7710,10 +7677,10 @@
         <v>193</v>
       </c>
       <c r="B69" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C69" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="D69" t="s">
         <v>3</v>
@@ -7810,10 +7777,10 @@
         <v>195</v>
       </c>
       <c r="B70" t="s">
-        <v>129</v>
+        <v>42</v>
       </c>
       <c r="C70" t="s">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="D70" t="s">
         <v>3</v>
@@ -7910,10 +7877,10 @@
         <v>197</v>
       </c>
       <c r="B71" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="C71" t="s">
-        <v>73</v>
+        <v>121</v>
       </c>
       <c r="D71" t="s">
         <v>3</v>
@@ -8010,10 +7977,10 @@
         <v>199</v>
       </c>
       <c r="B72" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C72" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="D72" t="s">
         <v>3</v>
@@ -8102,506 +8069,6 @@
         <v>3</v>
       </c>
       <c r="AH72" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="1:34">
-      <c r="A73" t="s">
-        <v>201</v>
-      </c>
-      <c r="B73" t="s">
-        <v>129</v>
-      </c>
-      <c r="C73" t="s">
-        <v>73</v>
-      </c>
-      <c r="D73" t="s">
-        <v>3</v>
-      </c>
-      <c r="E73" t="s">
-        <v>4</v>
-      </c>
-      <c r="F73" t="s">
-        <v>19</v>
-      </c>
-      <c r="G73" t="s">
-        <v>20</v>
-      </c>
-      <c r="H73" s="2">
-        <v>1</v>
-      </c>
-      <c r="I73" t="s">
-        <v>7</v>
-      </c>
-      <c r="J73" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="K73" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="L73" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="M73" t="s">
-        <v>8</v>
-      </c>
-      <c r="N73" s="2">
-        <v>0</v>
-      </c>
-      <c r="O73" s="2">
-        <v>0</v>
-      </c>
-      <c r="P73" s="4">
-        <v>0.000</v>
-      </c>
-      <c r="Q73" s="4">
-        <v>0.000</v>
-      </c>
-      <c r="R73" s="4">
-        <v>0.000</v>
-      </c>
-      <c r="S73" t="s">
-        <v>202</v>
-      </c>
-      <c r="T73" s="5"/>
-      <c r="U73" s="5"/>
-      <c r="V73" t="s">
-        <v>10</v>
-      </c>
-      <c r="W73" t="s">
-        <v>3</v>
-      </c>
-      <c r="X73" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y73" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z73" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA73" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB73" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC73" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD73" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE73" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF73" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG73" t="s">
-        <v>3</v>
-      </c>
-      <c r="AH73" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="74" spans="1:34">
-      <c r="A74" t="s">
-        <v>203</v>
-      </c>
-      <c r="B74" t="s">
-        <v>129</v>
-      </c>
-      <c r="C74" t="s">
-        <v>45</v>
-      </c>
-      <c r="D74" t="s">
-        <v>3</v>
-      </c>
-      <c r="E74" t="s">
-        <v>4</v>
-      </c>
-      <c r="F74" t="s">
-        <v>19</v>
-      </c>
-      <c r="G74" t="s">
-        <v>20</v>
-      </c>
-      <c r="H74" s="2">
-        <v>1</v>
-      </c>
-      <c r="I74" t="s">
-        <v>7</v>
-      </c>
-      <c r="J74" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="K74" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="L74" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="M74" t="s">
-        <v>8</v>
-      </c>
-      <c r="N74" s="2">
-        <v>0</v>
-      </c>
-      <c r="O74" s="2">
-        <v>0</v>
-      </c>
-      <c r="P74" s="4">
-        <v>0.000</v>
-      </c>
-      <c r="Q74" s="4">
-        <v>0.000</v>
-      </c>
-      <c r="R74" s="4">
-        <v>0.000</v>
-      </c>
-      <c r="S74" t="s">
-        <v>204</v>
-      </c>
-      <c r="T74" s="5"/>
-      <c r="U74" s="5"/>
-      <c r="V74" t="s">
-        <v>205</v>
-      </c>
-      <c r="W74" t="s">
-        <v>3</v>
-      </c>
-      <c r="X74" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z74" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA74" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB74" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC74" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD74" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE74" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF74" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG74" t="s">
-        <v>3</v>
-      </c>
-      <c r="AH74" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="75" spans="1:34">
-      <c r="A75" t="s">
-        <v>206</v>
-      </c>
-      <c r="B75" t="s">
-        <v>44</v>
-      </c>
-      <c r="C75" t="s">
-        <v>18</v>
-      </c>
-      <c r="D75" t="s">
-        <v>3</v>
-      </c>
-      <c r="E75" t="s">
-        <v>4</v>
-      </c>
-      <c r="F75" t="s">
-        <v>19</v>
-      </c>
-      <c r="G75" t="s">
-        <v>20</v>
-      </c>
-      <c r="H75" s="2">
-        <v>1</v>
-      </c>
-      <c r="I75" t="s">
-        <v>7</v>
-      </c>
-      <c r="J75" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="K75" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="L75" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="M75" t="s">
-        <v>8</v>
-      </c>
-      <c r="N75" s="2">
-        <v>0</v>
-      </c>
-      <c r="O75" s="2">
-        <v>0</v>
-      </c>
-      <c r="P75" s="4">
-        <v>0.000</v>
-      </c>
-      <c r="Q75" s="4">
-        <v>0.000</v>
-      </c>
-      <c r="R75" s="4">
-        <v>0.000</v>
-      </c>
-      <c r="S75" t="s">
-        <v>207</v>
-      </c>
-      <c r="T75" s="5"/>
-      <c r="U75" s="5"/>
-      <c r="V75" t="s">
-        <v>205</v>
-      </c>
-      <c r="W75" t="s">
-        <v>3</v>
-      </c>
-      <c r="X75" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y75" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z75" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA75" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB75" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC75" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD75" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE75" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF75" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG75" t="s">
-        <v>3</v>
-      </c>
-      <c r="AH75" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="76" spans="1:34">
-      <c r="A76" t="s">
-        <v>208</v>
-      </c>
-      <c r="B76" t="s">
-        <v>122</v>
-      </c>
-      <c r="C76" t="s">
-        <v>123</v>
-      </c>
-      <c r="D76" t="s">
-        <v>3</v>
-      </c>
-      <c r="E76" t="s">
-        <v>4</v>
-      </c>
-      <c r="F76" t="s">
-        <v>19</v>
-      </c>
-      <c r="G76" t="s">
-        <v>20</v>
-      </c>
-      <c r="H76" s="2">
-        <v>1</v>
-      </c>
-      <c r="I76" t="s">
-        <v>7</v>
-      </c>
-      <c r="J76" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="K76" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="L76" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="M76" t="s">
-        <v>8</v>
-      </c>
-      <c r="N76" s="2">
-        <v>0</v>
-      </c>
-      <c r="O76" s="2">
-        <v>0</v>
-      </c>
-      <c r="P76" s="4">
-        <v>0.000</v>
-      </c>
-      <c r="Q76" s="4">
-        <v>0.000</v>
-      </c>
-      <c r="R76" s="4">
-        <v>0.000</v>
-      </c>
-      <c r="S76" t="s">
-        <v>209</v>
-      </c>
-      <c r="T76" s="5"/>
-      <c r="U76" s="5"/>
-      <c r="V76" t="s">
-        <v>205</v>
-      </c>
-      <c r="W76" t="s">
-        <v>3</v>
-      </c>
-      <c r="X76" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y76" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z76" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA76" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB76" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC76" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD76" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE76" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF76" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG76" t="s">
-        <v>3</v>
-      </c>
-      <c r="AH76" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="1:34">
-      <c r="A77" t="s">
-        <v>210</v>
-      </c>
-      <c r="B77" t="s">
-        <v>129</v>
-      </c>
-      <c r="C77" t="s">
-        <v>45</v>
-      </c>
-      <c r="D77" t="s">
-        <v>3</v>
-      </c>
-      <c r="E77" t="s">
-        <v>4</v>
-      </c>
-      <c r="F77" t="s">
-        <v>19</v>
-      </c>
-      <c r="G77" t="s">
-        <v>20</v>
-      </c>
-      <c r="H77" s="2">
-        <v>1</v>
-      </c>
-      <c r="I77" t="s">
-        <v>7</v>
-      </c>
-      <c r="J77" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="K77" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="L77" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="M77" t="s">
-        <v>8</v>
-      </c>
-      <c r="N77" s="2">
-        <v>0</v>
-      </c>
-      <c r="O77" s="2">
-        <v>0</v>
-      </c>
-      <c r="P77" s="4">
-        <v>0.000</v>
-      </c>
-      <c r="Q77" s="4">
-        <v>0.000</v>
-      </c>
-      <c r="R77" s="4">
-        <v>0.000</v>
-      </c>
-      <c r="S77" t="s">
-        <v>211</v>
-      </c>
-      <c r="T77" s="5"/>
-      <c r="U77" s="5"/>
-      <c r="V77" t="s">
-        <v>205</v>
-      </c>
-      <c r="W77" t="s">
-        <v>3</v>
-      </c>
-      <c r="X77" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y77" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z77" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA77" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB77" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC77" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD77" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE77" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF77" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG77" t="s">
-        <v>3</v>
-      </c>
-      <c r="AH77" t="s">
         <v>3</v>
       </c>
     </row>

--- a/Newdata/成品報工.XLSX
+++ b/Newdata/成品報工.XLSX
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1667" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1874" uniqueCount="247">
   <si>
     <t>100003496</t>
   </si>
@@ -103,18 +103,12 @@
     <t>1430463</t>
   </si>
   <si>
-    <t>100003544</t>
+    <t>100003545</t>
   </si>
   <si>
     <t>0200</t>
   </si>
   <si>
-    <t>1432354</t>
-  </si>
-  <si>
-    <t>100003545</t>
-  </si>
-  <si>
     <t>1432573</t>
   </si>
   <si>
@@ -484,18 +478,6 @@
     <t>1458428</t>
   </si>
   <si>
-    <t>100003602</t>
-  </si>
-  <si>
-    <t>1458741</t>
-  </si>
-  <si>
-    <t>100003603</t>
-  </si>
-  <si>
-    <t>1458945</t>
-  </si>
-  <si>
     <t>100003604</t>
   </si>
   <si>
@@ -613,7 +595,61 @@
     <t>100003636</t>
   </si>
   <si>
-    <t>1476212</t>
+    <t>1476710</t>
+  </si>
+  <si>
+    <t>100003638</t>
+  </si>
+  <si>
+    <t>1477373</t>
+  </si>
+  <si>
+    <t>1477374</t>
+  </si>
+  <si>
+    <t>1477375</t>
+  </si>
+  <si>
+    <t>1477376</t>
+  </si>
+  <si>
+    <t>100003640</t>
+  </si>
+  <si>
+    <t>1479909</t>
+  </si>
+  <si>
+    <t>1479910</t>
+  </si>
+  <si>
+    <t>1479911</t>
+  </si>
+  <si>
+    <t>1479912</t>
+  </si>
+  <si>
+    <t>100003641</t>
+  </si>
+  <si>
+    <t>1481312</t>
+  </si>
+  <si>
+    <t>100003642</t>
+  </si>
+  <si>
+    <t>1481417</t>
+  </si>
+  <si>
+    <t>100003643</t>
+  </si>
+  <si>
+    <t>1481517</t>
+  </si>
+  <si>
+    <t>100003644</t>
+  </si>
+  <si>
+    <t>1481621</t>
   </si>
   <si>
     <t>訂單</t>
@@ -829,7 +865,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AH72"/>
+  <dimension ref="A1:AH81"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="11" customWidth="1"/>
@@ -870,106 +906,106 @@
   <sheetData>
     <row r="1" spans="1:34">
       <c r="A1" s="1" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="Q1" s="6" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="R1" s="6" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
     </row>
     <row r="2" spans="1:34">
@@ -2077,10 +2113,10 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="D13" t="s">
         <v>3</v>
@@ -2089,10 +2125,10 @@
         <v>4</v>
       </c>
       <c r="F13" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="G13" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="H13" s="2">
         <v>1</v>
@@ -2101,13 +2137,13 @@
         <v>7</v>
       </c>
       <c r="J13" s="3">
-        <v>1.5</v>
+        <v>1.0</v>
       </c>
       <c r="K13" s="3">
-        <v>1.5</v>
+        <v>1.0</v>
       </c>
       <c r="L13" s="3">
-        <v>1.5</v>
+        <v>1.0</v>
       </c>
       <c r="M13" t="s">
         <v>8</v>
@@ -2128,7 +2164,7 @@
         <v>0.000</v>
       </c>
       <c r="S13" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="T13" s="5"/>
       <c r="U13" s="5"/>
@@ -2174,13 +2210,13 @@
     </row>
     <row r="14" spans="1:34">
       <c r="A14" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C14" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D14" t="s">
         <v>3</v>
@@ -2189,10 +2225,10 @@
         <v>4</v>
       </c>
       <c r="F14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H14" s="2">
         <v>1</v>
@@ -2201,13 +2237,13 @@
         <v>7</v>
       </c>
       <c r="J14" s="3">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="K14" s="3">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="L14" s="3">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="M14" t="s">
         <v>8</v>
@@ -2228,7 +2264,7 @@
         <v>0.000</v>
       </c>
       <c r="S14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T14" s="5"/>
       <c r="U14" s="5"/>
@@ -2274,13 +2310,13 @@
     </row>
     <row r="15" spans="1:34">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C15" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="D15" t="s">
         <v>3</v>
@@ -2289,10 +2325,10 @@
         <v>4</v>
       </c>
       <c r="F15" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G15" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H15" s="2">
         <v>1</v>
@@ -2301,13 +2337,13 @@
         <v>7</v>
       </c>
       <c r="J15" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="K15" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="L15" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="M15" t="s">
         <v>8</v>
@@ -2328,7 +2364,7 @@
         <v>0.000</v>
       </c>
       <c r="S15" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="T15" s="5"/>
       <c r="U15" s="5"/>
@@ -2374,13 +2410,13 @@
     </row>
     <row r="16" spans="1:34">
       <c r="A16" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D16" t="s">
         <v>3</v>
@@ -2389,10 +2425,10 @@
         <v>4</v>
       </c>
       <c r="F16" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H16" s="2">
         <v>1</v>
@@ -2428,7 +2464,7 @@
         <v>0.000</v>
       </c>
       <c r="S16" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T16" s="5"/>
       <c r="U16" s="5"/>
@@ -2474,13 +2510,13 @@
     </row>
     <row r="17" spans="1:34">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="B17" t="s">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D17" t="s">
         <v>3</v>
@@ -2489,10 +2525,10 @@
         <v>4</v>
       </c>
       <c r="F17" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G17" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H17" s="2">
         <v>1</v>
@@ -2528,7 +2564,7 @@
         <v>0.000</v>
       </c>
       <c r="S17" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="T17" s="5"/>
       <c r="U17" s="5"/>
@@ -2574,13 +2610,13 @@
     </row>
     <row r="18" spans="1:34">
       <c r="A18" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B18" t="s">
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D18" t="s">
         <v>3</v>
@@ -2589,10 +2625,10 @@
         <v>4</v>
       </c>
       <c r="F18" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G18" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H18" s="2">
         <v>1</v>
@@ -2628,7 +2664,7 @@
         <v>0.000</v>
       </c>
       <c r="S18" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="T18" s="5"/>
       <c r="U18" s="5"/>
@@ -2674,13 +2710,13 @@
     </row>
     <row r="19" spans="1:34">
       <c r="A19" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B19" t="s">
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D19" t="s">
         <v>3</v>
@@ -2689,10 +2725,10 @@
         <v>4</v>
       </c>
       <c r="F19" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G19" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H19" s="2">
         <v>1</v>
@@ -2728,7 +2764,7 @@
         <v>0.000</v>
       </c>
       <c r="S19" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="T19" s="5"/>
       <c r="U19" s="5"/>
@@ -2774,13 +2810,13 @@
     </row>
     <row r="20" spans="1:34">
       <c r="A20" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B20" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C20" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D20" t="s">
         <v>3</v>
@@ -2789,10 +2825,10 @@
         <v>4</v>
       </c>
       <c r="F20" t="s">
-        <v>68</v>
+        <v>19</v>
       </c>
       <c r="G20" t="s">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="H20" s="2">
         <v>1</v>
@@ -2801,13 +2837,13 @@
         <v>7</v>
       </c>
       <c r="J20" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="K20" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="L20" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="M20" t="s">
         <v>8</v>
@@ -2874,13 +2910,13 @@
     </row>
     <row r="21" spans="1:34">
       <c r="A21" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="B21" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="C21" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="D21" t="s">
         <v>3</v>
@@ -2889,10 +2925,10 @@
         <v>4</v>
       </c>
       <c r="F21" t="s">
-        <v>19</v>
+        <v>73</v>
       </c>
       <c r="G21" t="s">
-        <v>20</v>
+        <v>74</v>
       </c>
       <c r="H21" s="2">
         <v>1</v>
@@ -2901,13 +2937,13 @@
         <v>7</v>
       </c>
       <c r="J21" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="K21" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="L21" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="M21" t="s">
         <v>8</v>
@@ -2928,7 +2964,7 @@
         <v>0.000</v>
       </c>
       <c r="S21" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="T21" s="5"/>
       <c r="U21" s="5"/>
@@ -2974,13 +3010,13 @@
     </row>
     <row r="22" spans="1:34">
       <c r="A22" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B22" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C22" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="D22" t="s">
         <v>3</v>
@@ -2989,10 +3025,10 @@
         <v>4</v>
       </c>
       <c r="F22" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G22" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H22" s="2">
         <v>1</v>
@@ -3028,7 +3064,7 @@
         <v>0.000</v>
       </c>
       <c r="S22" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="T22" s="5"/>
       <c r="U22" s="5"/>
@@ -3074,13 +3110,13 @@
     </row>
     <row r="23" spans="1:34">
       <c r="A23" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B23" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C23" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D23" t="s">
         <v>3</v>
@@ -3089,10 +3125,10 @@
         <v>4</v>
       </c>
       <c r="F23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G23" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H23" s="2">
         <v>1</v>
@@ -3128,7 +3164,7 @@
         <v>0.000</v>
       </c>
       <c r="S23" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="T23" s="5"/>
       <c r="U23" s="5"/>
@@ -3174,13 +3210,13 @@
     </row>
     <row r="24" spans="1:34">
       <c r="A24" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B24" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C24" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D24" t="s">
         <v>3</v>
@@ -3189,10 +3225,10 @@
         <v>4</v>
       </c>
       <c r="F24" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G24" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H24" s="2">
         <v>1</v>
@@ -3228,7 +3264,7 @@
         <v>0.000</v>
       </c>
       <c r="S24" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="T24" s="5"/>
       <c r="U24" s="5"/>
@@ -3274,13 +3310,13 @@
     </row>
     <row r="25" spans="1:34">
       <c r="A25" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B25" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C25" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D25" t="s">
         <v>3</v>
@@ -3289,10 +3325,10 @@
         <v>4</v>
       </c>
       <c r="F25" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G25" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H25" s="2">
         <v>1</v>
@@ -3328,7 +3364,7 @@
         <v>0.000</v>
       </c>
       <c r="S25" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="T25" s="5"/>
       <c r="U25" s="5"/>
@@ -3374,13 +3410,13 @@
     </row>
     <row r="26" spans="1:34">
       <c r="A26" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B26" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C26" t="s">
-        <v>90</v>
+        <v>57</v>
       </c>
       <c r="D26" t="s">
         <v>3</v>
@@ -3389,10 +3425,10 @@
         <v>4</v>
       </c>
       <c r="F26" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G26" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H26" s="2">
         <v>1</v>
@@ -3428,7 +3464,7 @@
         <v>0.000</v>
       </c>
       <c r="S26" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="T26" s="5"/>
       <c r="U26" s="5"/>
@@ -3474,13 +3510,13 @@
     </row>
     <row r="27" spans="1:34">
       <c r="A27" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B27" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C27" t="s">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="D27" t="s">
         <v>3</v>
@@ -3489,10 +3525,10 @@
         <v>4</v>
       </c>
       <c r="F27" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G27" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H27" s="2">
         <v>1</v>
@@ -3528,7 +3564,7 @@
         <v>0.000</v>
       </c>
       <c r="S27" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="T27" s="5"/>
       <c r="U27" s="5"/>
@@ -3574,13 +3610,13 @@
     </row>
     <row r="28" spans="1:34">
       <c r="A28" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B28" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C28" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D28" t="s">
         <v>3</v>
@@ -3589,10 +3625,10 @@
         <v>4</v>
       </c>
       <c r="F28" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G28" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H28" s="2">
         <v>1</v>
@@ -3628,7 +3664,7 @@
         <v>0.000</v>
       </c>
       <c r="S28" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="T28" s="5"/>
       <c r="U28" s="5"/>
@@ -3674,13 +3710,13 @@
     </row>
     <row r="29" spans="1:34">
       <c r="A29" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B29" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C29" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D29" t="s">
         <v>3</v>
@@ -3689,10 +3725,10 @@
         <v>4</v>
       </c>
       <c r="F29" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G29" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H29" s="2">
         <v>1</v>
@@ -3728,7 +3764,7 @@
         <v>0.000</v>
       </c>
       <c r="S29" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="T29" s="5"/>
       <c r="U29" s="5"/>
@@ -3774,13 +3810,13 @@
     </row>
     <row r="30" spans="1:34">
       <c r="A30" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B30" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C30" t="s">
-        <v>105</v>
+        <v>18</v>
       </c>
       <c r="D30" t="s">
         <v>3</v>
@@ -3789,10 +3825,10 @@
         <v>4</v>
       </c>
       <c r="F30" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G30" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H30" s="2">
         <v>1</v>
@@ -3828,7 +3864,7 @@
         <v>0.000</v>
       </c>
       <c r="S30" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="T30" s="5"/>
       <c r="U30" s="5"/>
@@ -3874,13 +3910,13 @@
     </row>
     <row r="31" spans="1:34">
       <c r="A31" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B31" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C31" t="s">
-        <v>18</v>
+        <v>110</v>
       </c>
       <c r="D31" t="s">
         <v>3</v>
@@ -3889,10 +3925,10 @@
         <v>4</v>
       </c>
       <c r="F31" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G31" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H31" s="2">
         <v>1</v>
@@ -3901,13 +3937,13 @@
         <v>7</v>
       </c>
       <c r="J31" s="3">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="K31" s="3">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="L31" s="3">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="M31" t="s">
         <v>8</v>
@@ -3928,7 +3964,7 @@
         <v>0.000</v>
       </c>
       <c r="S31" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="T31" s="5"/>
       <c r="U31" s="5"/>
@@ -3974,13 +4010,13 @@
     </row>
     <row r="32" spans="1:34">
       <c r="A32" t="s">
-        <v>73</v>
+        <v>114</v>
       </c>
       <c r="B32" t="s">
-        <v>74</v>
+        <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D32" t="s">
         <v>3</v>
@@ -3989,10 +4025,10 @@
         <v>4</v>
       </c>
       <c r="F32" t="s">
-        <v>113</v>
+        <v>66</v>
       </c>
       <c r="G32" t="s">
-        <v>114</v>
+        <v>67</v>
       </c>
       <c r="H32" s="2">
         <v>1</v>
@@ -4001,13 +4037,13 @@
         <v>7</v>
       </c>
       <c r="J32" s="3">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="K32" s="3">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="L32" s="3">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="M32" t="s">
         <v>8</v>
@@ -4028,7 +4064,7 @@
         <v>0.000</v>
       </c>
       <c r="S32" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="T32" s="5"/>
       <c r="U32" s="5"/>
@@ -4074,13 +4110,13 @@
     </row>
     <row r="33" spans="1:34">
       <c r="A33" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B33" t="s">
-        <v>1</v>
+        <v>118</v>
       </c>
       <c r="C33" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D33" t="s">
         <v>3</v>
@@ -4089,10 +4125,10 @@
         <v>4</v>
       </c>
       <c r="F33" t="s">
-        <v>68</v>
+        <v>19</v>
       </c>
       <c r="G33" t="s">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="H33" s="2">
         <v>1</v>
@@ -4101,13 +4137,13 @@
         <v>7</v>
       </c>
       <c r="J33" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="K33" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="L33" s="3">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="M33" t="s">
         <v>8</v>
@@ -4128,7 +4164,7 @@
         <v>0.000</v>
       </c>
       <c r="S33" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="T33" s="5"/>
       <c r="U33" s="5"/>
@@ -4174,13 +4210,13 @@
     </row>
     <row r="34" spans="1:34">
       <c r="A34" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B34" t="s">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D34" t="s">
         <v>3</v>
@@ -4228,7 +4264,7 @@
         <v>0.000</v>
       </c>
       <c r="S34" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="T34" s="5"/>
       <c r="U34" s="5"/>
@@ -4274,13 +4310,13 @@
     </row>
     <row r="35" spans="1:34">
       <c r="A35" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B35" t="s">
-        <v>1</v>
+        <v>125</v>
       </c>
       <c r="C35" t="s">
-        <v>124</v>
+        <v>41</v>
       </c>
       <c r="D35" t="s">
         <v>3</v>
@@ -4328,7 +4364,7 @@
         <v>0.000</v>
       </c>
       <c r="S35" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="T35" s="5"/>
       <c r="U35" s="5"/>
@@ -4374,13 +4410,13 @@
     </row>
     <row r="36" spans="1:34">
       <c r="A36" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B36" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C36" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D36" t="s">
         <v>3</v>
@@ -4477,10 +4513,10 @@
         <v>129</v>
       </c>
       <c r="B37" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C37" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D37" t="s">
         <v>3</v>
@@ -4577,10 +4613,10 @@
         <v>131</v>
       </c>
       <c r="B38" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C38" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D38" t="s">
         <v>3</v>
@@ -4677,10 +4713,10 @@
         <v>133</v>
       </c>
       <c r="B39" t="s">
-        <v>127</v>
+        <v>17</v>
       </c>
       <c r="C39" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="D39" t="s">
         <v>3</v>
@@ -4777,10 +4813,10 @@
         <v>135</v>
       </c>
       <c r="B40" t="s">
-        <v>17</v>
+        <v>118</v>
       </c>
       <c r="C40" t="s">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="D40" t="s">
         <v>3</v>
@@ -4877,10 +4913,10 @@
         <v>137</v>
       </c>
       <c r="B41" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C41" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="D41" t="s">
         <v>3</v>
@@ -4977,10 +5013,10 @@
         <v>139</v>
       </c>
       <c r="B42" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C42" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="D42" t="s">
         <v>3</v>
@@ -5077,10 +5113,10 @@
         <v>141</v>
       </c>
       <c r="B43" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C43" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="D43" t="s">
         <v>3</v>
@@ -5177,10 +5213,10 @@
         <v>143</v>
       </c>
       <c r="B44" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C44" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D44" t="s">
         <v>3</v>
@@ -5277,10 +5313,10 @@
         <v>145</v>
       </c>
       <c r="B45" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C45" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D45" t="s">
         <v>3</v>
@@ -5377,10 +5413,10 @@
         <v>147</v>
       </c>
       <c r="B46" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C46" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D46" t="s">
         <v>3</v>
@@ -5477,10 +5513,10 @@
         <v>149</v>
       </c>
       <c r="B47" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C47" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D47" t="s">
         <v>3</v>
@@ -5577,10 +5613,10 @@
         <v>151</v>
       </c>
       <c r="B48" t="s">
-        <v>127</v>
+        <v>17</v>
       </c>
       <c r="C48" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="D48" t="s">
         <v>3</v>
@@ -5677,10 +5713,10 @@
         <v>153</v>
       </c>
       <c r="B49" t="s">
-        <v>17</v>
+        <v>118</v>
       </c>
       <c r="C49" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="D49" t="s">
         <v>3</v>
@@ -5777,10 +5813,10 @@
         <v>155</v>
       </c>
       <c r="B50" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C50" t="s">
-        <v>121</v>
+        <v>41</v>
       </c>
       <c r="D50" t="s">
         <v>3</v>
@@ -5877,10 +5913,10 @@
         <v>157</v>
       </c>
       <c r="B51" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C51" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D51" t="s">
         <v>3</v>
@@ -5977,10 +6013,10 @@
         <v>159</v>
       </c>
       <c r="B52" t="s">
-        <v>127</v>
+        <v>17</v>
       </c>
       <c r="C52" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="D52" t="s">
         <v>3</v>
@@ -6077,10 +6113,10 @@
         <v>161</v>
       </c>
       <c r="B53" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C53" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="D53" t="s">
         <v>3</v>
@@ -6177,10 +6213,10 @@
         <v>163</v>
       </c>
       <c r="B54" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C54" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="D54" t="s">
         <v>3</v>
@@ -6277,10 +6313,10 @@
         <v>165</v>
       </c>
       <c r="B55" t="s">
-        <v>17</v>
+        <v>125</v>
       </c>
       <c r="C55" t="s">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="D55" t="s">
         <v>3</v>
@@ -6377,10 +6413,10 @@
         <v>167</v>
       </c>
       <c r="B56" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C56" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D56" t="s">
         <v>3</v>
@@ -6477,10 +6513,10 @@
         <v>169</v>
       </c>
       <c r="B57" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C57" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D57" t="s">
         <v>3</v>
@@ -6577,10 +6613,10 @@
         <v>171</v>
       </c>
       <c r="B58" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C58" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D58" t="s">
         <v>3</v>
@@ -6677,10 +6713,10 @@
         <v>173</v>
       </c>
       <c r="B59" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C59" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D59" t="s">
         <v>3</v>
@@ -6777,10 +6813,10 @@
         <v>175</v>
       </c>
       <c r="B60" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C60" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D60" t="s">
         <v>3</v>
@@ -6877,10 +6913,10 @@
         <v>177</v>
       </c>
       <c r="B61" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C61" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D61" t="s">
         <v>3</v>
@@ -6977,10 +7013,10 @@
         <v>179</v>
       </c>
       <c r="B62" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C62" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D62" t="s">
         <v>3</v>
@@ -7077,10 +7113,10 @@
         <v>181</v>
       </c>
       <c r="B63" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C63" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D63" t="s">
         <v>3</v>
@@ -7177,10 +7213,10 @@
         <v>183</v>
       </c>
       <c r="B64" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C64" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D64" t="s">
         <v>3</v>
@@ -7277,10 +7313,10 @@
         <v>185</v>
       </c>
       <c r="B65" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C65" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D65" t="s">
         <v>3</v>
@@ -7377,10 +7413,10 @@
         <v>187</v>
       </c>
       <c r="B66" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C66" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="D66" t="s">
         <v>3</v>
@@ -7477,10 +7513,10 @@
         <v>189</v>
       </c>
       <c r="B67" t="s">
-        <v>127</v>
+        <v>40</v>
       </c>
       <c r="C67" t="s">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="D67" t="s">
         <v>3</v>
@@ -7577,10 +7613,10 @@
         <v>191</v>
       </c>
       <c r="B68" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="C68" t="s">
-        <v>71</v>
+        <v>119</v>
       </c>
       <c r="D68" t="s">
         <v>3</v>
@@ -7677,10 +7713,10 @@
         <v>193</v>
       </c>
       <c r="B69" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C69" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D69" t="s">
         <v>3</v>
@@ -7777,10 +7813,10 @@
         <v>195</v>
       </c>
       <c r="B70" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C70" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D70" t="s">
         <v>3</v>
@@ -7789,10 +7825,10 @@
         <v>4</v>
       </c>
       <c r="F70" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="G70" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="H70" s="2">
         <v>1</v>
@@ -7801,13 +7837,13 @@
         <v>7</v>
       </c>
       <c r="J70" s="3">
-        <v>1.5</v>
+        <v>1.0</v>
       </c>
       <c r="K70" s="3">
-        <v>1.5</v>
+        <v>1.0</v>
       </c>
       <c r="L70" s="3">
-        <v>1.5</v>
+        <v>1.0</v>
       </c>
       <c r="M70" t="s">
         <v>8</v>
@@ -7874,13 +7910,13 @@
     </row>
     <row r="71" spans="1:34">
       <c r="A71" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B71" t="s">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="C71" t="s">
-        <v>121</v>
+        <v>48</v>
       </c>
       <c r="D71" t="s">
         <v>3</v>
@@ -7889,10 +7925,10 @@
         <v>4</v>
       </c>
       <c r="F71" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="G71" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H71" s="2">
         <v>1</v>
@@ -7901,13 +7937,13 @@
         <v>7</v>
       </c>
       <c r="J71" s="3">
-        <v>1.5</v>
+        <v>3.0</v>
       </c>
       <c r="K71" s="3">
-        <v>1.5</v>
+        <v>3.0</v>
       </c>
       <c r="L71" s="3">
-        <v>1.5</v>
+        <v>3.0</v>
       </c>
       <c r="M71" t="s">
         <v>8</v>
@@ -7928,7 +7964,7 @@
         <v>0.000</v>
       </c>
       <c r="S71" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="T71" s="5"/>
       <c r="U71" s="5"/>
@@ -7974,13 +8010,13 @@
     </row>
     <row r="72" spans="1:34">
       <c r="A72" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B72" t="s">
-        <v>127</v>
+        <v>40</v>
       </c>
       <c r="C72" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="D72" t="s">
         <v>3</v>
@@ -7989,10 +8025,10 @@
         <v>4</v>
       </c>
       <c r="F72" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="G72" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H72" s="2">
         <v>1</v>
@@ -8001,13 +8037,13 @@
         <v>7</v>
       </c>
       <c r="J72" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="K72" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="L72" s="3">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="M72" t="s">
         <v>8</v>
@@ -8028,7 +8064,7 @@
         <v>0.000</v>
       </c>
       <c r="S72" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="T72" s="5"/>
       <c r="U72" s="5"/>
@@ -8069,6 +8105,906 @@
         <v>3</v>
       </c>
       <c r="AH72" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:34">
+      <c r="A73" t="s">
+        <v>195</v>
+      </c>
+      <c r="B73" t="s">
+        <v>40</v>
+      </c>
+      <c r="C73" t="s">
+        <v>76</v>
+      </c>
+      <c r="D73" t="s">
+        <v>3</v>
+      </c>
+      <c r="E73" t="s">
+        <v>4</v>
+      </c>
+      <c r="F73" t="s">
+        <v>53</v>
+      </c>
+      <c r="G73" t="s">
+        <v>54</v>
+      </c>
+      <c r="H73" s="2">
+        <v>1</v>
+      </c>
+      <c r="I73" t="s">
+        <v>7</v>
+      </c>
+      <c r="J73" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="K73" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L73" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="M73" t="s">
+        <v>8</v>
+      </c>
+      <c r="N73" s="2">
+        <v>0</v>
+      </c>
+      <c r="O73" s="2">
+        <v>0</v>
+      </c>
+      <c r="P73" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="Q73" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="R73" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="S73" t="s">
+        <v>199</v>
+      </c>
+      <c r="T73" s="5"/>
+      <c r="U73" s="5"/>
+      <c r="V73" t="s">
+        <v>10</v>
+      </c>
+      <c r="W73" t="s">
+        <v>3</v>
+      </c>
+      <c r="X73" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y73" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z73" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA73" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB73" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC73" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD73" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE73" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF73" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG73" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH73" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:34">
+      <c r="A74" t="s">
+        <v>200</v>
+      </c>
+      <c r="B74" t="s">
+        <v>40</v>
+      </c>
+      <c r="C74" t="s">
+        <v>31</v>
+      </c>
+      <c r="D74" t="s">
+        <v>3</v>
+      </c>
+      <c r="E74" t="s">
+        <v>4</v>
+      </c>
+      <c r="F74" t="s">
+        <v>42</v>
+      </c>
+      <c r="G74" t="s">
+        <v>43</v>
+      </c>
+      <c r="H74" s="2">
+        <v>1</v>
+      </c>
+      <c r="I74" t="s">
+        <v>7</v>
+      </c>
+      <c r="J74" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="K74" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="L74" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="M74" t="s">
+        <v>8</v>
+      </c>
+      <c r="N74" s="2">
+        <v>0</v>
+      </c>
+      <c r="O74" s="2">
+        <v>0</v>
+      </c>
+      <c r="P74" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="Q74" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="R74" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="S74" t="s">
+        <v>201</v>
+      </c>
+      <c r="T74" s="5"/>
+      <c r="U74" s="5"/>
+      <c r="V74" t="s">
+        <v>10</v>
+      </c>
+      <c r="W74" t="s">
+        <v>3</v>
+      </c>
+      <c r="X74" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y74" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z74" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA74" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB74" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC74" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD74" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE74" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF74" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG74" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH74" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:34">
+      <c r="A75" t="s">
+        <v>200</v>
+      </c>
+      <c r="B75" t="s">
+        <v>40</v>
+      </c>
+      <c r="C75" t="s">
+        <v>48</v>
+      </c>
+      <c r="D75" t="s">
+        <v>3</v>
+      </c>
+      <c r="E75" t="s">
+        <v>4</v>
+      </c>
+      <c r="F75" t="s">
+        <v>45</v>
+      </c>
+      <c r="G75" t="s">
+        <v>46</v>
+      </c>
+      <c r="H75" s="2">
+        <v>1</v>
+      </c>
+      <c r="I75" t="s">
+        <v>7</v>
+      </c>
+      <c r="J75" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="K75" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L75" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="M75" t="s">
+        <v>8</v>
+      </c>
+      <c r="N75" s="2">
+        <v>0</v>
+      </c>
+      <c r="O75" s="2">
+        <v>0</v>
+      </c>
+      <c r="P75" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="Q75" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="R75" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="S75" t="s">
+        <v>202</v>
+      </c>
+      <c r="T75" s="5"/>
+      <c r="U75" s="5"/>
+      <c r="V75" t="s">
+        <v>10</v>
+      </c>
+      <c r="W75" t="s">
+        <v>3</v>
+      </c>
+      <c r="X75" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y75" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z75" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA75" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB75" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC75" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD75" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE75" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF75" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG75" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH75" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:34">
+      <c r="A76" t="s">
+        <v>200</v>
+      </c>
+      <c r="B76" t="s">
+        <v>40</v>
+      </c>
+      <c r="C76" t="s">
+        <v>52</v>
+      </c>
+      <c r="D76" t="s">
+        <v>3</v>
+      </c>
+      <c r="E76" t="s">
+        <v>4</v>
+      </c>
+      <c r="F76" t="s">
+        <v>49</v>
+      </c>
+      <c r="G76" t="s">
+        <v>50</v>
+      </c>
+      <c r="H76" s="2">
+        <v>1</v>
+      </c>
+      <c r="I76" t="s">
+        <v>7</v>
+      </c>
+      <c r="J76" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="K76" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L76" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="M76" t="s">
+        <v>8</v>
+      </c>
+      <c r="N76" s="2">
+        <v>0</v>
+      </c>
+      <c r="O76" s="2">
+        <v>0</v>
+      </c>
+      <c r="P76" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="Q76" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="R76" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="S76" t="s">
+        <v>203</v>
+      </c>
+      <c r="T76" s="5"/>
+      <c r="U76" s="5"/>
+      <c r="V76" t="s">
+        <v>10</v>
+      </c>
+      <c r="W76" t="s">
+        <v>3</v>
+      </c>
+      <c r="X76" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y76" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z76" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA76" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB76" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC76" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD76" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE76" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF76" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG76" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH76" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:34">
+      <c r="A77" t="s">
+        <v>200</v>
+      </c>
+      <c r="B77" t="s">
+        <v>40</v>
+      </c>
+      <c r="C77" t="s">
+        <v>76</v>
+      </c>
+      <c r="D77" t="s">
+        <v>3</v>
+      </c>
+      <c r="E77" t="s">
+        <v>4</v>
+      </c>
+      <c r="F77" t="s">
+        <v>53</v>
+      </c>
+      <c r="G77" t="s">
+        <v>54</v>
+      </c>
+      <c r="H77" s="2">
+        <v>1</v>
+      </c>
+      <c r="I77" t="s">
+        <v>7</v>
+      </c>
+      <c r="J77" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="K77" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L77" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="M77" t="s">
+        <v>8</v>
+      </c>
+      <c r="N77" s="2">
+        <v>0</v>
+      </c>
+      <c r="O77" s="2">
+        <v>0</v>
+      </c>
+      <c r="P77" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="Q77" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="R77" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="S77" t="s">
+        <v>204</v>
+      </c>
+      <c r="T77" s="5"/>
+      <c r="U77" s="5"/>
+      <c r="V77" t="s">
+        <v>10</v>
+      </c>
+      <c r="W77" t="s">
+        <v>3</v>
+      </c>
+      <c r="X77" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y77" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z77" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA77" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB77" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC77" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD77" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE77" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF77" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG77" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH77" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:34">
+      <c r="A78" t="s">
+        <v>205</v>
+      </c>
+      <c r="B78" t="s">
+        <v>125</v>
+      </c>
+      <c r="C78" t="s">
+        <v>69</v>
+      </c>
+      <c r="D78" t="s">
+        <v>3</v>
+      </c>
+      <c r="E78" t="s">
+        <v>4</v>
+      </c>
+      <c r="F78" t="s">
+        <v>19</v>
+      </c>
+      <c r="G78" t="s">
+        <v>20</v>
+      </c>
+      <c r="H78" s="2">
+        <v>1</v>
+      </c>
+      <c r="I78" t="s">
+        <v>7</v>
+      </c>
+      <c r="J78" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="K78" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="L78" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="M78" t="s">
+        <v>8</v>
+      </c>
+      <c r="N78" s="2">
+        <v>0</v>
+      </c>
+      <c r="O78" s="2">
+        <v>0</v>
+      </c>
+      <c r="P78" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="Q78" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="R78" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="S78" t="s">
+        <v>206</v>
+      </c>
+      <c r="T78" s="5"/>
+      <c r="U78" s="5"/>
+      <c r="V78" t="s">
+        <v>10</v>
+      </c>
+      <c r="W78" t="s">
+        <v>3</v>
+      </c>
+      <c r="X78" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y78" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z78" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA78" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB78" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC78" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD78" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE78" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF78" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG78" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH78" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:34">
+      <c r="A79" t="s">
+        <v>207</v>
+      </c>
+      <c r="B79" t="s">
+        <v>125</v>
+      </c>
+      <c r="C79" t="s">
+        <v>41</v>
+      </c>
+      <c r="D79" t="s">
+        <v>3</v>
+      </c>
+      <c r="E79" t="s">
+        <v>4</v>
+      </c>
+      <c r="F79" t="s">
+        <v>19</v>
+      </c>
+      <c r="G79" t="s">
+        <v>20</v>
+      </c>
+      <c r="H79" s="2">
+        <v>1</v>
+      </c>
+      <c r="I79" t="s">
+        <v>7</v>
+      </c>
+      <c r="J79" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="K79" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="L79" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="M79" t="s">
+        <v>8</v>
+      </c>
+      <c r="N79" s="2">
+        <v>0</v>
+      </c>
+      <c r="O79" s="2">
+        <v>0</v>
+      </c>
+      <c r="P79" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="Q79" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="R79" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="S79" t="s">
+        <v>208</v>
+      </c>
+      <c r="T79" s="5"/>
+      <c r="U79" s="5"/>
+      <c r="V79" t="s">
+        <v>10</v>
+      </c>
+      <c r="W79" t="s">
+        <v>3</v>
+      </c>
+      <c r="X79" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y79" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z79" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA79" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB79" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC79" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD79" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE79" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF79" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG79" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH79" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:34">
+      <c r="A80" t="s">
+        <v>209</v>
+      </c>
+      <c r="B80" t="s">
+        <v>125</v>
+      </c>
+      <c r="C80" t="s">
+        <v>41</v>
+      </c>
+      <c r="D80" t="s">
+        <v>3</v>
+      </c>
+      <c r="E80" t="s">
+        <v>4</v>
+      </c>
+      <c r="F80" t="s">
+        <v>19</v>
+      </c>
+      <c r="G80" t="s">
+        <v>20</v>
+      </c>
+      <c r="H80" s="2">
+        <v>1</v>
+      </c>
+      <c r="I80" t="s">
+        <v>7</v>
+      </c>
+      <c r="J80" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="K80" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="L80" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="M80" t="s">
+        <v>8</v>
+      </c>
+      <c r="N80" s="2">
+        <v>0</v>
+      </c>
+      <c r="O80" s="2">
+        <v>0</v>
+      </c>
+      <c r="P80" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="Q80" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="R80" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="S80" t="s">
+        <v>210</v>
+      </c>
+      <c r="T80" s="5"/>
+      <c r="U80" s="5"/>
+      <c r="V80" t="s">
+        <v>10</v>
+      </c>
+      <c r="W80" t="s">
+        <v>3</v>
+      </c>
+      <c r="X80" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y80" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z80" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA80" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB80" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC80" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD80" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE80" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF80" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG80" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH80" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:34">
+      <c r="A81" t="s">
+        <v>211</v>
+      </c>
+      <c r="B81" t="s">
+        <v>125</v>
+      </c>
+      <c r="C81" t="s">
+        <v>69</v>
+      </c>
+      <c r="D81" t="s">
+        <v>3</v>
+      </c>
+      <c r="E81" t="s">
+        <v>4</v>
+      </c>
+      <c r="F81" t="s">
+        <v>19</v>
+      </c>
+      <c r="G81" t="s">
+        <v>20</v>
+      </c>
+      <c r="H81" s="2">
+        <v>1</v>
+      </c>
+      <c r="I81" t="s">
+        <v>7</v>
+      </c>
+      <c r="J81" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="K81" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="L81" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="M81" t="s">
+        <v>8</v>
+      </c>
+      <c r="N81" s="2">
+        <v>0</v>
+      </c>
+      <c r="O81" s="2">
+        <v>0</v>
+      </c>
+      <c r="P81" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="Q81" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="R81" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="S81" t="s">
+        <v>212</v>
+      </c>
+      <c r="T81" s="5"/>
+      <c r="U81" s="5"/>
+      <c r="V81" t="s">
+        <v>10</v>
+      </c>
+      <c r="W81" t="s">
+        <v>3</v>
+      </c>
+      <c r="X81" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y81" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z81" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA81" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB81" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC81" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD81" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE81" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF81" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG81" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH81" t="s">
         <v>3</v>
       </c>
     </row>
